--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -6,6 +6,11 @@
     <sheet state="visible" name="Реєстр" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="Спірні" sheetId="2" r:id="rId6"/>
     <sheet state="visible" name="Розподіл розділів" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="Валюх" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="Вориняк" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="Журавський" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="Оліневич" sheetId="7" r:id="rId11"/>
+    <sheet state="visible" name="Оніщук" sheetId="8" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -13,219 +18,264 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="225">
+  <si>
+    <t>Учасник</t>
+  </si>
   <si>
     <t>№</t>
   </si>
   <si>
+    <t>Розділи SRS</t>
+  </si>
+  <si>
+    <t>ID вимоги / Розділ</t>
+  </si>
+  <si>
     <t>ID вимоги</t>
   </si>
   <si>
     <t>Критерій</t>
   </si>
   <si>
+    <t>Опис первинного дефекту</t>
+  </si>
+  <si>
     <t>Опис дефекту</t>
   </si>
   <si>
+    <t>Аргумент Аудитора-опонента</t>
+  </si>
+  <si>
     <t>Пропозиція виправлення</t>
   </si>
   <si>
+    <t>Рішення Керівника тестування</t>
+  </si>
+  <si>
+    <t>Валюх Артем</t>
+  </si>
+  <si>
+    <t>1, 3</t>
+  </si>
+  <si>
     <t>Хто знайшов</t>
   </si>
   <si>
-    <t>Учасник</t>
+    <t>Вориняк Василь</t>
   </si>
   <si>
     <t>F-30</t>
   </si>
   <si>
-    <t>ID вимоги / Розділ</t>
-  </si>
-  <si>
     <t>Повнота</t>
   </si>
   <si>
-    <t>Опис первинного дефекту</t>
-  </si>
-  <si>
-    <t>Аргумент Аудитора-опонента</t>
-  </si>
-  <si>
-    <t>Вимога описує успішний пошук, але не вказує реакцію системи на некоректні дати (наприклад, виїзд раніше за заїзд).</t>
-  </si>
-  <si>
-    <t>Рішення Керівника тестування</t>
+    <t>(п. 2.1) Вимога описує успішний пошук, але не вказує реакцію системи на некоректні дати (наприклад, виїзд раніше за заїзд).</t>
   </si>
   <si>
     <t>«Якщо дати некоректні, система не виконує пошук, показує повідомлення про помилку біля поля та зберігає введені дані».</t>
   </si>
   <si>
+    <t>2, 4, 6</t>
+  </si>
+  <si>
     <t>Журавський В.</t>
   </si>
   <si>
     <t>2.1 (Ролі)</t>
   </si>
   <si>
-    <t>Розділи SRS</t>
-  </si>
-  <si>
-    <t>Валюх Артем</t>
+    <t>Менеджер не має інтерфейсу, але користується правами адміністратора, що суперечить ролі.</t>
+  </si>
+  <si>
+    <t>Не доведена суперечність.</t>
   </si>
   <si>
     <t>F-40</t>
   </si>
   <si>
+    <t>Вилучено з реєстру.</t>
+  </si>
+  <si>
     <t>Тестопридатність</t>
   </si>
   <si>
+    <t>(п. 6.1) Слова «швидко», «ніколи» та «працює без помилок за будь-яких умов» не містять вимірюваних метрик.</t>
+  </si>
+  <si>
+    <t>Журавський Владислав</t>
+  </si>
+  <si>
+    <t>3, 5</t>
+  </si>
+  <si>
+    <t>«Система показує перелік вільних номерів не пізніше ніж через 2 с після натискання; зайняті номери не відображаються».</t>
+  </si>
+  <si>
+    <t>Оліневич Богдан</t>
+  </si>
+  <si>
+    <t>2.2 (Середовище)</t>
+  </si>
+  <si>
+    <t>1, 4, 6</t>
+  </si>
+  <si>
+    <t>Валюх А., Журавський В.</t>
+  </si>
+  <si>
+    <t>Оніщук Максим</t>
+  </si>
+  <si>
+    <t>Наявність залежностей Maven/JUnit суперечить твердженню «без зовнішніх залежностей».</t>
+  </si>
+  <si>
+    <t>2, 5</t>
+  </si>
+  <si>
+    <t>Maven/JUnit не обов'язково суперечать відсутності runtime-залежностей.</t>
+  </si>
+  <si>
+    <t>F-50 / GUI-50</t>
+  </si>
+  <si>
+    <t>Несуперечливість</t>
+  </si>
+  <si>
+    <t>(п. 3.1) F-50 визначає Service fee як £15, а GUI-50 для того самого блоку встановлює £10.</t>
+  </si>
+  <si>
+    <t>«Service fee» £10 (узгоджено з GUI-50).</t>
+  </si>
+  <si>
+    <t>Валюх А., Оліневич Б., Вориняк В.</t>
+  </si>
+  <si>
+    <t>F-60</t>
+  </si>
+  <si>
+    <t>Однозначність</t>
+  </si>
+  <si>
+    <t>Розділ 2</t>
+  </si>
+  <si>
+    <t>(п. 1.1) Фраза «надсилає гостю підтвердження» не визначає канал зв'язку (email, SMS) та конкретний склад повідомлення.</t>
+  </si>
+  <si>
     <t>Слова «швидко», «ніколи» та «працює без помилок за будь-яких умов» не містять вимірюваних метрик.</t>
   </si>
   <si>
-    <t>«Система показує перелік вільних номерів не пізніше ніж через 2 с після натискання; зайняті номери не відображаються». (Час 2 с потребує погодження).</t>
-  </si>
-  <si>
-    <t>Менеджер не має інтерфейсу, але користується правами адміністратора, що суперечить ролі.</t>
-  </si>
-  <si>
-    <t>Валюх А., Журавський В.</t>
-  </si>
-  <si>
-    <t>1, 3</t>
-  </si>
-  <si>
-    <t>F-50 / GUI-50</t>
-  </si>
-  <si>
-    <t>Несуперечливість</t>
-  </si>
-  <si>
-    <t>F-50 визначає Service fee як £15, а GUI-50 для того самого блоку встановлює £10.</t>
-  </si>
-  <si>
-    <t>Не доведена суперечність.</t>
-  </si>
-  <si>
-    <t>Вориняк Василь</t>
-  </si>
-  <si>
-    <t>Встановити однакове значення. Конкретна сума потребує підтвердження замовником.</t>
-  </si>
-  <si>
-    <t>Вилучено з реєстру.</t>
-  </si>
-  <si>
-    <t>Валюх А., Оліневич Б., Вориняк В.</t>
-  </si>
-  <si>
-    <t>2, 4, 6</t>
-  </si>
-  <si>
-    <t>F-60</t>
-  </si>
-  <si>
-    <t>Однозначність</t>
-  </si>
-  <si>
-    <t>Фраза «надсилає гостю підтвердження» не визначає канал зв'язку (email, SMS) та конкретний склад повідомлення.</t>
-  </si>
-  <si>
     <t>«Після успішного бронювання система надсилає на email гостя лист із номером бронювання, типом номера, датами та вартістю».</t>
   </si>
   <si>
-    <t>Журавський Владислав</t>
-  </si>
-  <si>
-    <t>3, 5</t>
-  </si>
-  <si>
-    <t>Оліневич Богдан</t>
-  </si>
-  <si>
-    <t>1, 4, 6</t>
+    <t>Жоден елемент розділу (ролі, обмеження) не має ідентифікатора (ID).</t>
+  </si>
+  <si>
+    <t>Усі елементи без ID — надто широке трактування для дефекту простежуваності.</t>
+  </si>
+  <si>
+    <t>«Система показує перелік вільних номерів не пізніше ніж через 2 с після натискання».</t>
+  </si>
+  <si>
+    <t>BL-70</t>
+  </si>
+  <si>
+    <t>Не описана поведінка системи (Race condition) при одночасному бронюванні номера.</t>
+  </si>
+  <si>
+    <t>Це радше додавання нової вимоги, ніж очевидний дефект наявної специфікації.</t>
   </si>
   <si>
     <t>F-80</t>
   </si>
   <si>
-    <t>2.2 (Середовище)</t>
-  </si>
-  <si>
     <t>Простежуваність</t>
   </si>
   <si>
-    <t>Оніщук Максим</t>
-  </si>
-  <si>
-    <t>Ідентифікатор F-80 використано двічі: для вимоги про вхід (Login) і для вимоги про вихід (Logout).</t>
-  </si>
-  <si>
-    <t>Наявність залежностей Maven/JUnit суперечить твердженню «без зовнішніх залежностей».</t>
+    <t>(п. 4.1) Ідентифікатор F-80 використано двічі: для вимоги про вхід (Login) і для вимоги про вихід (Logout).</t>
   </si>
   <si>
     <t>Залишити F-80 для входу, а вимозі про завершення сеансу присвоїти вільний ID F-85.</t>
   </si>
   <si>
-    <t>2, 5</t>
+    <t>F-50</t>
   </si>
   <si>
     <t>F-100</t>
   </si>
   <si>
-    <t>Формулювання «може обробити повідомлення» не визначає, що саме означає обробка (прочитати, відповісти, видалити).</t>
+    <t>Розділ 6</t>
+  </si>
+  <si>
+    <t>F-50 визначає Service fee як £15, хоча нижче в розділі 4 вказано іншу суму.</t>
+  </si>
+  <si>
+    <t>(п. 1.1) Формулювання «може обробити повідомлення» не визначає, що саме означає обробка (прочитати, відповісти, видалити).</t>
   </si>
   <si>
     <t>«Адміністратор відкриває повідомлення, переглядає текст і позначає його прочитаним; позначка "непрочитане" зникає».</t>
   </si>
   <si>
-    <t>Maven/JUnit не обов'язково суперечать відсутності runtime-залежностей.</t>
+    <t>Відсутня вимога щодо реакції системи на відмову платіжного провайдера.</t>
+  </si>
+  <si>
+    <t>Встановити однакове значення скрізь.</t>
+  </si>
+  <si>
+    <t>Некоректно, бо онлайн-оплата прямо винесена за межі продукту (розд. 1.2).</t>
   </si>
   <si>
     <t>F-110 / BL-60</t>
   </si>
   <si>
-    <t>У F-110 безкоштовне скасування можливе за 5 і більше днів, а в бізнес-логіці (BL-60) — за 7 і більше днів.</t>
-  </si>
-  <si>
-    <t>Узгодити єдину політику для F-110 та BL-60. Остаточний поріг (5 чи 7 днів) затверджує замовник.</t>
-  </si>
-  <si>
-    <t>Розділ 2</t>
+    <t>(п. 3.1) У F-110 безкоштовне скасування можливе за 5 і більше днів, а в бізнес-логіці (BL-60) — за 7 і більше днів.</t>
+  </si>
+  <si>
+    <t>Безкоштовне скасування за 7 або більше днів (узгоджено з BL-60).</t>
+  </si>
+  <si>
+    <t>Фраза «надсилає гостю підтвердження» не визначає канал зв'язку (email, SMS).</t>
+  </si>
+  <si>
+    <t>«Система надсилає на email гостя лист із номером бронювання».</t>
   </si>
   <si>
     <t>F-120</t>
   </si>
   <si>
-    <t>Жоден елемент розділу (ролі, обмеження) не має ідентифікатора (ID).</t>
-  </si>
-  <si>
     <t>Здійсненність</t>
   </si>
   <si>
-    <t>Усі елементи без ID — надто широке трактування для дефекту простежуваності.</t>
-  </si>
-  <si>
-    <t>Вимога передбачає звіт за майбутній період на основі «фактичних даних про заселення», яких у майбутньому ще не існує.</t>
+    <t>(п. 5.1) Вимога передбачає звіт за майбутній період на основі «фактичних даних про заселення», яких у майбутньому ще не існує.</t>
+  </si>
+  <si>
+    <t>Ідентифікатор F-80 використано двічі: для Login і для Logout.</t>
   </si>
   <si>
     <t>«Для майбутніх періодів формується прогноз заповнюваності на основі підтверджених бронювань».</t>
   </si>
   <si>
-    <t>BL-70</t>
-  </si>
-  <si>
-    <t>Не описана поведінка системи (Race condition) при одночасному бронюванні номера.</t>
-  </si>
-  <si>
-    <t>Це радше додавання нової вимоги, ніж очевидний дефект наявної специфікації.</t>
+    <t>Залишити F-80 для входу, а виходу дати вільний ID F-85.</t>
+  </si>
+  <si>
+    <t>F-110</t>
+  </si>
+  <si>
+    <t>У F-110 безкоштовне скасування можливе за 5 днів, а в бізнес-логіці — за 7.</t>
+  </si>
+  <si>
+    <t>Узгодити єдину політику для системи.</t>
   </si>
   <si>
     <t>GUI-20</t>
   </si>
   <si>
-    <t>Вказано, що дата відображається у двох форматах «залежно від налаштувань», але не визначено джерело цих налаштувань.</t>
-  </si>
-  <si>
-    <t>«Поля відображають дату у єдиному форматі дд/мм/рррр», або чітко вказати джерело (наприклад, локаль браузера).</t>
+    <t>(п. 1.1) Вказано, що дата відображається у двох форматах «залежно від налаштувань», але не визначено джерело цих налаштувань.</t>
+  </si>
+  <si>
+    <t>«Поля відображають дату у єдиному форматі дд/мм/рррр».</t>
   </si>
   <si>
     <t>Оліневич Б., Вориняк В.</t>
@@ -234,34 +284,28 @@
     <t>GUI-40</t>
   </si>
   <si>
-    <t>Розділ 6</t>
-  </si>
-  <si>
-    <t>Форма бронювання описана полями Firstname, Lastname, Email, але пропущено обов'язкове поле Phone, яке вимагає F-60.</t>
+    <t>(п. 2.1) Форма бронювання описана полями Firstname, Lastname, Email, але пропущено обов'язкове поле Phone, яке вимагає F-60.</t>
   </si>
   <si>
     <t>Додати до переліку полів форми GUI-40 поле Phone із відповідною підказкою.</t>
   </si>
   <si>
+    <t>Вимога передбачає звіт за майбутній період на основі фактичних даних, яких ще не існує.</t>
+  </si>
+  <si>
     <t>GUI-60</t>
   </si>
   <si>
-    <t>Відсутня вимога щодо реакції системи на відмову платіжного провайдера.</t>
-  </si>
-  <si>
-    <t>Вимога, щоб повідомлення були «доброзичливими і не дратувати гостя», є суб'єктивною і не перевіряється.</t>
+    <t>(п. 6.1) Вимога, щоб повідомлення були «доброзичливими і не дратувати гостя», є суб'єктивною і не перевіряється.</t>
   </si>
   <si>
     <t>«Повідомлення про помилку містить назву поля та причину відхилення без технічних кодів».</t>
   </si>
   <si>
-    <t>Некоректно, бо онлайн-оплата прямо винесена за межі продукту (розд. 1.2).</t>
-  </si>
-  <si>
     <t>GUI-70</t>
   </si>
   <si>
-    <t>Опис сторінки входу (Login) містить у шапці кнопку Logout, хоча користувач ще не автентифікований.</t>
+    <t>(п. 3.1) Опис сторінки входу (Login) містить у шапці кнопку Logout, хоча користувач ще не автентифікований.</t>
   </si>
   <si>
     <t>Прибрати Logout з опису сторінки входу й перенести в опис шапки адмінпанелі після успішного входу.</t>
@@ -273,115 +317,382 @@
     <t>GUI-80</t>
   </si>
   <si>
-    <t>Вимога вимагає, щоб кнопка була «неактивна», але водночас каже, що «при натисканні з порожніми полями система показує помилки».</t>
-  </si>
-  <si>
-    <t>Залишити кнопку активною для показу помилок при валідації, АБО зробити її неактивною і показувати помилки під час введення.</t>
+    <t>(п. 3.1) Вимога вимагає, щоб кнопка була «неактивна», але водночас каже, що «при натисканні з порожніми полями система показує помилки».</t>
+  </si>
+  <si>
+    <t>Кнопка залишається активною для показу помилок при валідації.</t>
   </si>
   <si>
     <t>Розділ 4 (Форма)</t>
   </si>
   <si>
+    <t>(п. 4.1) Вимога до форми «Send Us a Message» взагалі не має ідентифікатора.</t>
+  </si>
+  <si>
+    <t>Присвоїти цій вимозі унікальний ідентифікатор GUI-85.</t>
+  </si>
+  <si>
+    <t>GUI-90</t>
+  </si>
+  <si>
+    <t>(п. 5.1) Вимога «піксель-у-піксель» відображення на «всіх пристроях, включно з телефонами без браузера» нездійсненна.</t>
+  </si>
+  <si>
+    <t>«Інтерфейс зберігає адаптивну структуру та читабельність у підтримуваних версіях Chrome і Firefox».</t>
+  </si>
+  <si>
+    <t>BL-10</t>
+  </si>
+  <si>
+    <t>(п. 2.1) Метод validate приймає guests та capacity, але перелік перевірок не містить логіки перевірки на перевищення місткості.</t>
+  </si>
+  <si>
+    <t>Додати умову: «Метод перевіряє, що guests &gt;= 1 та guests &lt;= capacity; при порушенні повертає код помилки».</t>
+  </si>
+  <si>
+    <t>BL-30</t>
+  </si>
+  <si>
+    <t>(п. 1.1) Надбавка за «вихідні дні» не конкретизує, які саме ночі вважаються вихідними (п'ятниця-субота чи субота-неділя).</t>
+  </si>
+  <si>
+    <t>Чітко визначити дні: «за ночі з суботи на неділю та з неділі на понеділок».</t>
+  </si>
+  <si>
+    <t>Оніщук М., Журавський В.</t>
+  </si>
+  <si>
+    <t>BL-80</t>
+  </si>
+  <si>
+    <t>(п. 4.1) Вимога BL-80 повністю дублює бізнес-логіку плати за скасування, яка вже описана у BL-60, що створює ризик неузгодженості.</t>
+  </si>
+  <si>
+    <t>Текст вимоги замінено на посилання на правила, описані у вимозі BL-60.</t>
+  </si>
+  <si>
+    <t>Оніщук М.</t>
+  </si>
+  <si>
+    <t>P-10</t>
+  </si>
+  <si>
+    <t>(п. 5.1) Завантаження сторінки «не довше ніж за 50 мс за будь-якого з'єднання (включно з 2G)» неможливе через затримки мережі.</t>
+  </si>
+  <si>
+    <t>«Сторінка завантажується не довше ніж за 2 с на 4G-з'єднанні».</t>
+  </si>
+  <si>
+    <t>P-20</t>
+  </si>
+  <si>
+    <t>(п. 6.1) Вимога витримати «велике навантаження без деградації продуктивності» не містить метрик і кількості користувачів.</t>
+  </si>
+  <si>
+    <t>«Система підтримує 200 користувачів одночасно протягом 15 хв; 95-й перцентиль відповіді ≤ 2 с».</t>
+  </si>
+  <si>
+    <t>S-10</t>
+  </si>
+  <si>
+    <t>(п. 5.1) Гарантія «100% захисту від будь-яких невідомих кібератак» неможлива для реалізації та доведення.</t>
+  </si>
+  <si>
+    <t>«Застосунок не містить уразливостей рівня High/Critical за списком OWASP Top 10 на момент релізу».</t>
+  </si>
+  <si>
+    <t>U-10</t>
+  </si>
+  <si>
+    <t>(п. 6.1) Формулювання «інтуїтивно зрозумілий» не піддається об'єктивному вимірюванню.</t>
+  </si>
+  <si>
+    <t>«Не менше 80% нових користувачів успішно завершують тестове бронювання за ≤ 3 хвилини без підказок».</t>
+  </si>
+  <si>
+    <t>U-20</t>
+  </si>
+  <si>
+    <t>(п. 4.1) Вимога посилається на єдину схему розмітки «у вимозі GUI-120», якої взагалі не існує в документі.</t>
+  </si>
+  <si>
+    <t>Посилання на GUI-120 вилучено, базові вимоги (мітка над полем) консолідовано в існуючі.</t>
+  </si>
+  <si>
+    <t>D-20</t>
+  </si>
+  <si>
+    <t>(п. 4.1) Посилання на стандарт оформлення «SN-DOC-07» недійсне, оскільки його немає в переліку посилань (розділ 1.4).</t>
+  </si>
+  <si>
+    <t>Документ SN-DOC-07 додано до переліку посилань (1.4).</t>
+  </si>
+  <si>
+    <t>Менеджер не має інтерфейсу, але користується правами адміністратора, що суперечить ролі. (Відхилено на зведенні)</t>
+  </si>
+  <si>
+    <t>Описати окремий інтерфейс для Менеджера.</t>
+  </si>
+  <si>
+    <t>Жоден елемент розділу (ролі, обмеження) не має ідентифікатора (ID). (Відхилено на зведенні)</t>
+  </si>
+  <si>
+    <t>Додати ID до кожного абзацу.</t>
+  </si>
+  <si>
+    <t>Вказано, що дата відображається «залежно від налаштувань», але не вказано яких.</t>
+  </si>
+  <si>
+    <t>Задати жорстко формат дд/мм/рррр.</t>
+  </si>
+  <si>
+    <t>Форма описана без обов'язкового поля Phone.</t>
+  </si>
+  <si>
+    <t>Додати Phone до переліку полів форми.</t>
+  </si>
+  <si>
+    <t>GUI-50</t>
+  </si>
+  <si>
+    <t>У блоці «Price Summary» Service fee встановлено £10, а у вимозі функціоналу — £15.</t>
+  </si>
+  <si>
+    <t>Встановити однакову суму.</t>
+  </si>
+  <si>
+    <t>Вимога, щоб повідомлення були «доброзичливими», є суб'єктивною.</t>
+  </si>
+  <si>
+    <t>Написати, що повідомлення має містити назву поля та причину відмови.</t>
+  </si>
+  <si>
+    <t>Опис сторінки входу (Login) містить у шапці кнопку Logout для неавторизованих гостей.</t>
+  </si>
+  <si>
+    <t>Прибрати Logout з опису сторінки входу.</t>
+  </si>
+  <si>
+    <t>Вимога каже, що кнопка неактивна, але показує помилки при натисканні.</t>
+  </si>
+  <si>
+    <t>Залишити кнопку активною для показу помилок.</t>
+  </si>
+  <si>
+    <t>Форма (розд. 4)</t>
+  </si>
+  <si>
     <t>Вимога до форми «Send Us a Message» взагалі не має ідентифікатора.</t>
   </si>
   <si>
-    <t>Присвоїти цій вимозі унікальний ідентифікатор GUI-85.</t>
-  </si>
-  <si>
-    <t>GUI-90</t>
-  </si>
-  <si>
-    <t>Вимога «піксель-у-піксель» відображення на «всіх пристроях, включно з телефонами без браузера» нездійсненна.</t>
-  </si>
-  <si>
-    <t>«Інтерфейс зберігає адаптивну структуру та читабельність у підтримуваних версіях Chrome і Firefox».</t>
-  </si>
-  <si>
-    <t>BL-10</t>
-  </si>
-  <si>
-    <t>Метод validate приймає guests та capacity, але перелік перевірок не містить логіки перевірки на перевищення місткості.</t>
-  </si>
-  <si>
-    <t>Додати умову: «Метод перевіряє, що guests &gt;= 1 та guests &lt;= capacity; при порушенні повертає код помилки».</t>
-  </si>
-  <si>
-    <t>BL-30</t>
-  </si>
-  <si>
-    <t>Надбавка за «вихідні дні» не конкретизує, які саме ночі вважаються вихідними (п'ятниця-субота чи субота-неділя).</t>
-  </si>
-  <si>
-    <t>Чітко визначити дні: «за ночі з суботи на неділю та з неділі на понеділок» (потребує підтвердження замовником).</t>
-  </si>
-  <si>
-    <t>Оніщук М., Журавський В.</t>
-  </si>
-  <si>
-    <t>BL-80</t>
-  </si>
-  <si>
-    <t>Вимога BL-80 повністю дублює бізнес-логіку плати за скасування, яка вже описана у BL-60, що створює ризик неузгодженості.</t>
-  </si>
-  <si>
-    <t>Видалити BL-80 як дублікат, або залишити в ній лише посилання на алгоритм із BL-60.</t>
-  </si>
-  <si>
-    <t>Оніщук М.</t>
-  </si>
-  <si>
-    <t>P-10</t>
-  </si>
-  <si>
-    <t>Завантаження сторінки «не довше ніж за 50 мс за будь-якого з'єднання (включно з 2G)» неможливе через затримки мережі.</t>
-  </si>
-  <si>
-    <t>«Сторінка завантажується не довше ніж за 2 с на 4G-з'єднанні» (значення потребує погодження).</t>
-  </si>
-  <si>
-    <t>P-20</t>
-  </si>
-  <si>
-    <t>Вимога витримати «велике навантаження без деградації продуктивності» не містить метрик і кількості користувачів.</t>
-  </si>
-  <si>
-    <t>«Система підтримує 200 користувачів одночасно протягом 15 хв; 95-й перцентиль відповіді ≤ 2 с».</t>
-  </si>
-  <si>
-    <t>S-10</t>
-  </si>
-  <si>
-    <t>Гарантія «100% захисту від будь-яких невідомих кібератак» неможлива для реалізації та доведення.</t>
-  </si>
-  <si>
-    <t>«Застосунок не містить уразливостей рівня High/Critical за списком OWASP Top 10 на момент релізу».</t>
-  </si>
-  <si>
-    <t>U-10</t>
-  </si>
-  <si>
-    <t>Формулювання «інтуїтивно зрозумілий» не піддається об'єктивному вимірюванню.</t>
-  </si>
-  <si>
-    <t>«Не менше 80% нових користувачів успішно завершують тестове бронювання за ≤ 3 хвилини без підказок».</t>
-  </si>
-  <si>
-    <t>U-20</t>
-  </si>
-  <si>
-    <t>Вимога посилається на єдину схему розмітки «у вимозі GUI-120», якої взагалі не існує в документі.</t>
-  </si>
-  <si>
-    <t>Виправити посилання на існуючу вимогу розділу 4, або додати GUI-120 з описом цієї схеми розмітки.</t>
-  </si>
-  <si>
-    <t>D-20</t>
-  </si>
-  <si>
-    <t>Посилання на стандарт оформлення «SN-DOC-07» недійсне, оскільки його немає в переліку посилань (розділ 1.4).</t>
-  </si>
-  <si>
-    <t>Додати SN-DOC-07 до переліку посилань (1.4) або прибрати згадку і виписати вимоги до довідки напряму.</t>
+    <t>Присвоїти унікальний ідентифікатор GUI-85.</t>
+  </si>
+  <si>
+    <t>Вимога «піксель-у-піксель» відображення на «всіх пристроях» нездійсненна.</t>
+  </si>
+  <si>
+    <t>«Адаптивна структура у Chrome і Firefox».</t>
+  </si>
+  <si>
+    <t>Завантаження «не довше ніж за 50 мс за будь-якого з'єднання» неможливе.</t>
+  </si>
+  <si>
+    <t>«Не довше ніж за 2 с на 4G-з'єднанні».</t>
+  </si>
+  <si>
+    <t>«Велике навантаження без деградації» не містить метрик.</t>
+  </si>
+  <si>
+    <t>Вказати: 200 користувачів, 15 хв, відповідь ≤ 2 с.</t>
+  </si>
+  <si>
+    <t>«100% захист від невідомих кібератак» неможливий.</t>
+  </si>
+  <si>
+    <t>Відсутність вразливостей High/Critical за OWASP.</t>
+  </si>
+  <si>
+    <t>Формулювання «інтуїтивно зрозумілий» не вимірюється.</t>
+  </si>
+  <si>
+    <t>Вказати, що 80% нових користувачів завершують тест за 3 хв.</t>
+  </si>
+  <si>
+    <t>Посилання на неіснуючу вимогу GUI-120.</t>
+  </si>
+  <si>
+    <t>Видалити посилання на неіснуючу вимогу.</t>
+  </si>
+  <si>
+    <t>Посилання на стандарт оформлення «SN-DOC-07» недійсне, бо його немає в посиланнях.</t>
+  </si>
+  <si>
+    <t>Додати SN-DOC-07 до розділу 1.4.</t>
+  </si>
+  <si>
+    <t>Відсутня вимога щодо реакції системи на відмову платіжного провайдера. (Відхилено на зведенні)</t>
+  </si>
+  <si>
+    <t>Дописати обробку відмови платежу.</t>
+  </si>
+  <si>
+    <t>Незрозуміло звідки беруться налаштування формату дати.</t>
+  </si>
+  <si>
+    <t>Зробити єдиний формат для всіх.</t>
+  </si>
+  <si>
+    <t>У формі бронювання пропущено номер телефону.</t>
+  </si>
+  <si>
+    <t>Додати поле Phone.</t>
+  </si>
+  <si>
+    <t>У вимозі GUI-50 Service fee = £10, що розходиться з розділом функціоналу.</t>
+  </si>
+  <si>
+    <t>Узгодити одну ціну.</t>
+  </si>
+  <si>
+    <t>Вимога не дратувати гостя не піддається тестуванню.</t>
+  </si>
+  <si>
+    <t>Вказати чітко, що повідомлення показує помилку і назву поля.</t>
+  </si>
+  <si>
+    <t>Кнопка одночасно неактивна, але при натисканні показує помилки.</t>
+  </si>
+  <si>
+    <t>Або кнопка активна, або не показує помилок при кліку.</t>
+  </si>
+  <si>
+    <t>Не вказано реакцію системи на некоректні дати (наприклад, виїзд раніше за заїзд).</t>
+  </si>
+  <si>
+    <t>Контактна форма</t>
+  </si>
+  <si>
+    <t>Вимога до форми відправки не має ID.</t>
+  </si>
+  <si>
+    <t>«Система не виконує пошук, показує повідомлення про помилку біля поля».</t>
+  </si>
+  <si>
+    <t>Дати їй унікальний номер.</t>
+  </si>
+  <si>
+    <t>Працювати піксель-в-піксель на старих телефонах без браузера неможливо.</t>
+  </si>
+  <si>
+    <t>Вимагати підтримки актуальних браузерів (Chrome, Firefox).</t>
+  </si>
+  <si>
+    <t>50 мс на 2G нереалістично.</t>
+  </si>
+  <si>
+    <t>Підняти ліміт хоча б до 2 секунд на 4G.</t>
+  </si>
+  <si>
+    <t>Вимога не містить часу (просто написано «швидко»).</t>
+  </si>
+  <si>
+    <t>Відсутні метрики кількості користувачів.</t>
+  </si>
+  <si>
+    <t>Вказати ліміт у 2 секунди.</t>
+  </si>
+  <si>
+    <t>Задати 200 користувачів.</t>
+  </si>
+  <si>
+    <t>100% захист гарантувати не можна.</t>
+  </si>
+  <si>
+    <t>Описати відсутність Critical/High вразливостей.</t>
+  </si>
+  <si>
+    <t>Не визначено конкретний склад повідомлення підтвердження.</t>
+  </si>
+  <si>
+    <t>Надіслати номер бронювання, тип номера, дати та вартість.</t>
+  </si>
+  <si>
+    <t>ID F-80 дублюється для різних процесів.</t>
+  </si>
+  <si>
+    <t>Розділити на два ідентифікатори.</t>
+  </si>
+  <si>
+    <t>"Інтуїтивний" не можна заміряти.</t>
+  </si>
+  <si>
+    <t>Додати час (до 3 хвилин) для новачків.</t>
+  </si>
+  <si>
+    <t>«Обробити повідомлення» не визначає, що саме означає обробка.</t>
+  </si>
+  <si>
+    <t>«Відкриває повідомлення, переглядає текст і позначає прочитаним».</t>
+  </si>
+  <si>
+    <t>Бите посилання на GUI-120.</t>
+  </si>
+  <si>
+    <t>Прибрати посилання з тексту.</t>
+  </si>
+  <si>
+    <t>Конфлікт безкоштовного скасування між розділами (5 днів проти 7 днів).</t>
+  </si>
+  <si>
+    <t>Узгодити з розділом бізнес-логіки.</t>
+  </si>
+  <si>
+    <t>Неможливо скласти фактичний звіт за майбутнє.</t>
+  </si>
+  <si>
+    <t>Документа SN-DOC-07 немає в секції 1.4.</t>
+  </si>
+  <si>
+    <t>Замінити на формування прогнозу.</t>
+  </si>
+  <si>
+    <t>Додати стандарт до переліку 1.4.</t>
+  </si>
+  <si>
+    <t>Метод validate не містить логіки перевірки на перевищення місткості номера.</t>
+  </si>
+  <si>
+    <t>Додати умову guests &lt;= capacity.</t>
+  </si>
+  <si>
+    <t>Надбавка за «вихідні дні» не конкретизує дати.</t>
+  </si>
+  <si>
+    <t>Чітко визначити дні: субота та неділя.</t>
+  </si>
+  <si>
+    <t>Наявність залежностей Maven/JUnit суперечить твердженню «без зовнішніх залежностей». (Відхилено на зведенні)</t>
+  </si>
+  <si>
+    <t>Прибрати згадку JUnit/Maven.</t>
+  </si>
+  <si>
+    <t>Фраза про «ночі у вихідні дні» може трактуватися по-різному в різних країнах.</t>
+  </si>
+  <si>
+    <t>Написати чітко: з суботи на неділю та з неділі на понеділок.</t>
+  </si>
+  <si>
+    <t>Не описана Race condition при одночасному бронюванні одного номера. (Відхилено на зведенні)</t>
+  </si>
+  <si>
+    <t>Додати поведінку при конкурентному доступі.</t>
+  </si>
+  <si>
+    <t>BL-80 повністю дублює логіку плати за скасування, яка вже є у BL-60.</t>
+  </si>
+  <si>
+    <t>Видалити дублікат, замість цього послатися на BL-60.</t>
   </si>
 </sst>
 </file>
@@ -401,10 +712,6 @@
       <name val="Google Sans Text"/>
     </font>
     <font>
-      <color theme="1"/>
-      <name val="Google Sans Text"/>
-    </font>
-    <font>
       <b/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -414,6 +721,10 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Google Sans Text"/>
     </font>
   </fonts>
   <fills count="2">
@@ -444,7 +755,7 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color rgb="FF000000"/>
       </right>
       <top style="medium">
@@ -458,7 +769,7 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="medium">
@@ -483,12 +794,34 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -514,31 +847,9 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -589,106 +900,188 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="61">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="3" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="3" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    <xf borderId="9" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="11" fillId="0" fontId="3" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -706,6 +1099,26 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -922,4404 +1335,4904 @@
     <col customWidth="1" min="6" max="6" width="27.5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" ht="21.75" customHeight="1">
+      <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" ht="42.0" customHeight="1">
-      <c r="A2" s="4">
+      <c r="D1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="11"/>
+      <c r="V1" s="11"/>
+      <c r="W1" s="11"/>
+      <c r="X1" s="11"/>
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="11"/>
+    </row>
+    <row r="2" ht="36.0" customHeight="1">
+      <c r="A2" s="14">
         <v>1.0</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="7" t="s">
+      <c r="B2" s="15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" ht="42.0" customHeight="1">
-      <c r="A3" s="10">
+      <c r="C2" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+    </row>
+    <row r="3" ht="36.0" customHeight="1">
+      <c r="A3" s="21">
         <v>2.0</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="11"/>
+      <c r="T3" s="11"/>
+      <c r="U3" s="11"/>
+      <c r="V3" s="11"/>
+      <c r="W3" s="11"/>
+      <c r="X3" s="11"/>
+      <c r="Y3" s="11"/>
+      <c r="Z3" s="11"/>
+    </row>
+    <row r="4" ht="36.0" customHeight="1">
+      <c r="A4" s="21">
+        <v>3.0</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="11"/>
+      <c r="V4" s="11"/>
+      <c r="W4" s="11"/>
+      <c r="X4" s="11"/>
+      <c r="Y4" s="11"/>
+      <c r="Z4" s="11"/>
+    </row>
+    <row r="5" ht="36.0" customHeight="1">
+      <c r="A5" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="11"/>
+      <c r="Z5" s="11"/>
+    </row>
+    <row r="6" ht="36.0" customHeight="1">
+      <c r="A6" s="21">
+        <v>5.0</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="11"/>
+      <c r="T6" s="11"/>
+      <c r="U6" s="11"/>
+      <c r="V6" s="11"/>
+      <c r="W6" s="11"/>
+      <c r="X6" s="11"/>
+      <c r="Y6" s="11"/>
+      <c r="Z6" s="11"/>
+    </row>
+    <row r="7" ht="36.0" customHeight="1">
+      <c r="A7" s="21">
+        <v>6.0</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" ht="42.0" customHeight="1">
-      <c r="A4" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="11"/>
+      <c r="T7" s="11"/>
+      <c r="U7" s="11"/>
+      <c r="V7" s="11"/>
+      <c r="W7" s="11"/>
+      <c r="X7" s="11"/>
+      <c r="Y7" s="11"/>
+      <c r="Z7" s="11"/>
+    </row>
+    <row r="8" ht="36.0" customHeight="1">
+      <c r="A8" s="21">
+        <v>7.0</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
+      <c r="T8" s="11"/>
+      <c r="U8" s="11"/>
+      <c r="V8" s="11"/>
+      <c r="W8" s="11"/>
+      <c r="X8" s="11"/>
+      <c r="Y8" s="11"/>
+      <c r="Z8" s="11"/>
+    </row>
+    <row r="9" ht="36.0" customHeight="1">
+      <c r="A9" s="21">
+        <v>8.0</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="11"/>
+      <c r="T9" s="11"/>
+      <c r="U9" s="11"/>
+      <c r="V9" s="11"/>
+      <c r="W9" s="11"/>
+      <c r="X9" s="11"/>
+      <c r="Y9" s="11"/>
+      <c r="Z9" s="11"/>
+    </row>
+    <row r="10" ht="36.0" customHeight="1">
+      <c r="A10" s="21">
+        <v>9.0</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="11"/>
+      <c r="T10" s="11"/>
+      <c r="U10" s="11"/>
+      <c r="V10" s="11"/>
+      <c r="W10" s="11"/>
+      <c r="X10" s="11"/>
+      <c r="Y10" s="11"/>
+      <c r="Z10" s="11"/>
+    </row>
+    <row r="11" ht="36.0" customHeight="1">
+      <c r="A11" s="21">
+        <v>10.0</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="11"/>
+      <c r="T11" s="11"/>
+      <c r="U11" s="11"/>
+      <c r="V11" s="11"/>
+      <c r="W11" s="11"/>
+      <c r="X11" s="11"/>
+      <c r="Y11" s="11"/>
+      <c r="Z11" s="11"/>
+    </row>
+    <row r="12" ht="36.0" customHeight="1">
+      <c r="A12" s="21">
+        <v>11.0</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" ht="42.0" customHeight="1">
-      <c r="A5" s="10">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" ht="42.0" customHeight="1">
-      <c r="A6" s="10">
-        <v>5.0</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="D12" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
+      <c r="V12" s="11"/>
+      <c r="W12" s="11"/>
+      <c r="X12" s="11"/>
+      <c r="Y12" s="11"/>
+      <c r="Z12" s="11"/>
+    </row>
+    <row r="13" ht="36.0" customHeight="1">
+      <c r="A13" s="21">
+        <v>12.0</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
+      <c r="T13" s="11"/>
+      <c r="U13" s="11"/>
+      <c r="V13" s="11"/>
+      <c r="W13" s="11"/>
+      <c r="X13" s="11"/>
+      <c r="Y13" s="11"/>
+      <c r="Z13" s="11"/>
+    </row>
+    <row r="14" ht="36.0" customHeight="1">
+      <c r="A14" s="21">
+        <v>13.0</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="F14" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="11"/>
+      <c r="V14" s="11"/>
+      <c r="W14" s="11"/>
+      <c r="X14" s="11"/>
+      <c r="Y14" s="11"/>
+      <c r="Z14" s="11"/>
+    </row>
+    <row r="15" ht="36.0" customHeight="1">
+      <c r="A15" s="21">
+        <v>14.0</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="F15" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="11"/>
+      <c r="W15" s="11"/>
+      <c r="X15" s="11"/>
+      <c r="Y15" s="11"/>
+      <c r="Z15" s="11"/>
+    </row>
+    <row r="16" ht="36.0" customHeight="1">
+      <c r="A16" s="21">
+        <v>15.0</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="F16" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="11"/>
+      <c r="W16" s="11"/>
+      <c r="X16" s="11"/>
+      <c r="Y16" s="11"/>
+      <c r="Z16" s="11"/>
+    </row>
+    <row r="17" ht="36.0" customHeight="1">
+      <c r="A17" s="21">
+        <v>16.0</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="F17" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
+      <c r="V17" s="11"/>
+      <c r="W17" s="11"/>
+      <c r="X17" s="11"/>
+      <c r="Y17" s="11"/>
+      <c r="Z17" s="11"/>
+    </row>
+    <row r="18" ht="36.0" customHeight="1">
+      <c r="A18" s="21">
+        <v>17.0</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="C18" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" ht="42.0" customHeight="1">
-      <c r="A7" s="10">
-        <v>6.0</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" ht="42.0" customHeight="1">
-      <c r="A8" s="10">
-        <v>7.0</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="D18" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="F18" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11"/>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="11"/>
+      <c r="T18" s="11"/>
+      <c r="U18" s="11"/>
+      <c r="V18" s="11"/>
+      <c r="W18" s="11"/>
+      <c r="X18" s="11"/>
+      <c r="Y18" s="11"/>
+      <c r="Z18" s="11"/>
+    </row>
+    <row r="19" ht="36.0" customHeight="1">
+      <c r="A19" s="21">
+        <v>18.0</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" ht="42.0" customHeight="1">
-      <c r="A9" s="10">
-        <v>8.0</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" ht="42.0" customHeight="1">
-      <c r="A10" s="10">
-        <v>9.0</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" ht="42.0" customHeight="1">
-      <c r="A11" s="10">
-        <v>10.0</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" s="6" t="s">
+      <c r="D19" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="F19" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="11"/>
+      <c r="T19" s="11"/>
+      <c r="U19" s="11"/>
+      <c r="V19" s="11"/>
+      <c r="W19" s="11"/>
+      <c r="X19" s="11"/>
+      <c r="Y19" s="11"/>
+      <c r="Z19" s="11"/>
+    </row>
+    <row r="20" ht="36.0" customHeight="1">
+      <c r="A20" s="21">
+        <v>19.0</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" ht="42.0" customHeight="1">
-      <c r="A12" s="10">
-        <v>11.0</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" ht="42.0" customHeight="1">
-      <c r="A13" s="10">
-        <v>12.0</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" ht="42.0" customHeight="1">
-      <c r="A14" s="10">
-        <v>13.0</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="6" t="s">
+      <c r="D20" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="F20" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" ht="42.0" customHeight="1">
-      <c r="A15" s="10">
-        <v>14.0</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" ht="42.0" customHeight="1">
-      <c r="A16" s="10">
-        <v>15.0</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" ht="42.0" customHeight="1">
-      <c r="A17" s="10">
-        <v>16.0</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" ht="42.0" customHeight="1">
-      <c r="A18" s="10">
-        <v>17.0</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" ht="42.0" customHeight="1">
-      <c r="A19" s="10">
-        <v>18.0</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" ht="42.0" customHeight="1">
-      <c r="A20" s="10">
-        <v>19.0</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" ht="42.0" customHeight="1">
-      <c r="A21" s="10">
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="11"/>
+      <c r="P20" s="11"/>
+      <c r="Q20" s="11"/>
+      <c r="R20" s="11"/>
+      <c r="S20" s="11"/>
+      <c r="T20" s="11"/>
+      <c r="U20" s="11"/>
+      <c r="V20" s="11"/>
+      <c r="W20" s="11"/>
+      <c r="X20" s="11"/>
+      <c r="Y20" s="11"/>
+      <c r="Z20" s="11"/>
+    </row>
+    <row r="21" ht="36.0" customHeight="1">
+      <c r="A21" s="21">
         <v>20.0</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" ht="42.0" customHeight="1">
-      <c r="A22" s="10">
+      <c r="B21" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="F21" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11"/>
+      <c r="R21" s="11"/>
+      <c r="S21" s="11"/>
+      <c r="T21" s="11"/>
+      <c r="U21" s="11"/>
+      <c r="V21" s="11"/>
+      <c r="W21" s="11"/>
+      <c r="X21" s="11"/>
+      <c r="Y21" s="11"/>
+      <c r="Z21" s="11"/>
+    </row>
+    <row r="22" ht="36.0" customHeight="1">
+      <c r="A22" s="21">
         <v>21.0</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" ht="42.0" customHeight="1">
-      <c r="A23" s="10">
+      <c r="B22" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="F22" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11"/>
+      <c r="R22" s="11"/>
+      <c r="S22" s="11"/>
+      <c r="T22" s="11"/>
+      <c r="U22" s="11"/>
+      <c r="V22" s="11"/>
+      <c r="W22" s="11"/>
+      <c r="X22" s="11"/>
+      <c r="Y22" s="11"/>
+      <c r="Z22" s="11"/>
+    </row>
+    <row r="23" ht="36.0" customHeight="1">
+      <c r="A23" s="48">
         <v>22.0</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" ht="42.0" customHeight="1">
-      <c r="A24" s="10">
+      <c r="B23" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="F23" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="11"/>
+      <c r="S23" s="11"/>
+      <c r="T23" s="11"/>
+      <c r="U23" s="11"/>
+      <c r="V23" s="11"/>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+      <c r="Z23" s="11"/>
+    </row>
+    <row r="24" ht="36.0" customHeight="1">
+      <c r="A24" s="48">
         <v>23.0</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" ht="42.0" customHeight="1">
-      <c r="A25" s="22">
+      <c r="B24" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="F24" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="11"/>
+      <c r="S24" s="11"/>
+      <c r="T24" s="11"/>
+      <c r="U24" s="11"/>
+      <c r="V24" s="11"/>
+      <c r="W24" s="11"/>
+      <c r="X24" s="11"/>
+      <c r="Y24" s="11"/>
+      <c r="Z24" s="11"/>
+    </row>
+    <row r="25" ht="36.0" customHeight="1">
+      <c r="A25" s="49">
         <v>24.0</v>
       </c>
-      <c r="B25" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="F25" s="27" t="s">
-        <v>71</v>
-      </c>
+      <c r="B25" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="C25" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="E25" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="F25" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="11"/>
+      <c r="R25" s="11"/>
+      <c r="S25" s="11"/>
+      <c r="T25" s="11"/>
+      <c r="U25" s="11"/>
+      <c r="V25" s="11"/>
+      <c r="W25" s="11"/>
+      <c r="X25" s="11"/>
+      <c r="Y25" s="11"/>
+      <c r="Z25" s="11"/>
     </row>
     <row r="26" ht="42.0" customHeight="1">
-      <c r="A26" s="28"/>
+      <c r="A26" s="51"/>
     </row>
     <row r="27" ht="42.0" customHeight="1">
-      <c r="A27" s="28"/>
+      <c r="A27" s="51"/>
     </row>
     <row r="28" ht="42.0" customHeight="1">
-      <c r="A28" s="28"/>
+      <c r="A28" s="51"/>
     </row>
     <row r="29" ht="42.0" customHeight="1">
-      <c r="A29" s="28"/>
+      <c r="A29" s="51"/>
     </row>
     <row r="30" ht="42.0" customHeight="1">
-      <c r="A30" s="28"/>
+      <c r="A30" s="51"/>
     </row>
     <row r="31" ht="42.0" customHeight="1">
-      <c r="A31" s="28"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="31"/>
+      <c r="A31" s="51"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="53"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="54"/>
     </row>
     <row r="32" ht="34.5" customHeight="1">
-      <c r="B32" s="32"/>
-      <c r="C32" s="32"/>
+      <c r="B32" s="55"/>
+      <c r="C32" s="55"/>
     </row>
     <row r="33" ht="34.5" customHeight="1">
-      <c r="B33" s="32"/>
-      <c r="C33" s="32"/>
+      <c r="B33" s="55"/>
+      <c r="C33" s="55"/>
     </row>
     <row r="34" ht="34.5" customHeight="1">
-      <c r="B34" s="32"/>
-      <c r="C34" s="32"/>
+      <c r="B34" s="55"/>
+      <c r="C34" s="55"/>
     </row>
     <row r="35" ht="34.5" customHeight="1">
-      <c r="B35" s="32"/>
-      <c r="C35" s="32"/>
+      <c r="B35" s="55"/>
+      <c r="C35" s="55"/>
     </row>
     <row r="36" ht="34.5" customHeight="1">
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
     </row>
     <row r="37" ht="34.5" customHeight="1">
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
+      <c r="B37" s="55"/>
+      <c r="C37" s="55"/>
     </row>
     <row r="38" ht="34.5" customHeight="1">
-      <c r="B38" s="32"/>
-      <c r="C38" s="32"/>
+      <c r="B38" s="55"/>
+      <c r="C38" s="55"/>
     </row>
     <row r="39" ht="34.5" customHeight="1">
-      <c r="B39" s="32"/>
-      <c r="C39" s="32"/>
+      <c r="B39" s="55"/>
+      <c r="C39" s="55"/>
     </row>
     <row r="40" ht="34.5" customHeight="1">
-      <c r="B40" s="32"/>
-      <c r="C40" s="32"/>
+      <c r="B40" s="55"/>
+      <c r="C40" s="55"/>
     </row>
     <row r="41" ht="34.5" customHeight="1">
-      <c r="B41" s="32"/>
-      <c r="C41" s="32"/>
+      <c r="B41" s="55"/>
+      <c r="C41" s="55"/>
     </row>
     <row r="42" ht="34.5" customHeight="1">
-      <c r="B42" s="32"/>
-      <c r="C42" s="32"/>
+      <c r="B42" s="55"/>
+      <c r="C42" s="55"/>
     </row>
     <row r="43" ht="34.5" customHeight="1">
-      <c r="B43" s="32"/>
-      <c r="C43" s="32"/>
+      <c r="B43" s="55"/>
+      <c r="C43" s="55"/>
     </row>
     <row r="44" ht="34.5" customHeight="1">
-      <c r="B44" s="32"/>
-      <c r="C44" s="32"/>
+      <c r="B44" s="55"/>
+      <c r="C44" s="55"/>
     </row>
     <row r="45" ht="34.5" customHeight="1">
-      <c r="B45" s="32"/>
-      <c r="C45" s="32"/>
+      <c r="B45" s="55"/>
+      <c r="C45" s="55"/>
     </row>
     <row r="46" ht="34.5" customHeight="1">
-      <c r="B46" s="32"/>
-      <c r="C46" s="32"/>
+      <c r="B46" s="55"/>
+      <c r="C46" s="55"/>
     </row>
     <row r="47" ht="34.5" customHeight="1">
-      <c r="B47" s="32"/>
-      <c r="C47" s="32"/>
+      <c r="B47" s="55"/>
+      <c r="C47" s="55"/>
     </row>
     <row r="48" ht="34.5" customHeight="1">
-      <c r="B48" s="32"/>
-      <c r="C48" s="32"/>
+      <c r="B48" s="55"/>
+      <c r="C48" s="55"/>
     </row>
     <row r="49" ht="34.5" customHeight="1">
-      <c r="B49" s="32"/>
-      <c r="C49" s="32"/>
+      <c r="B49" s="55"/>
+      <c r="C49" s="55"/>
     </row>
     <row r="50" ht="34.5" customHeight="1">
-      <c r="B50" s="32"/>
-      <c r="C50" s="32"/>
+      <c r="B50" s="55"/>
+      <c r="C50" s="55"/>
     </row>
     <row r="51" ht="34.5" customHeight="1">
-      <c r="B51" s="32"/>
-      <c r="C51" s="32"/>
+      <c r="B51" s="55"/>
+      <c r="C51" s="55"/>
     </row>
     <row r="52" ht="34.5" customHeight="1">
-      <c r="B52" s="32"/>
-      <c r="C52" s="32"/>
+      <c r="B52" s="55"/>
+      <c r="C52" s="55"/>
     </row>
     <row r="53" ht="34.5" customHeight="1">
-      <c r="B53" s="32"/>
-      <c r="C53" s="32"/>
+      <c r="B53" s="55"/>
+      <c r="C53" s="55"/>
     </row>
     <row r="54" ht="34.5" customHeight="1">
-      <c r="B54" s="32"/>
-      <c r="C54" s="32"/>
+      <c r="B54" s="55"/>
+      <c r="C54" s="55"/>
     </row>
     <row r="55" ht="34.5" customHeight="1">
-      <c r="B55" s="32"/>
-      <c r="C55" s="32"/>
+      <c r="B55" s="55"/>
+      <c r="C55" s="55"/>
     </row>
     <row r="56" ht="34.5" customHeight="1">
-      <c r="B56" s="32"/>
-      <c r="C56" s="32"/>
+      <c r="B56" s="55"/>
+      <c r="C56" s="55"/>
     </row>
     <row r="57" ht="34.5" customHeight="1">
-      <c r="B57" s="32"/>
-      <c r="C57" s="32"/>
+      <c r="B57" s="55"/>
+      <c r="C57" s="55"/>
     </row>
     <row r="58" ht="34.5" customHeight="1">
-      <c r="B58" s="32"/>
-      <c r="C58" s="32"/>
+      <c r="B58" s="55"/>
+      <c r="C58" s="55"/>
     </row>
     <row r="59" ht="34.5" customHeight="1">
-      <c r="B59" s="32"/>
-      <c r="C59" s="32"/>
+      <c r="B59" s="55"/>
+      <c r="C59" s="55"/>
     </row>
     <row r="60" ht="34.5" customHeight="1">
-      <c r="B60" s="32"/>
-      <c r="C60" s="32"/>
+      <c r="B60" s="55"/>
+      <c r="C60" s="55"/>
     </row>
     <row r="61" ht="34.5" customHeight="1">
-      <c r="B61" s="32"/>
-      <c r="C61" s="32"/>
+      <c r="B61" s="55"/>
+      <c r="C61" s="55"/>
     </row>
     <row r="62" ht="34.5" customHeight="1">
-      <c r="B62" s="32"/>
-      <c r="C62" s="32"/>
+      <c r="B62" s="55"/>
+      <c r="C62" s="55"/>
     </row>
     <row r="63" ht="34.5" customHeight="1">
-      <c r="B63" s="32"/>
-      <c r="C63" s="32"/>
+      <c r="B63" s="55"/>
+      <c r="C63" s="55"/>
     </row>
     <row r="64" ht="34.5" customHeight="1">
-      <c r="B64" s="32"/>
-      <c r="C64" s="32"/>
+      <c r="B64" s="55"/>
+      <c r="C64" s="55"/>
     </row>
     <row r="65" ht="34.5" customHeight="1">
-      <c r="B65" s="32"/>
-      <c r="C65" s="32"/>
+      <c r="B65" s="55"/>
+      <c r="C65" s="55"/>
     </row>
     <row r="66" ht="34.5" customHeight="1">
-      <c r="B66" s="32"/>
-      <c r="C66" s="32"/>
+      <c r="B66" s="55"/>
+      <c r="C66" s="55"/>
     </row>
     <row r="67" ht="34.5" customHeight="1">
-      <c r="B67" s="32"/>
-      <c r="C67" s="32"/>
+      <c r="B67" s="55"/>
+      <c r="C67" s="55"/>
     </row>
     <row r="68" ht="34.5" customHeight="1">
-      <c r="B68" s="32"/>
-      <c r="C68" s="32"/>
+      <c r="B68" s="55"/>
+      <c r="C68" s="55"/>
     </row>
     <row r="69" ht="34.5" customHeight="1">
-      <c r="B69" s="32"/>
-      <c r="C69" s="32"/>
+      <c r="B69" s="55"/>
+      <c r="C69" s="55"/>
     </row>
     <row r="70" ht="34.5" customHeight="1">
-      <c r="B70" s="32"/>
-      <c r="C70" s="32"/>
+      <c r="B70" s="55"/>
+      <c r="C70" s="55"/>
     </row>
     <row r="71" ht="34.5" customHeight="1">
-      <c r="B71" s="32"/>
-      <c r="C71" s="32"/>
+      <c r="B71" s="55"/>
+      <c r="C71" s="55"/>
     </row>
     <row r="72" ht="34.5" customHeight="1">
-      <c r="B72" s="32"/>
-      <c r="C72" s="32"/>
+      <c r="B72" s="55"/>
+      <c r="C72" s="55"/>
     </row>
     <row r="73" ht="34.5" customHeight="1">
-      <c r="B73" s="32"/>
-      <c r="C73" s="32"/>
+      <c r="B73" s="55"/>
+      <c r="C73" s="55"/>
     </row>
     <row r="74" ht="34.5" customHeight="1">
-      <c r="B74" s="32"/>
-      <c r="C74" s="32"/>
+      <c r="B74" s="55"/>
+      <c r="C74" s="55"/>
     </row>
     <row r="75" ht="34.5" customHeight="1">
-      <c r="B75" s="32"/>
-      <c r="C75" s="32"/>
+      <c r="B75" s="55"/>
+      <c r="C75" s="55"/>
     </row>
     <row r="76" ht="34.5" customHeight="1">
-      <c r="B76" s="32"/>
-      <c r="C76" s="32"/>
+      <c r="B76" s="55"/>
+      <c r="C76" s="55"/>
     </row>
     <row r="77" ht="34.5" customHeight="1">
-      <c r="B77" s="32"/>
-      <c r="C77" s="32"/>
+      <c r="B77" s="55"/>
+      <c r="C77" s="55"/>
     </row>
     <row r="78" ht="34.5" customHeight="1">
-      <c r="B78" s="32"/>
-      <c r="C78" s="32"/>
+      <c r="B78" s="55"/>
+      <c r="C78" s="55"/>
     </row>
     <row r="79" ht="34.5" customHeight="1">
-      <c r="B79" s="32"/>
-      <c r="C79" s="32"/>
+      <c r="B79" s="55"/>
+      <c r="C79" s="55"/>
     </row>
     <row r="80" ht="34.5" customHeight="1">
-      <c r="B80" s="32"/>
-      <c r="C80" s="32"/>
+      <c r="B80" s="55"/>
+      <c r="C80" s="55"/>
     </row>
     <row r="81" ht="34.5" customHeight="1">
-      <c r="B81" s="32"/>
-      <c r="C81" s="32"/>
+      <c r="B81" s="55"/>
+      <c r="C81" s="55"/>
     </row>
     <row r="82" ht="34.5" customHeight="1">
-      <c r="B82" s="32"/>
-      <c r="C82" s="32"/>
+      <c r="B82" s="55"/>
+      <c r="C82" s="55"/>
     </row>
     <row r="83" ht="34.5" customHeight="1">
-      <c r="B83" s="32"/>
-      <c r="C83" s="32"/>
+      <c r="B83" s="55"/>
+      <c r="C83" s="55"/>
     </row>
     <row r="84" ht="34.5" customHeight="1">
-      <c r="B84" s="32"/>
-      <c r="C84" s="32"/>
+      <c r="B84" s="55"/>
+      <c r="C84" s="55"/>
     </row>
     <row r="85" ht="34.5" customHeight="1">
-      <c r="B85" s="32"/>
-      <c r="C85" s="32"/>
+      <c r="B85" s="55"/>
+      <c r="C85" s="55"/>
     </row>
     <row r="86" ht="34.5" customHeight="1">
-      <c r="B86" s="32"/>
-      <c r="C86" s="32"/>
+      <c r="B86" s="55"/>
+      <c r="C86" s="55"/>
     </row>
     <row r="87" ht="34.5" customHeight="1">
-      <c r="B87" s="32"/>
-      <c r="C87" s="32"/>
+      <c r="B87" s="55"/>
+      <c r="C87" s="55"/>
     </row>
     <row r="88" ht="34.5" customHeight="1">
-      <c r="B88" s="32"/>
-      <c r="C88" s="32"/>
+      <c r="B88" s="55"/>
+      <c r="C88" s="55"/>
     </row>
     <row r="89" ht="34.5" customHeight="1">
-      <c r="B89" s="32"/>
-      <c r="C89" s="32"/>
+      <c r="B89" s="55"/>
+      <c r="C89" s="55"/>
     </row>
     <row r="90" ht="34.5" customHeight="1">
-      <c r="B90" s="32"/>
-      <c r="C90" s="32"/>
+      <c r="B90" s="55"/>
+      <c r="C90" s="55"/>
     </row>
     <row r="91" ht="34.5" customHeight="1">
-      <c r="B91" s="32"/>
-      <c r="C91" s="32"/>
+      <c r="B91" s="55"/>
+      <c r="C91" s="55"/>
     </row>
     <row r="92" ht="34.5" customHeight="1">
-      <c r="B92" s="32"/>
-      <c r="C92" s="32"/>
+      <c r="B92" s="55"/>
+      <c r="C92" s="55"/>
     </row>
     <row r="93" ht="34.5" customHeight="1">
-      <c r="B93" s="32"/>
-      <c r="C93" s="32"/>
+      <c r="B93" s="55"/>
+      <c r="C93" s="55"/>
     </row>
     <row r="94" ht="34.5" customHeight="1">
-      <c r="B94" s="32"/>
-      <c r="C94" s="32"/>
+      <c r="B94" s="55"/>
+      <c r="C94" s="55"/>
     </row>
     <row r="95" ht="34.5" customHeight="1">
-      <c r="B95" s="32"/>
-      <c r="C95" s="32"/>
+      <c r="B95" s="55"/>
+      <c r="C95" s="55"/>
     </row>
     <row r="96" ht="34.5" customHeight="1">
-      <c r="B96" s="32"/>
-      <c r="C96" s="32"/>
+      <c r="B96" s="55"/>
+      <c r="C96" s="55"/>
     </row>
     <row r="97" ht="34.5" customHeight="1">
-      <c r="B97" s="32"/>
-      <c r="C97" s="32"/>
+      <c r="B97" s="55"/>
+      <c r="C97" s="55"/>
     </row>
     <row r="98" ht="34.5" customHeight="1">
-      <c r="B98" s="32"/>
-      <c r="C98" s="32"/>
+      <c r="B98" s="55"/>
+      <c r="C98" s="55"/>
     </row>
     <row r="99" ht="34.5" customHeight="1">
-      <c r="B99" s="32"/>
-      <c r="C99" s="32"/>
+      <c r="B99" s="55"/>
+      <c r="C99" s="55"/>
     </row>
     <row r="100" ht="34.5" customHeight="1">
-      <c r="B100" s="32"/>
-      <c r="C100" s="32"/>
+      <c r="B100" s="55"/>
+      <c r="C100" s="55"/>
     </row>
     <row r="101" ht="34.5" customHeight="1">
-      <c r="B101" s="32"/>
-      <c r="C101" s="32"/>
+      <c r="B101" s="55"/>
+      <c r="C101" s="55"/>
     </row>
     <row r="102" ht="34.5" customHeight="1">
-      <c r="B102" s="32"/>
-      <c r="C102" s="32"/>
+      <c r="B102" s="55"/>
+      <c r="C102" s="55"/>
     </row>
     <row r="103" ht="34.5" customHeight="1">
-      <c r="B103" s="32"/>
-      <c r="C103" s="32"/>
+      <c r="B103" s="55"/>
+      <c r="C103" s="55"/>
     </row>
     <row r="104" ht="34.5" customHeight="1">
-      <c r="B104" s="32"/>
-      <c r="C104" s="32"/>
+      <c r="B104" s="55"/>
+      <c r="C104" s="55"/>
     </row>
     <row r="105" ht="34.5" customHeight="1">
-      <c r="B105" s="32"/>
-      <c r="C105" s="32"/>
+      <c r="B105" s="55"/>
+      <c r="C105" s="55"/>
     </row>
     <row r="106" ht="34.5" customHeight="1">
-      <c r="B106" s="32"/>
-      <c r="C106" s="32"/>
+      <c r="B106" s="55"/>
+      <c r="C106" s="55"/>
     </row>
     <row r="107" ht="34.5" customHeight="1">
-      <c r="B107" s="32"/>
-      <c r="C107" s="32"/>
+      <c r="B107" s="55"/>
+      <c r="C107" s="55"/>
     </row>
     <row r="108" ht="34.5" customHeight="1">
-      <c r="B108" s="32"/>
-      <c r="C108" s="32"/>
+      <c r="B108" s="55"/>
+      <c r="C108" s="55"/>
     </row>
     <row r="109" ht="34.5" customHeight="1">
-      <c r="B109" s="32"/>
-      <c r="C109" s="32"/>
+      <c r="B109" s="55"/>
+      <c r="C109" s="55"/>
     </row>
     <row r="110" ht="34.5" customHeight="1">
-      <c r="B110" s="32"/>
-      <c r="C110" s="32"/>
+      <c r="B110" s="55"/>
+      <c r="C110" s="55"/>
     </row>
     <row r="111" ht="34.5" customHeight="1">
-      <c r="B111" s="32"/>
-      <c r="C111" s="32"/>
+      <c r="B111" s="55"/>
+      <c r="C111" s="55"/>
     </row>
     <row r="112" ht="34.5" customHeight="1">
-      <c r="B112" s="32"/>
-      <c r="C112" s="32"/>
+      <c r="B112" s="55"/>
+      <c r="C112" s="55"/>
     </row>
     <row r="113" ht="34.5" customHeight="1">
-      <c r="B113" s="32"/>
-      <c r="C113" s="32"/>
+      <c r="B113" s="55"/>
+      <c r="C113" s="55"/>
     </row>
     <row r="114" ht="34.5" customHeight="1">
-      <c r="B114" s="32"/>
-      <c r="C114" s="32"/>
+      <c r="B114" s="55"/>
+      <c r="C114" s="55"/>
     </row>
     <row r="115" ht="34.5" customHeight="1">
-      <c r="B115" s="32"/>
-      <c r="C115" s="32"/>
+      <c r="B115" s="55"/>
+      <c r="C115" s="55"/>
     </row>
     <row r="116" ht="34.5" customHeight="1">
-      <c r="B116" s="32"/>
-      <c r="C116" s="32"/>
+      <c r="B116" s="55"/>
+      <c r="C116" s="55"/>
     </row>
     <row r="117" ht="34.5" customHeight="1">
-      <c r="B117" s="32"/>
-      <c r="C117" s="32"/>
+      <c r="B117" s="55"/>
+      <c r="C117" s="55"/>
     </row>
     <row r="118" ht="34.5" customHeight="1">
-      <c r="B118" s="32"/>
-      <c r="C118" s="32"/>
+      <c r="B118" s="55"/>
+      <c r="C118" s="55"/>
     </row>
     <row r="119" ht="34.5" customHeight="1">
-      <c r="B119" s="32"/>
-      <c r="C119" s="32"/>
+      <c r="B119" s="55"/>
+      <c r="C119" s="55"/>
     </row>
     <row r="120" ht="34.5" customHeight="1">
-      <c r="B120" s="32"/>
-      <c r="C120" s="32"/>
+      <c r="B120" s="55"/>
+      <c r="C120" s="55"/>
     </row>
     <row r="121" ht="34.5" customHeight="1">
-      <c r="B121" s="32"/>
-      <c r="C121" s="32"/>
+      <c r="B121" s="55"/>
+      <c r="C121" s="55"/>
     </row>
     <row r="122" ht="34.5" customHeight="1">
-      <c r="B122" s="32"/>
-      <c r="C122" s="32"/>
+      <c r="B122" s="55"/>
+      <c r="C122" s="55"/>
     </row>
     <row r="123" ht="34.5" customHeight="1">
-      <c r="B123" s="32"/>
-      <c r="C123" s="32"/>
+      <c r="B123" s="55"/>
+      <c r="C123" s="55"/>
     </row>
     <row r="124" ht="34.5" customHeight="1">
-      <c r="B124" s="32"/>
-      <c r="C124" s="32"/>
+      <c r="B124" s="55"/>
+      <c r="C124" s="55"/>
     </row>
     <row r="125" ht="34.5" customHeight="1">
-      <c r="B125" s="32"/>
-      <c r="C125" s="32"/>
+      <c r="B125" s="55"/>
+      <c r="C125" s="55"/>
     </row>
     <row r="126" ht="34.5" customHeight="1">
-      <c r="B126" s="32"/>
-      <c r="C126" s="32"/>
+      <c r="B126" s="55"/>
+      <c r="C126" s="55"/>
     </row>
     <row r="127" ht="34.5" customHeight="1">
-      <c r="B127" s="32"/>
-      <c r="C127" s="32"/>
+      <c r="B127" s="55"/>
+      <c r="C127" s="55"/>
     </row>
     <row r="128" ht="34.5" customHeight="1">
-      <c r="B128" s="32"/>
-      <c r="C128" s="32"/>
+      <c r="B128" s="55"/>
+      <c r="C128" s="55"/>
     </row>
     <row r="129" ht="34.5" customHeight="1">
-      <c r="B129" s="32"/>
-      <c r="C129" s="32"/>
+      <c r="B129" s="55"/>
+      <c r="C129" s="55"/>
     </row>
     <row r="130" ht="34.5" customHeight="1">
-      <c r="B130" s="32"/>
-      <c r="C130" s="32"/>
+      <c r="B130" s="55"/>
+      <c r="C130" s="55"/>
     </row>
     <row r="131" ht="34.5" customHeight="1">
-      <c r="B131" s="32"/>
-      <c r="C131" s="32"/>
+      <c r="B131" s="55"/>
+      <c r="C131" s="55"/>
     </row>
     <row r="132" ht="34.5" customHeight="1">
-      <c r="B132" s="32"/>
-      <c r="C132" s="32"/>
+      <c r="B132" s="55"/>
+      <c r="C132" s="55"/>
     </row>
     <row r="133" ht="34.5" customHeight="1">
-      <c r="B133" s="32"/>
-      <c r="C133" s="32"/>
+      <c r="B133" s="55"/>
+      <c r="C133" s="55"/>
     </row>
     <row r="134" ht="34.5" customHeight="1">
-      <c r="B134" s="32"/>
-      <c r="C134" s="32"/>
+      <c r="B134" s="55"/>
+      <c r="C134" s="55"/>
     </row>
     <row r="135" ht="34.5" customHeight="1">
-      <c r="B135" s="32"/>
-      <c r="C135" s="32"/>
+      <c r="B135" s="55"/>
+      <c r="C135" s="55"/>
     </row>
     <row r="136" ht="34.5" customHeight="1">
-      <c r="B136" s="32"/>
-      <c r="C136" s="32"/>
+      <c r="B136" s="55"/>
+      <c r="C136" s="55"/>
     </row>
     <row r="137" ht="34.5" customHeight="1">
-      <c r="B137" s="32"/>
-      <c r="C137" s="32"/>
+      <c r="B137" s="55"/>
+      <c r="C137" s="55"/>
     </row>
     <row r="138" ht="34.5" customHeight="1">
-      <c r="B138" s="32"/>
-      <c r="C138" s="32"/>
+      <c r="B138" s="55"/>
+      <c r="C138" s="55"/>
     </row>
     <row r="139" ht="34.5" customHeight="1">
-      <c r="B139" s="32"/>
-      <c r="C139" s="32"/>
+      <c r="B139" s="55"/>
+      <c r="C139" s="55"/>
     </row>
     <row r="140" ht="34.5" customHeight="1">
-      <c r="B140" s="32"/>
-      <c r="C140" s="32"/>
+      <c r="B140" s="55"/>
+      <c r="C140" s="55"/>
     </row>
     <row r="141" ht="34.5" customHeight="1">
-      <c r="B141" s="32"/>
-      <c r="C141" s="32"/>
+      <c r="B141" s="55"/>
+      <c r="C141" s="55"/>
     </row>
     <row r="142" ht="34.5" customHeight="1">
-      <c r="B142" s="32"/>
-      <c r="C142" s="32"/>
+      <c r="B142" s="55"/>
+      <c r="C142" s="55"/>
     </row>
     <row r="143" ht="34.5" customHeight="1">
-      <c r="B143" s="32"/>
-      <c r="C143" s="32"/>
+      <c r="B143" s="55"/>
+      <c r="C143" s="55"/>
     </row>
     <row r="144" ht="34.5" customHeight="1">
-      <c r="B144" s="32"/>
-      <c r="C144" s="32"/>
+      <c r="B144" s="55"/>
+      <c r="C144" s="55"/>
     </row>
     <row r="145" ht="34.5" customHeight="1">
-      <c r="B145" s="32"/>
-      <c r="C145" s="32"/>
+      <c r="B145" s="55"/>
+      <c r="C145" s="55"/>
     </row>
     <row r="146" ht="34.5" customHeight="1">
-      <c r="B146" s="32"/>
-      <c r="C146" s="32"/>
+      <c r="B146" s="55"/>
+      <c r="C146" s="55"/>
     </row>
     <row r="147" ht="34.5" customHeight="1">
-      <c r="B147" s="32"/>
-      <c r="C147" s="32"/>
+      <c r="B147" s="55"/>
+      <c r="C147" s="55"/>
     </row>
     <row r="148" ht="34.5" customHeight="1">
-      <c r="B148" s="32"/>
-      <c r="C148" s="32"/>
+      <c r="B148" s="55"/>
+      <c r="C148" s="55"/>
     </row>
     <row r="149" ht="34.5" customHeight="1">
-      <c r="B149" s="32"/>
-      <c r="C149" s="32"/>
+      <c r="B149" s="55"/>
+      <c r="C149" s="55"/>
     </row>
     <row r="150" ht="34.5" customHeight="1">
-      <c r="B150" s="32"/>
-      <c r="C150" s="32"/>
+      <c r="B150" s="55"/>
+      <c r="C150" s="55"/>
     </row>
     <row r="151" ht="34.5" customHeight="1">
-      <c r="B151" s="32"/>
-      <c r="C151" s="32"/>
+      <c r="B151" s="55"/>
+      <c r="C151" s="55"/>
     </row>
     <row r="152" ht="34.5" customHeight="1">
-      <c r="B152" s="32"/>
-      <c r="C152" s="32"/>
+      <c r="B152" s="55"/>
+      <c r="C152" s="55"/>
     </row>
     <row r="153" ht="34.5" customHeight="1">
-      <c r="B153" s="32"/>
-      <c r="C153" s="32"/>
+      <c r="B153" s="55"/>
+      <c r="C153" s="55"/>
     </row>
     <row r="154" ht="34.5" customHeight="1">
-      <c r="B154" s="32"/>
-      <c r="C154" s="32"/>
+      <c r="B154" s="55"/>
+      <c r="C154" s="55"/>
     </row>
     <row r="155" ht="34.5" customHeight="1">
-      <c r="B155" s="32"/>
-      <c r="C155" s="32"/>
+      <c r="B155" s="55"/>
+      <c r="C155" s="55"/>
     </row>
     <row r="156" ht="34.5" customHeight="1">
-      <c r="B156" s="32"/>
-      <c r="C156" s="32"/>
+      <c r="B156" s="55"/>
+      <c r="C156" s="55"/>
     </row>
     <row r="157" ht="34.5" customHeight="1">
-      <c r="B157" s="32"/>
-      <c r="C157" s="32"/>
+      <c r="B157" s="55"/>
+      <c r="C157" s="55"/>
     </row>
     <row r="158" ht="34.5" customHeight="1">
-      <c r="B158" s="32"/>
-      <c r="C158" s="32"/>
+      <c r="B158" s="55"/>
+      <c r="C158" s="55"/>
     </row>
     <row r="159" ht="34.5" customHeight="1">
-      <c r="B159" s="32"/>
-      <c r="C159" s="32"/>
+      <c r="B159" s="55"/>
+      <c r="C159" s="55"/>
     </row>
     <row r="160" ht="34.5" customHeight="1">
-      <c r="B160" s="32"/>
-      <c r="C160" s="32"/>
+      <c r="B160" s="55"/>
+      <c r="C160" s="55"/>
     </row>
     <row r="161" ht="34.5" customHeight="1">
-      <c r="B161" s="32"/>
-      <c r="C161" s="32"/>
+      <c r="B161" s="55"/>
+      <c r="C161" s="55"/>
     </row>
     <row r="162" ht="34.5" customHeight="1">
-      <c r="B162" s="32"/>
-      <c r="C162" s="32"/>
+      <c r="B162" s="55"/>
+      <c r="C162" s="55"/>
     </row>
     <row r="163" ht="34.5" customHeight="1">
-      <c r="B163" s="32"/>
-      <c r="C163" s="32"/>
+      <c r="B163" s="55"/>
+      <c r="C163" s="55"/>
     </row>
     <row r="164" ht="34.5" customHeight="1">
-      <c r="B164" s="32"/>
-      <c r="C164" s="32"/>
+      <c r="B164" s="55"/>
+      <c r="C164" s="55"/>
     </row>
     <row r="165" ht="34.5" customHeight="1">
-      <c r="B165" s="32"/>
-      <c r="C165" s="32"/>
+      <c r="B165" s="55"/>
+      <c r="C165" s="55"/>
     </row>
     <row r="166" ht="34.5" customHeight="1">
-      <c r="B166" s="32"/>
-      <c r="C166" s="32"/>
+      <c r="B166" s="55"/>
+      <c r="C166" s="55"/>
     </row>
     <row r="167" ht="34.5" customHeight="1">
-      <c r="B167" s="32"/>
-      <c r="C167" s="32"/>
+      <c r="B167" s="55"/>
+      <c r="C167" s="55"/>
     </row>
     <row r="168" ht="34.5" customHeight="1">
-      <c r="B168" s="32"/>
-      <c r="C168" s="32"/>
+      <c r="B168" s="55"/>
+      <c r="C168" s="55"/>
     </row>
     <row r="169" ht="34.5" customHeight="1">
-      <c r="B169" s="32"/>
-      <c r="C169" s="32"/>
+      <c r="B169" s="55"/>
+      <c r="C169" s="55"/>
     </row>
     <row r="170" ht="34.5" customHeight="1">
-      <c r="B170" s="32"/>
-      <c r="C170" s="32"/>
+      <c r="B170" s="55"/>
+      <c r="C170" s="55"/>
     </row>
     <row r="171" ht="34.5" customHeight="1">
-      <c r="B171" s="32"/>
-      <c r="C171" s="32"/>
+      <c r="B171" s="55"/>
+      <c r="C171" s="55"/>
     </row>
     <row r="172" ht="34.5" customHeight="1">
-      <c r="B172" s="32"/>
-      <c r="C172" s="32"/>
+      <c r="B172" s="55"/>
+      <c r="C172" s="55"/>
     </row>
     <row r="173" ht="34.5" customHeight="1">
-      <c r="B173" s="32"/>
-      <c r="C173" s="32"/>
+      <c r="B173" s="55"/>
+      <c r="C173" s="55"/>
     </row>
     <row r="174" ht="34.5" customHeight="1">
-      <c r="B174" s="32"/>
-      <c r="C174" s="32"/>
+      <c r="B174" s="55"/>
+      <c r="C174" s="55"/>
     </row>
     <row r="175" ht="34.5" customHeight="1">
-      <c r="B175" s="32"/>
-      <c r="C175" s="32"/>
+      <c r="B175" s="55"/>
+      <c r="C175" s="55"/>
     </row>
     <row r="176" ht="34.5" customHeight="1">
-      <c r="B176" s="32"/>
-      <c r="C176" s="32"/>
+      <c r="B176" s="55"/>
+      <c r="C176" s="55"/>
     </row>
     <row r="177" ht="34.5" customHeight="1">
-      <c r="B177" s="32"/>
-      <c r="C177" s="32"/>
+      <c r="B177" s="55"/>
+      <c r="C177" s="55"/>
     </row>
     <row r="178" ht="34.5" customHeight="1">
-      <c r="B178" s="32"/>
-      <c r="C178" s="32"/>
+      <c r="B178" s="55"/>
+      <c r="C178" s="55"/>
     </row>
     <row r="179" ht="34.5" customHeight="1">
-      <c r="B179" s="32"/>
-      <c r="C179" s="32"/>
+      <c r="B179" s="55"/>
+      <c r="C179" s="55"/>
     </row>
     <row r="180" ht="34.5" customHeight="1">
-      <c r="B180" s="32"/>
-      <c r="C180" s="32"/>
+      <c r="B180" s="55"/>
+      <c r="C180" s="55"/>
     </row>
     <row r="181" ht="34.5" customHeight="1">
-      <c r="B181" s="32"/>
-      <c r="C181" s="32"/>
+      <c r="B181" s="55"/>
+      <c r="C181" s="55"/>
     </row>
     <row r="182" ht="34.5" customHeight="1">
-      <c r="B182" s="32"/>
-      <c r="C182" s="32"/>
+      <c r="B182" s="55"/>
+      <c r="C182" s="55"/>
     </row>
     <row r="183" ht="34.5" customHeight="1">
-      <c r="B183" s="32"/>
-      <c r="C183" s="32"/>
+      <c r="B183" s="55"/>
+      <c r="C183" s="55"/>
     </row>
     <row r="184" ht="34.5" customHeight="1">
-      <c r="B184" s="32"/>
-      <c r="C184" s="32"/>
+      <c r="B184" s="55"/>
+      <c r="C184" s="55"/>
     </row>
     <row r="185" ht="34.5" customHeight="1">
-      <c r="B185" s="32"/>
-      <c r="C185" s="32"/>
+      <c r="B185" s="55"/>
+      <c r="C185" s="55"/>
     </row>
     <row r="186" ht="34.5" customHeight="1">
-      <c r="B186" s="32"/>
-      <c r="C186" s="32"/>
+      <c r="B186" s="55"/>
+      <c r="C186" s="55"/>
     </row>
     <row r="187" ht="34.5" customHeight="1">
-      <c r="B187" s="32"/>
-      <c r="C187" s="32"/>
+      <c r="B187" s="55"/>
+      <c r="C187" s="55"/>
     </row>
     <row r="188" ht="34.5" customHeight="1">
-      <c r="B188" s="32"/>
-      <c r="C188" s="32"/>
+      <c r="B188" s="55"/>
+      <c r="C188" s="55"/>
     </row>
     <row r="189" ht="34.5" customHeight="1">
-      <c r="B189" s="32"/>
-      <c r="C189" s="32"/>
+      <c r="B189" s="55"/>
+      <c r="C189" s="55"/>
     </row>
     <row r="190" ht="34.5" customHeight="1">
-      <c r="B190" s="32"/>
-      <c r="C190" s="32"/>
+      <c r="B190" s="55"/>
+      <c r="C190" s="55"/>
     </row>
     <row r="191" ht="34.5" customHeight="1">
-      <c r="B191" s="32"/>
-      <c r="C191" s="32"/>
+      <c r="B191" s="55"/>
+      <c r="C191" s="55"/>
     </row>
     <row r="192" ht="34.5" customHeight="1">
-      <c r="B192" s="32"/>
-      <c r="C192" s="32"/>
+      <c r="B192" s="55"/>
+      <c r="C192" s="55"/>
     </row>
     <row r="193" ht="34.5" customHeight="1">
-      <c r="B193" s="32"/>
-      <c r="C193" s="32"/>
+      <c r="B193" s="55"/>
+      <c r="C193" s="55"/>
     </row>
     <row r="194" ht="34.5" customHeight="1">
-      <c r="B194" s="32"/>
-      <c r="C194" s="32"/>
+      <c r="B194" s="55"/>
+      <c r="C194" s="55"/>
     </row>
     <row r="195" ht="34.5" customHeight="1">
-      <c r="B195" s="32"/>
-      <c r="C195" s="32"/>
+      <c r="B195" s="55"/>
+      <c r="C195" s="55"/>
     </row>
     <row r="196" ht="34.5" customHeight="1">
-      <c r="B196" s="32"/>
-      <c r="C196" s="32"/>
+      <c r="B196" s="55"/>
+      <c r="C196" s="55"/>
     </row>
     <row r="197" ht="34.5" customHeight="1">
-      <c r="B197" s="32"/>
-      <c r="C197" s="32"/>
+      <c r="B197" s="55"/>
+      <c r="C197" s="55"/>
     </row>
     <row r="198" ht="34.5" customHeight="1">
-      <c r="B198" s="32"/>
-      <c r="C198" s="32"/>
+      <c r="B198" s="55"/>
+      <c r="C198" s="55"/>
     </row>
     <row r="199" ht="34.5" customHeight="1">
-      <c r="B199" s="32"/>
-      <c r="C199" s="32"/>
+      <c r="B199" s="55"/>
+      <c r="C199" s="55"/>
     </row>
     <row r="200" ht="34.5" customHeight="1">
-      <c r="B200" s="32"/>
-      <c r="C200" s="32"/>
+      <c r="B200" s="55"/>
+      <c r="C200" s="55"/>
     </row>
     <row r="201" ht="34.5" customHeight="1">
-      <c r="B201" s="32"/>
-      <c r="C201" s="32"/>
+      <c r="B201" s="55"/>
+      <c r="C201" s="55"/>
     </row>
     <row r="202" ht="34.5" customHeight="1">
-      <c r="B202" s="32"/>
-      <c r="C202" s="32"/>
+      <c r="B202" s="55"/>
+      <c r="C202" s="55"/>
     </row>
     <row r="203" ht="34.5" customHeight="1">
-      <c r="B203" s="32"/>
-      <c r="C203" s="32"/>
+      <c r="B203" s="55"/>
+      <c r="C203" s="55"/>
     </row>
     <row r="204" ht="34.5" customHeight="1">
-      <c r="B204" s="32"/>
-      <c r="C204" s="32"/>
+      <c r="B204" s="55"/>
+      <c r="C204" s="55"/>
     </row>
     <row r="205" ht="34.5" customHeight="1">
-      <c r="B205" s="32"/>
-      <c r="C205" s="32"/>
+      <c r="B205" s="55"/>
+      <c r="C205" s="55"/>
     </row>
     <row r="206" ht="34.5" customHeight="1">
-      <c r="B206" s="32"/>
-      <c r="C206" s="32"/>
+      <c r="B206" s="55"/>
+      <c r="C206" s="55"/>
     </row>
     <row r="207" ht="34.5" customHeight="1">
-      <c r="B207" s="32"/>
-      <c r="C207" s="32"/>
+      <c r="B207" s="55"/>
+      <c r="C207" s="55"/>
     </row>
     <row r="208" ht="34.5" customHeight="1">
-      <c r="B208" s="32"/>
-      <c r="C208" s="32"/>
+      <c r="B208" s="55"/>
+      <c r="C208" s="55"/>
     </row>
     <row r="209" ht="34.5" customHeight="1">
-      <c r="B209" s="32"/>
-      <c r="C209" s="32"/>
+      <c r="B209" s="55"/>
+      <c r="C209" s="55"/>
     </row>
     <row r="210" ht="34.5" customHeight="1">
-      <c r="B210" s="32"/>
-      <c r="C210" s="32"/>
+      <c r="B210" s="55"/>
+      <c r="C210" s="55"/>
     </row>
     <row r="211" ht="34.5" customHeight="1">
-      <c r="B211" s="32"/>
-      <c r="C211" s="32"/>
+      <c r="B211" s="55"/>
+      <c r="C211" s="55"/>
     </row>
     <row r="212" ht="34.5" customHeight="1">
-      <c r="B212" s="32"/>
-      <c r="C212" s="32"/>
+      <c r="B212" s="55"/>
+      <c r="C212" s="55"/>
     </row>
     <row r="213" ht="34.5" customHeight="1">
-      <c r="B213" s="32"/>
-      <c r="C213" s="32"/>
+      <c r="B213" s="55"/>
+      <c r="C213" s="55"/>
     </row>
     <row r="214" ht="34.5" customHeight="1">
-      <c r="B214" s="32"/>
-      <c r="C214" s="32"/>
+      <c r="B214" s="55"/>
+      <c r="C214" s="55"/>
     </row>
     <row r="215" ht="34.5" customHeight="1">
-      <c r="B215" s="32"/>
-      <c r="C215" s="32"/>
+      <c r="B215" s="55"/>
+      <c r="C215" s="55"/>
     </row>
     <row r="216" ht="34.5" customHeight="1">
-      <c r="B216" s="32"/>
-      <c r="C216" s="32"/>
+      <c r="B216" s="55"/>
+      <c r="C216" s="55"/>
     </row>
     <row r="217" ht="34.5" customHeight="1">
-      <c r="B217" s="32"/>
-      <c r="C217" s="32"/>
+      <c r="B217" s="55"/>
+      <c r="C217" s="55"/>
     </row>
     <row r="218" ht="34.5" customHeight="1">
-      <c r="B218" s="32"/>
-      <c r="C218" s="32"/>
+      <c r="B218" s="55"/>
+      <c r="C218" s="55"/>
     </row>
     <row r="219" ht="34.5" customHeight="1">
-      <c r="B219" s="32"/>
-      <c r="C219" s="32"/>
+      <c r="B219" s="55"/>
+      <c r="C219" s="55"/>
     </row>
     <row r="220" ht="34.5" customHeight="1">
-      <c r="B220" s="32"/>
-      <c r="C220" s="32"/>
+      <c r="B220" s="55"/>
+      <c r="C220" s="55"/>
     </row>
     <row r="221" ht="34.5" customHeight="1">
-      <c r="B221" s="32"/>
-      <c r="C221" s="32"/>
+      <c r="B221" s="55"/>
+      <c r="C221" s="55"/>
     </row>
     <row r="222" ht="34.5" customHeight="1">
-      <c r="B222" s="32"/>
-      <c r="C222" s="32"/>
+      <c r="B222" s="55"/>
+      <c r="C222" s="55"/>
     </row>
     <row r="223" ht="34.5" customHeight="1">
-      <c r="B223" s="32"/>
-      <c r="C223" s="32"/>
+      <c r="B223" s="55"/>
+      <c r="C223" s="55"/>
     </row>
     <row r="224" ht="34.5" customHeight="1">
-      <c r="B224" s="32"/>
-      <c r="C224" s="32"/>
+      <c r="B224" s="55"/>
+      <c r="C224" s="55"/>
     </row>
     <row r="225" ht="34.5" customHeight="1">
-      <c r="B225" s="32"/>
-      <c r="C225" s="32"/>
+      <c r="B225" s="55"/>
+      <c r="C225" s="55"/>
     </row>
     <row r="226" ht="34.5" customHeight="1">
-      <c r="B226" s="32"/>
-      <c r="C226" s="32"/>
+      <c r="B226" s="55"/>
+      <c r="C226" s="55"/>
     </row>
     <row r="227" ht="34.5" customHeight="1">
-      <c r="B227" s="32"/>
-      <c r="C227" s="32"/>
+      <c r="B227" s="55"/>
+      <c r="C227" s="55"/>
     </row>
     <row r="228" ht="34.5" customHeight="1">
-      <c r="B228" s="32"/>
-      <c r="C228" s="32"/>
+      <c r="B228" s="55"/>
+      <c r="C228" s="55"/>
     </row>
     <row r="229" ht="34.5" customHeight="1">
-      <c r="B229" s="32"/>
-      <c r="C229" s="32"/>
+      <c r="B229" s="55"/>
+      <c r="C229" s="55"/>
     </row>
     <row r="230" ht="34.5" customHeight="1">
-      <c r="B230" s="32"/>
-      <c r="C230" s="32"/>
+      <c r="B230" s="55"/>
+      <c r="C230" s="55"/>
     </row>
     <row r="231" ht="34.5" customHeight="1">
-      <c r="B231" s="32"/>
-      <c r="C231" s="32"/>
+      <c r="B231" s="55"/>
+      <c r="C231" s="55"/>
     </row>
     <row r="232" ht="34.5" customHeight="1">
-      <c r="B232" s="32"/>
-      <c r="C232" s="32"/>
+      <c r="B232" s="55"/>
+      <c r="C232" s="55"/>
     </row>
     <row r="233" ht="34.5" customHeight="1">
-      <c r="B233" s="32"/>
-      <c r="C233" s="32"/>
+      <c r="B233" s="55"/>
+      <c r="C233" s="55"/>
     </row>
     <row r="234" ht="34.5" customHeight="1">
-      <c r="B234" s="32"/>
-      <c r="C234" s="32"/>
+      <c r="B234" s="55"/>
+      <c r="C234" s="55"/>
     </row>
     <row r="235" ht="34.5" customHeight="1">
-      <c r="B235" s="32"/>
-      <c r="C235" s="32"/>
+      <c r="B235" s="55"/>
+      <c r="C235" s="55"/>
     </row>
     <row r="236" ht="34.5" customHeight="1">
-      <c r="B236" s="32"/>
-      <c r="C236" s="32"/>
+      <c r="B236" s="55"/>
+      <c r="C236" s="55"/>
     </row>
     <row r="237" ht="34.5" customHeight="1">
-      <c r="B237" s="32"/>
-      <c r="C237" s="32"/>
+      <c r="B237" s="55"/>
+      <c r="C237" s="55"/>
     </row>
     <row r="238" ht="34.5" customHeight="1">
-      <c r="B238" s="32"/>
-      <c r="C238" s="32"/>
+      <c r="B238" s="55"/>
+      <c r="C238" s="55"/>
     </row>
     <row r="239" ht="34.5" customHeight="1">
-      <c r="B239" s="32"/>
-      <c r="C239" s="32"/>
+      <c r="B239" s="55"/>
+      <c r="C239" s="55"/>
     </row>
     <row r="240" ht="34.5" customHeight="1">
-      <c r="B240" s="32"/>
-      <c r="C240" s="32"/>
+      <c r="B240" s="55"/>
+      <c r="C240" s="55"/>
     </row>
     <row r="241" ht="34.5" customHeight="1">
-      <c r="B241" s="32"/>
-      <c r="C241" s="32"/>
+      <c r="B241" s="55"/>
+      <c r="C241" s="55"/>
     </row>
     <row r="242" ht="34.5" customHeight="1">
-      <c r="B242" s="32"/>
-      <c r="C242" s="32"/>
+      <c r="B242" s="55"/>
+      <c r="C242" s="55"/>
     </row>
     <row r="243" ht="34.5" customHeight="1">
-      <c r="B243" s="32"/>
-      <c r="C243" s="32"/>
+      <c r="B243" s="55"/>
+      <c r="C243" s="55"/>
     </row>
     <row r="244" ht="34.5" customHeight="1">
-      <c r="B244" s="32"/>
-      <c r="C244" s="32"/>
+      <c r="B244" s="55"/>
+      <c r="C244" s="55"/>
     </row>
     <row r="245" ht="34.5" customHeight="1">
-      <c r="B245" s="32"/>
-      <c r="C245" s="32"/>
+      <c r="B245" s="55"/>
+      <c r="C245" s="55"/>
     </row>
     <row r="246" ht="34.5" customHeight="1">
-      <c r="B246" s="32"/>
-      <c r="C246" s="32"/>
+      <c r="B246" s="55"/>
+      <c r="C246" s="55"/>
     </row>
     <row r="247" ht="34.5" customHeight="1">
-      <c r="B247" s="32"/>
-      <c r="C247" s="32"/>
+      <c r="B247" s="55"/>
+      <c r="C247" s="55"/>
     </row>
     <row r="248" ht="34.5" customHeight="1">
-      <c r="B248" s="32"/>
-      <c r="C248" s="32"/>
+      <c r="B248" s="55"/>
+      <c r="C248" s="55"/>
     </row>
     <row r="249" ht="34.5" customHeight="1">
-      <c r="B249" s="32"/>
-      <c r="C249" s="32"/>
+      <c r="B249" s="55"/>
+      <c r="C249" s="55"/>
     </row>
     <row r="250" ht="34.5" customHeight="1">
-      <c r="B250" s="32"/>
-      <c r="C250" s="32"/>
+      <c r="B250" s="55"/>
+      <c r="C250" s="55"/>
     </row>
     <row r="251" ht="34.5" customHeight="1">
-      <c r="B251" s="32"/>
-      <c r="C251" s="32"/>
+      <c r="B251" s="55"/>
+      <c r="C251" s="55"/>
     </row>
     <row r="252" ht="34.5" customHeight="1">
-      <c r="B252" s="32"/>
-      <c r="C252" s="32"/>
+      <c r="B252" s="55"/>
+      <c r="C252" s="55"/>
     </row>
     <row r="253" ht="34.5" customHeight="1">
-      <c r="B253" s="32"/>
-      <c r="C253" s="32"/>
+      <c r="B253" s="55"/>
+      <c r="C253" s="55"/>
     </row>
     <row r="254" ht="34.5" customHeight="1">
-      <c r="B254" s="32"/>
-      <c r="C254" s="32"/>
+      <c r="B254" s="55"/>
+      <c r="C254" s="55"/>
     </row>
     <row r="255" ht="34.5" customHeight="1">
-      <c r="B255" s="32"/>
-      <c r="C255" s="32"/>
+      <c r="B255" s="55"/>
+      <c r="C255" s="55"/>
     </row>
     <row r="256" ht="34.5" customHeight="1">
-      <c r="B256" s="32"/>
-      <c r="C256" s="32"/>
+      <c r="B256" s="55"/>
+      <c r="C256" s="55"/>
     </row>
     <row r="257" ht="34.5" customHeight="1">
-      <c r="B257" s="32"/>
-      <c r="C257" s="32"/>
+      <c r="B257" s="55"/>
+      <c r="C257" s="55"/>
     </row>
     <row r="258" ht="34.5" customHeight="1">
-      <c r="B258" s="32"/>
-      <c r="C258" s="32"/>
+      <c r="B258" s="55"/>
+      <c r="C258" s="55"/>
     </row>
     <row r="259" ht="34.5" customHeight="1">
-      <c r="B259" s="32"/>
-      <c r="C259" s="32"/>
+      <c r="B259" s="55"/>
+      <c r="C259" s="55"/>
     </row>
     <row r="260" ht="34.5" customHeight="1">
-      <c r="B260" s="32"/>
-      <c r="C260" s="32"/>
+      <c r="B260" s="55"/>
+      <c r="C260" s="55"/>
     </row>
     <row r="261" ht="34.5" customHeight="1">
-      <c r="B261" s="32"/>
-      <c r="C261" s="32"/>
+      <c r="B261" s="55"/>
+      <c r="C261" s="55"/>
     </row>
     <row r="262" ht="34.5" customHeight="1">
-      <c r="B262" s="32"/>
-      <c r="C262" s="32"/>
+      <c r="B262" s="55"/>
+      <c r="C262" s="55"/>
     </row>
     <row r="263" ht="34.5" customHeight="1">
-      <c r="B263" s="32"/>
-      <c r="C263" s="32"/>
+      <c r="B263" s="55"/>
+      <c r="C263" s="55"/>
     </row>
     <row r="264" ht="34.5" customHeight="1">
-      <c r="B264" s="32"/>
-      <c r="C264" s="32"/>
+      <c r="B264" s="55"/>
+      <c r="C264" s="55"/>
     </row>
     <row r="265" ht="34.5" customHeight="1">
-      <c r="B265" s="32"/>
-      <c r="C265" s="32"/>
+      <c r="B265" s="55"/>
+      <c r="C265" s="55"/>
     </row>
     <row r="266" ht="34.5" customHeight="1">
-      <c r="B266" s="32"/>
-      <c r="C266" s="32"/>
+      <c r="B266" s="55"/>
+      <c r="C266" s="55"/>
     </row>
     <row r="267" ht="34.5" customHeight="1">
-      <c r="B267" s="32"/>
-      <c r="C267" s="32"/>
+      <c r="B267" s="55"/>
+      <c r="C267" s="55"/>
     </row>
     <row r="268" ht="34.5" customHeight="1">
-      <c r="B268" s="32"/>
-      <c r="C268" s="32"/>
+      <c r="B268" s="55"/>
+      <c r="C268" s="55"/>
     </row>
     <row r="269" ht="34.5" customHeight="1">
-      <c r="B269" s="32"/>
-      <c r="C269" s="32"/>
+      <c r="B269" s="55"/>
+      <c r="C269" s="55"/>
     </row>
     <row r="270" ht="34.5" customHeight="1">
-      <c r="B270" s="32"/>
-      <c r="C270" s="32"/>
+      <c r="B270" s="55"/>
+      <c r="C270" s="55"/>
     </row>
     <row r="271" ht="34.5" customHeight="1">
-      <c r="B271" s="32"/>
-      <c r="C271" s="32"/>
+      <c r="B271" s="55"/>
+      <c r="C271" s="55"/>
     </row>
     <row r="272" ht="34.5" customHeight="1">
-      <c r="B272" s="32"/>
-      <c r="C272" s="32"/>
+      <c r="B272" s="55"/>
+      <c r="C272" s="55"/>
     </row>
     <row r="273" ht="34.5" customHeight="1">
-      <c r="B273" s="32"/>
-      <c r="C273" s="32"/>
+      <c r="B273" s="55"/>
+      <c r="C273" s="55"/>
     </row>
     <row r="274" ht="34.5" customHeight="1">
-      <c r="B274" s="32"/>
-      <c r="C274" s="32"/>
+      <c r="B274" s="55"/>
+      <c r="C274" s="55"/>
     </row>
     <row r="275" ht="34.5" customHeight="1">
-      <c r="B275" s="32"/>
-      <c r="C275" s="32"/>
+      <c r="B275" s="55"/>
+      <c r="C275" s="55"/>
     </row>
     <row r="276" ht="34.5" customHeight="1">
-      <c r="B276" s="32"/>
-      <c r="C276" s="32"/>
+      <c r="B276" s="55"/>
+      <c r="C276" s="55"/>
     </row>
     <row r="277" ht="34.5" customHeight="1">
-      <c r="B277" s="32"/>
-      <c r="C277" s="32"/>
+      <c r="B277" s="55"/>
+      <c r="C277" s="55"/>
     </row>
     <row r="278" ht="34.5" customHeight="1">
-      <c r="B278" s="32"/>
-      <c r="C278" s="32"/>
+      <c r="B278" s="55"/>
+      <c r="C278" s="55"/>
     </row>
     <row r="279" ht="34.5" customHeight="1">
-      <c r="B279" s="32"/>
-      <c r="C279" s="32"/>
+      <c r="B279" s="55"/>
+      <c r="C279" s="55"/>
     </row>
     <row r="280" ht="34.5" customHeight="1">
-      <c r="B280" s="32"/>
-      <c r="C280" s="32"/>
+      <c r="B280" s="55"/>
+      <c r="C280" s="55"/>
     </row>
     <row r="281" ht="34.5" customHeight="1">
-      <c r="B281" s="32"/>
-      <c r="C281" s="32"/>
+      <c r="B281" s="55"/>
+      <c r="C281" s="55"/>
     </row>
     <row r="282" ht="34.5" customHeight="1">
-      <c r="B282" s="32"/>
-      <c r="C282" s="32"/>
+      <c r="B282" s="55"/>
+      <c r="C282" s="55"/>
     </row>
     <row r="283" ht="34.5" customHeight="1">
-      <c r="B283" s="32"/>
-      <c r="C283" s="32"/>
+      <c r="B283" s="55"/>
+      <c r="C283" s="55"/>
     </row>
     <row r="284" ht="34.5" customHeight="1">
-      <c r="B284" s="32"/>
-      <c r="C284" s="32"/>
+      <c r="B284" s="55"/>
+      <c r="C284" s="55"/>
     </row>
     <row r="285" ht="34.5" customHeight="1">
-      <c r="B285" s="32"/>
-      <c r="C285" s="32"/>
+      <c r="B285" s="55"/>
+      <c r="C285" s="55"/>
     </row>
     <row r="286" ht="34.5" customHeight="1">
-      <c r="B286" s="32"/>
-      <c r="C286" s="32"/>
+      <c r="B286" s="55"/>
+      <c r="C286" s="55"/>
     </row>
     <row r="287" ht="34.5" customHeight="1">
-      <c r="B287" s="32"/>
-      <c r="C287" s="32"/>
+      <c r="B287" s="55"/>
+      <c r="C287" s="55"/>
     </row>
     <row r="288" ht="34.5" customHeight="1">
-      <c r="B288" s="32"/>
-      <c r="C288" s="32"/>
+      <c r="B288" s="55"/>
+      <c r="C288" s="55"/>
     </row>
     <row r="289" ht="34.5" customHeight="1">
-      <c r="B289" s="32"/>
-      <c r="C289" s="32"/>
+      <c r="B289" s="55"/>
+      <c r="C289" s="55"/>
     </row>
     <row r="290" ht="34.5" customHeight="1">
-      <c r="B290" s="32"/>
-      <c r="C290" s="32"/>
+      <c r="B290" s="55"/>
+      <c r="C290" s="55"/>
     </row>
     <row r="291" ht="34.5" customHeight="1">
-      <c r="B291" s="32"/>
-      <c r="C291" s="32"/>
+      <c r="B291" s="55"/>
+      <c r="C291" s="55"/>
     </row>
     <row r="292" ht="34.5" customHeight="1">
-      <c r="B292" s="32"/>
-      <c r="C292" s="32"/>
+      <c r="B292" s="55"/>
+      <c r="C292" s="55"/>
     </row>
     <row r="293" ht="34.5" customHeight="1">
-      <c r="B293" s="32"/>
-      <c r="C293" s="32"/>
+      <c r="B293" s="55"/>
+      <c r="C293" s="55"/>
     </row>
     <row r="294" ht="34.5" customHeight="1">
-      <c r="B294" s="32"/>
-      <c r="C294" s="32"/>
+      <c r="B294" s="55"/>
+      <c r="C294" s="55"/>
     </row>
     <row r="295" ht="34.5" customHeight="1">
-      <c r="B295" s="32"/>
-      <c r="C295" s="32"/>
+      <c r="B295" s="55"/>
+      <c r="C295" s="55"/>
     </row>
     <row r="296" ht="34.5" customHeight="1">
-      <c r="B296" s="32"/>
-      <c r="C296" s="32"/>
+      <c r="B296" s="55"/>
+      <c r="C296" s="55"/>
     </row>
     <row r="297" ht="34.5" customHeight="1">
-      <c r="B297" s="32"/>
-      <c r="C297" s="32"/>
+      <c r="B297" s="55"/>
+      <c r="C297" s="55"/>
     </row>
     <row r="298" ht="34.5" customHeight="1">
-      <c r="B298" s="32"/>
-      <c r="C298" s="32"/>
+      <c r="B298" s="55"/>
+      <c r="C298" s="55"/>
     </row>
     <row r="299" ht="34.5" customHeight="1">
-      <c r="B299" s="32"/>
-      <c r="C299" s="32"/>
+      <c r="B299" s="55"/>
+      <c r="C299" s="55"/>
     </row>
     <row r="300" ht="34.5" customHeight="1">
-      <c r="B300" s="32"/>
-      <c r="C300" s="32"/>
+      <c r="B300" s="55"/>
+      <c r="C300" s="55"/>
     </row>
     <row r="301" ht="34.5" customHeight="1">
-      <c r="B301" s="32"/>
-      <c r="C301" s="32"/>
+      <c r="B301" s="55"/>
+      <c r="C301" s="55"/>
     </row>
     <row r="302" ht="34.5" customHeight="1">
-      <c r="B302" s="32"/>
-      <c r="C302" s="32"/>
+      <c r="B302" s="55"/>
+      <c r="C302" s="55"/>
     </row>
     <row r="303" ht="34.5" customHeight="1">
-      <c r="B303" s="32"/>
-      <c r="C303" s="32"/>
+      <c r="B303" s="55"/>
+      <c r="C303" s="55"/>
     </row>
     <row r="304" ht="34.5" customHeight="1">
-      <c r="B304" s="32"/>
-      <c r="C304" s="32"/>
+      <c r="B304" s="55"/>
+      <c r="C304" s="55"/>
     </row>
     <row r="305" ht="34.5" customHeight="1">
-      <c r="B305" s="32"/>
-      <c r="C305" s="32"/>
+      <c r="B305" s="55"/>
+      <c r="C305" s="55"/>
     </row>
     <row r="306" ht="34.5" customHeight="1">
-      <c r="B306" s="32"/>
-      <c r="C306" s="32"/>
+      <c r="B306" s="55"/>
+      <c r="C306" s="55"/>
     </row>
     <row r="307" ht="34.5" customHeight="1">
-      <c r="B307" s="32"/>
-      <c r="C307" s="32"/>
+      <c r="B307" s="55"/>
+      <c r="C307" s="55"/>
     </row>
     <row r="308" ht="34.5" customHeight="1">
-      <c r="B308" s="32"/>
-      <c r="C308" s="32"/>
+      <c r="B308" s="55"/>
+      <c r="C308" s="55"/>
     </row>
     <row r="309" ht="34.5" customHeight="1">
-      <c r="B309" s="32"/>
-      <c r="C309" s="32"/>
+      <c r="B309" s="55"/>
+      <c r="C309" s="55"/>
     </row>
     <row r="310" ht="34.5" customHeight="1">
-      <c r="B310" s="32"/>
-      <c r="C310" s="32"/>
+      <c r="B310" s="55"/>
+      <c r="C310" s="55"/>
     </row>
     <row r="311" ht="34.5" customHeight="1">
-      <c r="B311" s="32"/>
-      <c r="C311" s="32"/>
+      <c r="B311" s="55"/>
+      <c r="C311" s="55"/>
     </row>
     <row r="312" ht="34.5" customHeight="1">
-      <c r="B312" s="32"/>
-      <c r="C312" s="32"/>
+      <c r="B312" s="55"/>
+      <c r="C312" s="55"/>
     </row>
     <row r="313" ht="34.5" customHeight="1">
-      <c r="B313" s="32"/>
-      <c r="C313" s="32"/>
+      <c r="B313" s="55"/>
+      <c r="C313" s="55"/>
     </row>
     <row r="314" ht="34.5" customHeight="1">
-      <c r="B314" s="32"/>
-      <c r="C314" s="32"/>
+      <c r="B314" s="55"/>
+      <c r="C314" s="55"/>
     </row>
     <row r="315" ht="34.5" customHeight="1">
-      <c r="B315" s="32"/>
-      <c r="C315" s="32"/>
+      <c r="B315" s="55"/>
+      <c r="C315" s="55"/>
     </row>
     <row r="316" ht="34.5" customHeight="1">
-      <c r="B316" s="32"/>
-      <c r="C316" s="32"/>
+      <c r="B316" s="55"/>
+      <c r="C316" s="55"/>
     </row>
     <row r="317" ht="34.5" customHeight="1">
-      <c r="B317" s="32"/>
-      <c r="C317" s="32"/>
+      <c r="B317" s="55"/>
+      <c r="C317" s="55"/>
     </row>
     <row r="318" ht="34.5" customHeight="1">
-      <c r="B318" s="32"/>
-      <c r="C318" s="32"/>
+      <c r="B318" s="55"/>
+      <c r="C318" s="55"/>
     </row>
     <row r="319" ht="34.5" customHeight="1">
-      <c r="B319" s="32"/>
-      <c r="C319" s="32"/>
+      <c r="B319" s="55"/>
+      <c r="C319" s="55"/>
     </row>
     <row r="320" ht="34.5" customHeight="1">
-      <c r="B320" s="32"/>
-      <c r="C320" s="32"/>
+      <c r="B320" s="55"/>
+      <c r="C320" s="55"/>
     </row>
     <row r="321" ht="34.5" customHeight="1">
-      <c r="B321" s="32"/>
-      <c r="C321" s="32"/>
+      <c r="B321" s="55"/>
+      <c r="C321" s="55"/>
     </row>
     <row r="322" ht="34.5" customHeight="1">
-      <c r="B322" s="32"/>
-      <c r="C322" s="32"/>
+      <c r="B322" s="55"/>
+      <c r="C322" s="55"/>
     </row>
     <row r="323" ht="34.5" customHeight="1">
-      <c r="B323" s="32"/>
-      <c r="C323" s="32"/>
+      <c r="B323" s="55"/>
+      <c r="C323" s="55"/>
     </row>
     <row r="324" ht="34.5" customHeight="1">
-      <c r="B324" s="32"/>
-      <c r="C324" s="32"/>
+      <c r="B324" s="55"/>
+      <c r="C324" s="55"/>
     </row>
     <row r="325" ht="34.5" customHeight="1">
-      <c r="B325" s="32"/>
-      <c r="C325" s="32"/>
+      <c r="B325" s="55"/>
+      <c r="C325" s="55"/>
     </row>
     <row r="326" ht="34.5" customHeight="1">
-      <c r="B326" s="32"/>
-      <c r="C326" s="32"/>
+      <c r="B326" s="55"/>
+      <c r="C326" s="55"/>
     </row>
     <row r="327" ht="34.5" customHeight="1">
-      <c r="B327" s="32"/>
-      <c r="C327" s="32"/>
+      <c r="B327" s="55"/>
+      <c r="C327" s="55"/>
     </row>
     <row r="328" ht="34.5" customHeight="1">
-      <c r="B328" s="32"/>
-      <c r="C328" s="32"/>
+      <c r="B328" s="55"/>
+      <c r="C328" s="55"/>
     </row>
     <row r="329" ht="34.5" customHeight="1">
-      <c r="B329" s="32"/>
-      <c r="C329" s="32"/>
+      <c r="B329" s="55"/>
+      <c r="C329" s="55"/>
     </row>
     <row r="330" ht="34.5" customHeight="1">
-      <c r="B330" s="32"/>
-      <c r="C330" s="32"/>
+      <c r="B330" s="55"/>
+      <c r="C330" s="55"/>
     </row>
     <row r="331" ht="34.5" customHeight="1">
-      <c r="B331" s="32"/>
-      <c r="C331" s="32"/>
+      <c r="B331" s="55"/>
+      <c r="C331" s="55"/>
     </row>
     <row r="332" ht="34.5" customHeight="1">
-      <c r="B332" s="32"/>
-      <c r="C332" s="32"/>
+      <c r="B332" s="55"/>
+      <c r="C332" s="55"/>
     </row>
     <row r="333" ht="34.5" customHeight="1">
-      <c r="B333" s="32"/>
-      <c r="C333" s="32"/>
+      <c r="B333" s="55"/>
+      <c r="C333" s="55"/>
     </row>
     <row r="334" ht="34.5" customHeight="1">
-      <c r="B334" s="32"/>
-      <c r="C334" s="32"/>
+      <c r="B334" s="55"/>
+      <c r="C334" s="55"/>
     </row>
     <row r="335" ht="34.5" customHeight="1">
-      <c r="B335" s="32"/>
-      <c r="C335" s="32"/>
+      <c r="B335" s="55"/>
+      <c r="C335" s="55"/>
     </row>
     <row r="336" ht="34.5" customHeight="1">
-      <c r="B336" s="32"/>
-      <c r="C336" s="32"/>
+      <c r="B336" s="55"/>
+      <c r="C336" s="55"/>
     </row>
     <row r="337" ht="34.5" customHeight="1">
-      <c r="B337" s="32"/>
-      <c r="C337" s="32"/>
+      <c r="B337" s="55"/>
+      <c r="C337" s="55"/>
     </row>
     <row r="338" ht="34.5" customHeight="1">
-      <c r="B338" s="32"/>
-      <c r="C338" s="32"/>
+      <c r="B338" s="55"/>
+      <c r="C338" s="55"/>
     </row>
     <row r="339" ht="34.5" customHeight="1">
-      <c r="B339" s="32"/>
-      <c r="C339" s="32"/>
+      <c r="B339" s="55"/>
+      <c r="C339" s="55"/>
     </row>
     <row r="340" ht="34.5" customHeight="1">
-      <c r="B340" s="32"/>
-      <c r="C340" s="32"/>
+      <c r="B340" s="55"/>
+      <c r="C340" s="55"/>
     </row>
     <row r="341" ht="34.5" customHeight="1">
-      <c r="B341" s="32"/>
-      <c r="C341" s="32"/>
+      <c r="B341" s="55"/>
+      <c r="C341" s="55"/>
     </row>
     <row r="342" ht="34.5" customHeight="1">
-      <c r="B342" s="32"/>
-      <c r="C342" s="32"/>
+      <c r="B342" s="55"/>
+      <c r="C342" s="55"/>
     </row>
     <row r="343" ht="34.5" customHeight="1">
-      <c r="B343" s="32"/>
-      <c r="C343" s="32"/>
+      <c r="B343" s="55"/>
+      <c r="C343" s="55"/>
     </row>
     <row r="344" ht="34.5" customHeight="1">
-      <c r="B344" s="32"/>
-      <c r="C344" s="32"/>
+      <c r="B344" s="55"/>
+      <c r="C344" s="55"/>
     </row>
     <row r="345" ht="34.5" customHeight="1">
-      <c r="B345" s="32"/>
-      <c r="C345" s="32"/>
+      <c r="B345" s="55"/>
+      <c r="C345" s="55"/>
     </row>
     <row r="346" ht="34.5" customHeight="1">
-      <c r="B346" s="32"/>
-      <c r="C346" s="32"/>
+      <c r="B346" s="55"/>
+      <c r="C346" s="55"/>
     </row>
     <row r="347" ht="34.5" customHeight="1">
-      <c r="B347" s="32"/>
-      <c r="C347" s="32"/>
+      <c r="B347" s="55"/>
+      <c r="C347" s="55"/>
     </row>
     <row r="348" ht="34.5" customHeight="1">
-      <c r="B348" s="32"/>
-      <c r="C348" s="32"/>
+      <c r="B348" s="55"/>
+      <c r="C348" s="55"/>
     </row>
     <row r="349" ht="34.5" customHeight="1">
-      <c r="B349" s="32"/>
-      <c r="C349" s="32"/>
+      <c r="B349" s="55"/>
+      <c r="C349" s="55"/>
     </row>
     <row r="350" ht="34.5" customHeight="1">
-      <c r="B350" s="32"/>
-      <c r="C350" s="32"/>
+      <c r="B350" s="55"/>
+      <c r="C350" s="55"/>
     </row>
     <row r="351" ht="34.5" customHeight="1">
-      <c r="B351" s="32"/>
-      <c r="C351" s="32"/>
+      <c r="B351" s="55"/>
+      <c r="C351" s="55"/>
     </row>
     <row r="352" ht="34.5" customHeight="1">
-      <c r="B352" s="32"/>
-      <c r="C352" s="32"/>
+      <c r="B352" s="55"/>
+      <c r="C352" s="55"/>
     </row>
     <row r="353" ht="34.5" customHeight="1">
-      <c r="B353" s="32"/>
-      <c r="C353" s="32"/>
+      <c r="B353" s="55"/>
+      <c r="C353" s="55"/>
     </row>
     <row r="354" ht="34.5" customHeight="1">
-      <c r="B354" s="32"/>
-      <c r="C354" s="32"/>
+      <c r="B354" s="55"/>
+      <c r="C354" s="55"/>
     </row>
     <row r="355" ht="34.5" customHeight="1">
-      <c r="B355" s="32"/>
-      <c r="C355" s="32"/>
+      <c r="B355" s="55"/>
+      <c r="C355" s="55"/>
     </row>
     <row r="356" ht="34.5" customHeight="1">
-      <c r="B356" s="32"/>
-      <c r="C356" s="32"/>
+      <c r="B356" s="55"/>
+      <c r="C356" s="55"/>
     </row>
     <row r="357" ht="34.5" customHeight="1">
-      <c r="B357" s="32"/>
-      <c r="C357" s="32"/>
+      <c r="B357" s="55"/>
+      <c r="C357" s="55"/>
     </row>
     <row r="358" ht="34.5" customHeight="1">
-      <c r="B358" s="32"/>
-      <c r="C358" s="32"/>
+      <c r="B358" s="55"/>
+      <c r="C358" s="55"/>
     </row>
     <row r="359" ht="34.5" customHeight="1">
-      <c r="B359" s="32"/>
-      <c r="C359" s="32"/>
+      <c r="B359" s="55"/>
+      <c r="C359" s="55"/>
     </row>
     <row r="360" ht="34.5" customHeight="1">
-      <c r="B360" s="32"/>
-      <c r="C360" s="32"/>
+      <c r="B360" s="55"/>
+      <c r="C360" s="55"/>
     </row>
     <row r="361" ht="34.5" customHeight="1">
-      <c r="B361" s="32"/>
-      <c r="C361" s="32"/>
+      <c r="B361" s="55"/>
+      <c r="C361" s="55"/>
     </row>
     <row r="362" ht="34.5" customHeight="1">
-      <c r="B362" s="32"/>
-      <c r="C362" s="32"/>
+      <c r="B362" s="55"/>
+      <c r="C362" s="55"/>
     </row>
     <row r="363" ht="34.5" customHeight="1">
-      <c r="B363" s="32"/>
-      <c r="C363" s="32"/>
+      <c r="B363" s="55"/>
+      <c r="C363" s="55"/>
     </row>
     <row r="364" ht="34.5" customHeight="1">
-      <c r="B364" s="32"/>
-      <c r="C364" s="32"/>
+      <c r="B364" s="55"/>
+      <c r="C364" s="55"/>
     </row>
     <row r="365" ht="34.5" customHeight="1">
-      <c r="B365" s="32"/>
-      <c r="C365" s="32"/>
+      <c r="B365" s="55"/>
+      <c r="C365" s="55"/>
     </row>
     <row r="366" ht="34.5" customHeight="1">
-      <c r="B366" s="32"/>
-      <c r="C366" s="32"/>
+      <c r="B366" s="55"/>
+      <c r="C366" s="55"/>
     </row>
     <row r="367" ht="34.5" customHeight="1">
-      <c r="B367" s="32"/>
-      <c r="C367" s="32"/>
+      <c r="B367" s="55"/>
+      <c r="C367" s="55"/>
     </row>
     <row r="368" ht="34.5" customHeight="1">
-      <c r="B368" s="32"/>
-      <c r="C368" s="32"/>
+      <c r="B368" s="55"/>
+      <c r="C368" s="55"/>
     </row>
     <row r="369" ht="34.5" customHeight="1">
-      <c r="B369" s="32"/>
-      <c r="C369" s="32"/>
+      <c r="B369" s="55"/>
+      <c r="C369" s="55"/>
     </row>
     <row r="370" ht="34.5" customHeight="1">
-      <c r="B370" s="32"/>
-      <c r="C370" s="32"/>
+      <c r="B370" s="55"/>
+      <c r="C370" s="55"/>
     </row>
     <row r="371" ht="34.5" customHeight="1">
-      <c r="B371" s="32"/>
-      <c r="C371" s="32"/>
+      <c r="B371" s="55"/>
+      <c r="C371" s="55"/>
     </row>
     <row r="372" ht="34.5" customHeight="1">
-      <c r="B372" s="32"/>
-      <c r="C372" s="32"/>
+      <c r="B372" s="55"/>
+      <c r="C372" s="55"/>
     </row>
     <row r="373" ht="34.5" customHeight="1">
-      <c r="B373" s="32"/>
-      <c r="C373" s="32"/>
+      <c r="B373" s="55"/>
+      <c r="C373" s="55"/>
     </row>
     <row r="374" ht="34.5" customHeight="1">
-      <c r="B374" s="32"/>
-      <c r="C374" s="32"/>
+      <c r="B374" s="55"/>
+      <c r="C374" s="55"/>
     </row>
     <row r="375" ht="34.5" customHeight="1">
-      <c r="B375" s="32"/>
-      <c r="C375" s="32"/>
+      <c r="B375" s="55"/>
+      <c r="C375" s="55"/>
     </row>
     <row r="376" ht="34.5" customHeight="1">
-      <c r="B376" s="32"/>
-      <c r="C376" s="32"/>
+      <c r="B376" s="55"/>
+      <c r="C376" s="55"/>
     </row>
     <row r="377" ht="34.5" customHeight="1">
-      <c r="B377" s="32"/>
-      <c r="C377" s="32"/>
+      <c r="B377" s="55"/>
+      <c r="C377" s="55"/>
     </row>
     <row r="378" ht="34.5" customHeight="1">
-      <c r="B378" s="32"/>
-      <c r="C378" s="32"/>
+      <c r="B378" s="55"/>
+      <c r="C378" s="55"/>
     </row>
     <row r="379" ht="34.5" customHeight="1">
-      <c r="B379" s="32"/>
-      <c r="C379" s="32"/>
+      <c r="B379" s="55"/>
+      <c r="C379" s="55"/>
     </row>
     <row r="380" ht="34.5" customHeight="1">
-      <c r="B380" s="32"/>
-      <c r="C380" s="32"/>
+      <c r="B380" s="55"/>
+      <c r="C380" s="55"/>
     </row>
     <row r="381" ht="34.5" customHeight="1">
-      <c r="B381" s="32"/>
-      <c r="C381" s="32"/>
+      <c r="B381" s="55"/>
+      <c r="C381" s="55"/>
     </row>
     <row r="382" ht="34.5" customHeight="1">
-      <c r="B382" s="32"/>
-      <c r="C382" s="32"/>
+      <c r="B382" s="55"/>
+      <c r="C382" s="55"/>
     </row>
     <row r="383" ht="34.5" customHeight="1">
-      <c r="B383" s="32"/>
-      <c r="C383" s="32"/>
+      <c r="B383" s="55"/>
+      <c r="C383" s="55"/>
     </row>
     <row r="384" ht="34.5" customHeight="1">
-      <c r="B384" s="32"/>
-      <c r="C384" s="32"/>
+      <c r="B384" s="55"/>
+      <c r="C384" s="55"/>
     </row>
     <row r="385" ht="34.5" customHeight="1">
-      <c r="B385" s="32"/>
-      <c r="C385" s="32"/>
+      <c r="B385" s="55"/>
+      <c r="C385" s="55"/>
     </row>
     <row r="386" ht="34.5" customHeight="1">
-      <c r="B386" s="32"/>
-      <c r="C386" s="32"/>
+      <c r="B386" s="55"/>
+      <c r="C386" s="55"/>
     </row>
     <row r="387" ht="34.5" customHeight="1">
-      <c r="B387" s="32"/>
-      <c r="C387" s="32"/>
+      <c r="B387" s="55"/>
+      <c r="C387" s="55"/>
     </row>
     <row r="388" ht="34.5" customHeight="1">
-      <c r="B388" s="32"/>
-      <c r="C388" s="32"/>
+      <c r="B388" s="55"/>
+      <c r="C388" s="55"/>
     </row>
     <row r="389" ht="34.5" customHeight="1">
-      <c r="B389" s="32"/>
-      <c r="C389" s="32"/>
+      <c r="B389" s="55"/>
+      <c r="C389" s="55"/>
     </row>
     <row r="390" ht="34.5" customHeight="1">
-      <c r="B390" s="32"/>
-      <c r="C390" s="32"/>
+      <c r="B390" s="55"/>
+      <c r="C390" s="55"/>
     </row>
     <row r="391" ht="34.5" customHeight="1">
-      <c r="B391" s="32"/>
-      <c r="C391" s="32"/>
+      <c r="B391" s="55"/>
+      <c r="C391" s="55"/>
     </row>
     <row r="392" ht="34.5" customHeight="1">
-      <c r="B392" s="32"/>
-      <c r="C392" s="32"/>
+      <c r="B392" s="55"/>
+      <c r="C392" s="55"/>
     </row>
     <row r="393" ht="34.5" customHeight="1">
-      <c r="B393" s="32"/>
-      <c r="C393" s="32"/>
+      <c r="B393" s="55"/>
+      <c r="C393" s="55"/>
     </row>
     <row r="394" ht="34.5" customHeight="1">
-      <c r="B394" s="32"/>
-      <c r="C394" s="32"/>
+      <c r="B394" s="55"/>
+      <c r="C394" s="55"/>
     </row>
     <row r="395" ht="34.5" customHeight="1">
-      <c r="B395" s="32"/>
-      <c r="C395" s="32"/>
+      <c r="B395" s="55"/>
+      <c r="C395" s="55"/>
     </row>
     <row r="396" ht="34.5" customHeight="1">
-      <c r="B396" s="32"/>
-      <c r="C396" s="32"/>
+      <c r="B396" s="55"/>
+      <c r="C396" s="55"/>
     </row>
     <row r="397" ht="34.5" customHeight="1">
-      <c r="B397" s="32"/>
-      <c r="C397" s="32"/>
+      <c r="B397" s="55"/>
+      <c r="C397" s="55"/>
     </row>
     <row r="398" ht="34.5" customHeight="1">
-      <c r="B398" s="32"/>
-      <c r="C398" s="32"/>
+      <c r="B398" s="55"/>
+      <c r="C398" s="55"/>
     </row>
     <row r="399" ht="34.5" customHeight="1">
-      <c r="B399" s="32"/>
-      <c r="C399" s="32"/>
+      <c r="B399" s="55"/>
+      <c r="C399" s="55"/>
     </row>
     <row r="400" ht="34.5" customHeight="1">
-      <c r="B400" s="32"/>
-      <c r="C400" s="32"/>
+      <c r="B400" s="55"/>
+      <c r="C400" s="55"/>
     </row>
     <row r="401" ht="34.5" customHeight="1">
-      <c r="B401" s="32"/>
-      <c r="C401" s="32"/>
+      <c r="B401" s="55"/>
+      <c r="C401" s="55"/>
     </row>
     <row r="402" ht="34.5" customHeight="1">
-      <c r="B402" s="32"/>
-      <c r="C402" s="32"/>
+      <c r="B402" s="55"/>
+      <c r="C402" s="55"/>
     </row>
     <row r="403" ht="34.5" customHeight="1">
-      <c r="B403" s="32"/>
-      <c r="C403" s="32"/>
+      <c r="B403" s="55"/>
+      <c r="C403" s="55"/>
     </row>
     <row r="404" ht="34.5" customHeight="1">
-      <c r="B404" s="32"/>
-      <c r="C404" s="32"/>
+      <c r="B404" s="55"/>
+      <c r="C404" s="55"/>
     </row>
     <row r="405" ht="34.5" customHeight="1">
-      <c r="B405" s="32"/>
-      <c r="C405" s="32"/>
+      <c r="B405" s="55"/>
+      <c r="C405" s="55"/>
     </row>
     <row r="406" ht="34.5" customHeight="1">
-      <c r="B406" s="32"/>
-      <c r="C406" s="32"/>
+      <c r="B406" s="55"/>
+      <c r="C406" s="55"/>
     </row>
     <row r="407" ht="34.5" customHeight="1">
-      <c r="B407" s="32"/>
-      <c r="C407" s="32"/>
+      <c r="B407" s="55"/>
+      <c r="C407" s="55"/>
     </row>
     <row r="408" ht="34.5" customHeight="1">
-      <c r="B408" s="32"/>
-      <c r="C408" s="32"/>
+      <c r="B408" s="55"/>
+      <c r="C408" s="55"/>
     </row>
     <row r="409" ht="34.5" customHeight="1">
-      <c r="B409" s="32"/>
-      <c r="C409" s="32"/>
+      <c r="B409" s="55"/>
+      <c r="C409" s="55"/>
     </row>
     <row r="410" ht="34.5" customHeight="1">
-      <c r="B410" s="32"/>
-      <c r="C410" s="32"/>
+      <c r="B410" s="55"/>
+      <c r="C410" s="55"/>
     </row>
     <row r="411" ht="34.5" customHeight="1">
-      <c r="B411" s="32"/>
-      <c r="C411" s="32"/>
+      <c r="B411" s="55"/>
+      <c r="C411" s="55"/>
     </row>
     <row r="412" ht="34.5" customHeight="1">
-      <c r="B412" s="32"/>
-      <c r="C412" s="32"/>
+      <c r="B412" s="55"/>
+      <c r="C412" s="55"/>
     </row>
     <row r="413" ht="34.5" customHeight="1">
-      <c r="B413" s="32"/>
-      <c r="C413" s="32"/>
+      <c r="B413" s="55"/>
+      <c r="C413" s="55"/>
     </row>
     <row r="414" ht="34.5" customHeight="1">
-      <c r="B414" s="32"/>
-      <c r="C414" s="32"/>
+      <c r="B414" s="55"/>
+      <c r="C414" s="55"/>
     </row>
     <row r="415" ht="34.5" customHeight="1">
-      <c r="B415" s="32"/>
-      <c r="C415" s="32"/>
+      <c r="B415" s="55"/>
+      <c r="C415" s="55"/>
     </row>
     <row r="416" ht="34.5" customHeight="1">
-      <c r="B416" s="32"/>
-      <c r="C416" s="32"/>
+      <c r="B416" s="55"/>
+      <c r="C416" s="55"/>
     </row>
     <row r="417" ht="34.5" customHeight="1">
-      <c r="B417" s="32"/>
-      <c r="C417" s="32"/>
+      <c r="B417" s="55"/>
+      <c r="C417" s="55"/>
     </row>
     <row r="418" ht="34.5" customHeight="1">
-      <c r="B418" s="32"/>
-      <c r="C418" s="32"/>
+      <c r="B418" s="55"/>
+      <c r="C418" s="55"/>
     </row>
     <row r="419" ht="34.5" customHeight="1">
-      <c r="B419" s="32"/>
-      <c r="C419" s="32"/>
+      <c r="B419" s="55"/>
+      <c r="C419" s="55"/>
     </row>
     <row r="420" ht="34.5" customHeight="1">
-      <c r="B420" s="32"/>
-      <c r="C420" s="32"/>
+      <c r="B420" s="55"/>
+      <c r="C420" s="55"/>
     </row>
     <row r="421" ht="34.5" customHeight="1">
-      <c r="B421" s="32"/>
-      <c r="C421" s="32"/>
+      <c r="B421" s="55"/>
+      <c r="C421" s="55"/>
     </row>
     <row r="422" ht="34.5" customHeight="1">
-      <c r="B422" s="32"/>
-      <c r="C422" s="32"/>
+      <c r="B422" s="55"/>
+      <c r="C422" s="55"/>
     </row>
     <row r="423" ht="34.5" customHeight="1">
-      <c r="B423" s="32"/>
-      <c r="C423" s="32"/>
+      <c r="B423" s="55"/>
+      <c r="C423" s="55"/>
     </row>
     <row r="424" ht="34.5" customHeight="1">
-      <c r="B424" s="32"/>
-      <c r="C424" s="32"/>
+      <c r="B424" s="55"/>
+      <c r="C424" s="55"/>
     </row>
     <row r="425" ht="34.5" customHeight="1">
-      <c r="B425" s="32"/>
-      <c r="C425" s="32"/>
+      <c r="B425" s="55"/>
+      <c r="C425" s="55"/>
     </row>
     <row r="426" ht="34.5" customHeight="1">
-      <c r="B426" s="32"/>
-      <c r="C426" s="32"/>
+      <c r="B426" s="55"/>
+      <c r="C426" s="55"/>
     </row>
     <row r="427" ht="34.5" customHeight="1">
-      <c r="B427" s="32"/>
-      <c r="C427" s="32"/>
+      <c r="B427" s="55"/>
+      <c r="C427" s="55"/>
     </row>
     <row r="428" ht="34.5" customHeight="1">
-      <c r="B428" s="32"/>
-      <c r="C428" s="32"/>
+      <c r="B428" s="55"/>
+      <c r="C428" s="55"/>
     </row>
     <row r="429" ht="34.5" customHeight="1">
-      <c r="B429" s="32"/>
-      <c r="C429" s="32"/>
+      <c r="B429" s="55"/>
+      <c r="C429" s="55"/>
     </row>
     <row r="430" ht="34.5" customHeight="1">
-      <c r="B430" s="32"/>
-      <c r="C430" s="32"/>
+      <c r="B430" s="55"/>
+      <c r="C430" s="55"/>
     </row>
     <row r="431" ht="34.5" customHeight="1">
-      <c r="B431" s="32"/>
-      <c r="C431" s="32"/>
+      <c r="B431" s="55"/>
+      <c r="C431" s="55"/>
     </row>
     <row r="432" ht="34.5" customHeight="1">
-      <c r="B432" s="32"/>
-      <c r="C432" s="32"/>
+      <c r="B432" s="55"/>
+      <c r="C432" s="55"/>
     </row>
     <row r="433" ht="34.5" customHeight="1">
-      <c r="B433" s="32"/>
-      <c r="C433" s="32"/>
+      <c r="B433" s="55"/>
+      <c r="C433" s="55"/>
     </row>
     <row r="434" ht="34.5" customHeight="1">
-      <c r="B434" s="32"/>
-      <c r="C434" s="32"/>
+      <c r="B434" s="55"/>
+      <c r="C434" s="55"/>
     </row>
     <row r="435" ht="34.5" customHeight="1">
-      <c r="B435" s="32"/>
-      <c r="C435" s="32"/>
+      <c r="B435" s="55"/>
+      <c r="C435" s="55"/>
     </row>
     <row r="436" ht="34.5" customHeight="1">
-      <c r="B436" s="32"/>
-      <c r="C436" s="32"/>
+      <c r="B436" s="55"/>
+      <c r="C436" s="55"/>
     </row>
     <row r="437" ht="34.5" customHeight="1">
-      <c r="B437" s="32"/>
-      <c r="C437" s="32"/>
+      <c r="B437" s="55"/>
+      <c r="C437" s="55"/>
     </row>
     <row r="438" ht="34.5" customHeight="1">
-      <c r="B438" s="32"/>
-      <c r="C438" s="32"/>
+      <c r="B438" s="55"/>
+      <c r="C438" s="55"/>
     </row>
     <row r="439" ht="34.5" customHeight="1">
-      <c r="B439" s="32"/>
-      <c r="C439" s="32"/>
+      <c r="B439" s="55"/>
+      <c r="C439" s="55"/>
     </row>
     <row r="440" ht="34.5" customHeight="1">
-      <c r="B440" s="32"/>
-      <c r="C440" s="32"/>
+      <c r="B440" s="55"/>
+      <c r="C440" s="55"/>
     </row>
     <row r="441" ht="34.5" customHeight="1">
-      <c r="B441" s="32"/>
-      <c r="C441" s="32"/>
+      <c r="B441" s="55"/>
+      <c r="C441" s="55"/>
     </row>
     <row r="442" ht="34.5" customHeight="1">
-      <c r="B442" s="32"/>
-      <c r="C442" s="32"/>
+      <c r="B442" s="55"/>
+      <c r="C442" s="55"/>
     </row>
     <row r="443" ht="34.5" customHeight="1">
-      <c r="B443" s="32"/>
-      <c r="C443" s="32"/>
+      <c r="B443" s="55"/>
+      <c r="C443" s="55"/>
     </row>
     <row r="444" ht="34.5" customHeight="1">
-      <c r="B444" s="32"/>
-      <c r="C444" s="32"/>
+      <c r="B444" s="55"/>
+      <c r="C444" s="55"/>
     </row>
     <row r="445" ht="34.5" customHeight="1">
-      <c r="B445" s="32"/>
-      <c r="C445" s="32"/>
+      <c r="B445" s="55"/>
+      <c r="C445" s="55"/>
     </row>
     <row r="446" ht="34.5" customHeight="1">
-      <c r="B446" s="32"/>
-      <c r="C446" s="32"/>
+      <c r="B446" s="55"/>
+      <c r="C446" s="55"/>
     </row>
     <row r="447" ht="34.5" customHeight="1">
-      <c r="B447" s="32"/>
-      <c r="C447" s="32"/>
+      <c r="B447" s="55"/>
+      <c r="C447" s="55"/>
     </row>
     <row r="448" ht="34.5" customHeight="1">
-      <c r="B448" s="32"/>
-      <c r="C448" s="32"/>
+      <c r="B448" s="55"/>
+      <c r="C448" s="55"/>
     </row>
     <row r="449" ht="34.5" customHeight="1">
-      <c r="B449" s="32"/>
-      <c r="C449" s="32"/>
+      <c r="B449" s="55"/>
+      <c r="C449" s="55"/>
     </row>
     <row r="450" ht="34.5" customHeight="1">
-      <c r="B450" s="32"/>
-      <c r="C450" s="32"/>
+      <c r="B450" s="55"/>
+      <c r="C450" s="55"/>
     </row>
     <row r="451" ht="34.5" customHeight="1">
-      <c r="B451" s="32"/>
-      <c r="C451" s="32"/>
+      <c r="B451" s="55"/>
+      <c r="C451" s="55"/>
     </row>
     <row r="452" ht="34.5" customHeight="1">
-      <c r="B452" s="32"/>
-      <c r="C452" s="32"/>
+      <c r="B452" s="55"/>
+      <c r="C452" s="55"/>
     </row>
     <row r="453" ht="34.5" customHeight="1">
-      <c r="B453" s="32"/>
-      <c r="C453" s="32"/>
+      <c r="B453" s="55"/>
+      <c r="C453" s="55"/>
     </row>
     <row r="454" ht="34.5" customHeight="1">
-      <c r="B454" s="32"/>
-      <c r="C454" s="32"/>
+      <c r="B454" s="55"/>
+      <c r="C454" s="55"/>
     </row>
     <row r="455" ht="34.5" customHeight="1">
-      <c r="B455" s="32"/>
-      <c r="C455" s="32"/>
+      <c r="B455" s="55"/>
+      <c r="C455" s="55"/>
     </row>
     <row r="456" ht="34.5" customHeight="1">
-      <c r="B456" s="32"/>
-      <c r="C456" s="32"/>
+      <c r="B456" s="55"/>
+      <c r="C456" s="55"/>
     </row>
     <row r="457" ht="34.5" customHeight="1">
-      <c r="B457" s="32"/>
-      <c r="C457" s="32"/>
+      <c r="B457" s="55"/>
+      <c r="C457" s="55"/>
     </row>
     <row r="458" ht="34.5" customHeight="1">
-      <c r="B458" s="32"/>
-      <c r="C458" s="32"/>
+      <c r="B458" s="55"/>
+      <c r="C458" s="55"/>
     </row>
     <row r="459" ht="34.5" customHeight="1">
-      <c r="B459" s="32"/>
-      <c r="C459" s="32"/>
+      <c r="B459" s="55"/>
+      <c r="C459" s="55"/>
     </row>
     <row r="460" ht="34.5" customHeight="1">
-      <c r="B460" s="32"/>
-      <c r="C460" s="32"/>
+      <c r="B460" s="55"/>
+      <c r="C460" s="55"/>
     </row>
     <row r="461" ht="34.5" customHeight="1">
-      <c r="B461" s="32"/>
-      <c r="C461" s="32"/>
+      <c r="B461" s="55"/>
+      <c r="C461" s="55"/>
     </row>
     <row r="462" ht="34.5" customHeight="1">
-      <c r="B462" s="32"/>
-      <c r="C462" s="32"/>
+      <c r="B462" s="55"/>
+      <c r="C462" s="55"/>
     </row>
     <row r="463" ht="34.5" customHeight="1">
-      <c r="B463" s="32"/>
-      <c r="C463" s="32"/>
+      <c r="B463" s="55"/>
+      <c r="C463" s="55"/>
     </row>
     <row r="464" ht="34.5" customHeight="1">
-      <c r="B464" s="32"/>
-      <c r="C464" s="32"/>
+      <c r="B464" s="55"/>
+      <c r="C464" s="55"/>
     </row>
     <row r="465" ht="34.5" customHeight="1">
-      <c r="B465" s="32"/>
-      <c r="C465" s="32"/>
+      <c r="B465" s="55"/>
+      <c r="C465" s="55"/>
     </row>
     <row r="466" ht="34.5" customHeight="1">
-      <c r="B466" s="32"/>
-      <c r="C466" s="32"/>
+      <c r="B466" s="55"/>
+      <c r="C466" s="55"/>
     </row>
     <row r="467" ht="34.5" customHeight="1">
-      <c r="B467" s="32"/>
-      <c r="C467" s="32"/>
+      <c r="B467" s="55"/>
+      <c r="C467" s="55"/>
     </row>
     <row r="468" ht="34.5" customHeight="1">
-      <c r="B468" s="32"/>
-      <c r="C468" s="32"/>
+      <c r="B468" s="55"/>
+      <c r="C468" s="55"/>
     </row>
     <row r="469" ht="34.5" customHeight="1">
-      <c r="B469" s="32"/>
-      <c r="C469" s="32"/>
+      <c r="B469" s="55"/>
+      <c r="C469" s="55"/>
     </row>
     <row r="470" ht="34.5" customHeight="1">
-      <c r="B470" s="32"/>
-      <c r="C470" s="32"/>
+      <c r="B470" s="55"/>
+      <c r="C470" s="55"/>
     </row>
     <row r="471" ht="34.5" customHeight="1">
-      <c r="B471" s="32"/>
-      <c r="C471" s="32"/>
+      <c r="B471" s="55"/>
+      <c r="C471" s="55"/>
     </row>
     <row r="472" ht="34.5" customHeight="1">
-      <c r="B472" s="32"/>
-      <c r="C472" s="32"/>
+      <c r="B472" s="55"/>
+      <c r="C472" s="55"/>
     </row>
     <row r="473" ht="34.5" customHeight="1">
-      <c r="B473" s="32"/>
-      <c r="C473" s="32"/>
+      <c r="B473" s="55"/>
+      <c r="C473" s="55"/>
     </row>
     <row r="474" ht="34.5" customHeight="1">
-      <c r="B474" s="32"/>
-      <c r="C474" s="32"/>
+      <c r="B474" s="55"/>
+      <c r="C474" s="55"/>
     </row>
     <row r="475" ht="34.5" customHeight="1">
-      <c r="B475" s="32"/>
-      <c r="C475" s="32"/>
+      <c r="B475" s="55"/>
+      <c r="C475" s="55"/>
     </row>
     <row r="476" ht="34.5" customHeight="1">
-      <c r="B476" s="32"/>
-      <c r="C476" s="32"/>
+      <c r="B476" s="55"/>
+      <c r="C476" s="55"/>
     </row>
     <row r="477" ht="34.5" customHeight="1">
-      <c r="B477" s="32"/>
-      <c r="C477" s="32"/>
+      <c r="B477" s="55"/>
+      <c r="C477" s="55"/>
     </row>
     <row r="478" ht="34.5" customHeight="1">
-      <c r="B478" s="32"/>
-      <c r="C478" s="32"/>
+      <c r="B478" s="55"/>
+      <c r="C478" s="55"/>
     </row>
     <row r="479" ht="34.5" customHeight="1">
-      <c r="B479" s="32"/>
-      <c r="C479" s="32"/>
+      <c r="B479" s="55"/>
+      <c r="C479" s="55"/>
     </row>
     <row r="480" ht="34.5" customHeight="1">
-      <c r="B480" s="32"/>
-      <c r="C480" s="32"/>
+      <c r="B480" s="55"/>
+      <c r="C480" s="55"/>
     </row>
     <row r="481" ht="34.5" customHeight="1">
-      <c r="B481" s="32"/>
-      <c r="C481" s="32"/>
+      <c r="B481" s="55"/>
+      <c r="C481" s="55"/>
     </row>
     <row r="482" ht="34.5" customHeight="1">
-      <c r="B482" s="32"/>
-      <c r="C482" s="32"/>
+      <c r="B482" s="55"/>
+      <c r="C482" s="55"/>
     </row>
     <row r="483" ht="34.5" customHeight="1">
-      <c r="B483" s="32"/>
-      <c r="C483" s="32"/>
+      <c r="B483" s="55"/>
+      <c r="C483" s="55"/>
     </row>
     <row r="484" ht="34.5" customHeight="1">
-      <c r="B484" s="32"/>
-      <c r="C484" s="32"/>
+      <c r="B484" s="55"/>
+      <c r="C484" s="55"/>
     </row>
     <row r="485" ht="34.5" customHeight="1">
-      <c r="B485" s="32"/>
-      <c r="C485" s="32"/>
+      <c r="B485" s="55"/>
+      <c r="C485" s="55"/>
     </row>
     <row r="486" ht="34.5" customHeight="1">
-      <c r="B486" s="32"/>
-      <c r="C486" s="32"/>
+      <c r="B486" s="55"/>
+      <c r="C486" s="55"/>
     </row>
     <row r="487" ht="34.5" customHeight="1">
-      <c r="B487" s="32"/>
-      <c r="C487" s="32"/>
+      <c r="B487" s="55"/>
+      <c r="C487" s="55"/>
     </row>
     <row r="488" ht="34.5" customHeight="1">
-      <c r="B488" s="32"/>
-      <c r="C488" s="32"/>
+      <c r="B488" s="55"/>
+      <c r="C488" s="55"/>
     </row>
     <row r="489" ht="34.5" customHeight="1">
-      <c r="B489" s="32"/>
-      <c r="C489" s="32"/>
+      <c r="B489" s="55"/>
+      <c r="C489" s="55"/>
     </row>
     <row r="490" ht="34.5" customHeight="1">
-      <c r="B490" s="32"/>
-      <c r="C490" s="32"/>
+      <c r="B490" s="55"/>
+      <c r="C490" s="55"/>
     </row>
     <row r="491" ht="34.5" customHeight="1">
-      <c r="B491" s="32"/>
-      <c r="C491" s="32"/>
+      <c r="B491" s="55"/>
+      <c r="C491" s="55"/>
     </row>
     <row r="492" ht="34.5" customHeight="1">
-      <c r="B492" s="32"/>
-      <c r="C492" s="32"/>
+      <c r="B492" s="55"/>
+      <c r="C492" s="55"/>
     </row>
     <row r="493" ht="34.5" customHeight="1">
-      <c r="B493" s="32"/>
-      <c r="C493" s="32"/>
+      <c r="B493" s="55"/>
+      <c r="C493" s="55"/>
     </row>
     <row r="494" ht="34.5" customHeight="1">
-      <c r="B494" s="32"/>
-      <c r="C494" s="32"/>
+      <c r="B494" s="55"/>
+      <c r="C494" s="55"/>
     </row>
     <row r="495" ht="34.5" customHeight="1">
-      <c r="B495" s="32"/>
-      <c r="C495" s="32"/>
+      <c r="B495" s="55"/>
+      <c r="C495" s="55"/>
     </row>
     <row r="496" ht="34.5" customHeight="1">
-      <c r="B496" s="32"/>
-      <c r="C496" s="32"/>
+      <c r="B496" s="55"/>
+      <c r="C496" s="55"/>
     </row>
     <row r="497" ht="34.5" customHeight="1">
-      <c r="B497" s="32"/>
-      <c r="C497" s="32"/>
+      <c r="B497" s="55"/>
+      <c r="C497" s="55"/>
     </row>
     <row r="498" ht="34.5" customHeight="1">
-      <c r="B498" s="32"/>
-      <c r="C498" s="32"/>
+      <c r="B498" s="55"/>
+      <c r="C498" s="55"/>
     </row>
     <row r="499" ht="34.5" customHeight="1">
-      <c r="B499" s="32"/>
-      <c r="C499" s="32"/>
+      <c r="B499" s="55"/>
+      <c r="C499" s="55"/>
     </row>
     <row r="500" ht="34.5" customHeight="1">
-      <c r="B500" s="32"/>
-      <c r="C500" s="32"/>
+      <c r="B500" s="55"/>
+      <c r="C500" s="55"/>
     </row>
     <row r="501" ht="34.5" customHeight="1">
-      <c r="B501" s="32"/>
-      <c r="C501" s="32"/>
+      <c r="B501" s="55"/>
+      <c r="C501" s="55"/>
     </row>
     <row r="502" ht="34.5" customHeight="1">
-      <c r="B502" s="32"/>
-      <c r="C502" s="32"/>
+      <c r="B502" s="55"/>
+      <c r="C502" s="55"/>
     </row>
     <row r="503" ht="34.5" customHeight="1">
-      <c r="B503" s="32"/>
-      <c r="C503" s="32"/>
+      <c r="B503" s="55"/>
+      <c r="C503" s="55"/>
     </row>
     <row r="504" ht="34.5" customHeight="1">
-      <c r="B504" s="32"/>
-      <c r="C504" s="32"/>
+      <c r="B504" s="55"/>
+      <c r="C504" s="55"/>
     </row>
     <row r="505" ht="34.5" customHeight="1">
-      <c r="B505" s="32"/>
-      <c r="C505" s="32"/>
+      <c r="B505" s="55"/>
+      <c r="C505" s="55"/>
     </row>
     <row r="506" ht="34.5" customHeight="1">
-      <c r="B506" s="32"/>
-      <c r="C506" s="32"/>
+      <c r="B506" s="55"/>
+      <c r="C506" s="55"/>
     </row>
     <row r="507" ht="34.5" customHeight="1">
-      <c r="B507" s="32"/>
-      <c r="C507" s="32"/>
+      <c r="B507" s="55"/>
+      <c r="C507" s="55"/>
     </row>
     <row r="508" ht="34.5" customHeight="1">
-      <c r="B508" s="32"/>
-      <c r="C508" s="32"/>
+      <c r="B508" s="55"/>
+      <c r="C508" s="55"/>
     </row>
     <row r="509" ht="34.5" customHeight="1">
-      <c r="B509" s="32"/>
-      <c r="C509" s="32"/>
+      <c r="B509" s="55"/>
+      <c r="C509" s="55"/>
     </row>
     <row r="510" ht="34.5" customHeight="1">
-      <c r="B510" s="32"/>
-      <c r="C510" s="32"/>
+      <c r="B510" s="55"/>
+      <c r="C510" s="55"/>
     </row>
     <row r="511" ht="34.5" customHeight="1">
-      <c r="B511" s="32"/>
-      <c r="C511" s="32"/>
+      <c r="B511" s="55"/>
+      <c r="C511" s="55"/>
     </row>
     <row r="512" ht="34.5" customHeight="1">
-      <c r="B512" s="32"/>
-      <c r="C512" s="32"/>
+      <c r="B512" s="55"/>
+      <c r="C512" s="55"/>
     </row>
     <row r="513" ht="34.5" customHeight="1">
-      <c r="B513" s="32"/>
-      <c r="C513" s="32"/>
+      <c r="B513" s="55"/>
+      <c r="C513" s="55"/>
     </row>
     <row r="514" ht="34.5" customHeight="1">
-      <c r="B514" s="32"/>
-      <c r="C514" s="32"/>
+      <c r="B514" s="55"/>
+      <c r="C514" s="55"/>
     </row>
     <row r="515" ht="34.5" customHeight="1">
-      <c r="B515" s="32"/>
-      <c r="C515" s="32"/>
+      <c r="B515" s="55"/>
+      <c r="C515" s="55"/>
     </row>
     <row r="516" ht="34.5" customHeight="1">
-      <c r="B516" s="32"/>
-      <c r="C516" s="32"/>
+      <c r="B516" s="55"/>
+      <c r="C516" s="55"/>
     </row>
     <row r="517" ht="34.5" customHeight="1">
-      <c r="B517" s="32"/>
-      <c r="C517" s="32"/>
+      <c r="B517" s="55"/>
+      <c r="C517" s="55"/>
     </row>
     <row r="518" ht="34.5" customHeight="1">
-      <c r="B518" s="32"/>
-      <c r="C518" s="32"/>
+      <c r="B518" s="55"/>
+      <c r="C518" s="55"/>
     </row>
     <row r="519" ht="34.5" customHeight="1">
-      <c r="B519" s="32"/>
-      <c r="C519" s="32"/>
+      <c r="B519" s="55"/>
+      <c r="C519" s="55"/>
     </row>
     <row r="520" ht="34.5" customHeight="1">
-      <c r="B520" s="32"/>
-      <c r="C520" s="32"/>
+      <c r="B520" s="55"/>
+      <c r="C520" s="55"/>
     </row>
     <row r="521" ht="34.5" customHeight="1">
-      <c r="B521" s="32"/>
-      <c r="C521" s="32"/>
+      <c r="B521" s="55"/>
+      <c r="C521" s="55"/>
     </row>
     <row r="522" ht="34.5" customHeight="1">
-      <c r="B522" s="32"/>
-      <c r="C522" s="32"/>
+      <c r="B522" s="55"/>
+      <c r="C522" s="55"/>
     </row>
     <row r="523" ht="34.5" customHeight="1">
-      <c r="B523" s="32"/>
-      <c r="C523" s="32"/>
+      <c r="B523" s="55"/>
+      <c r="C523" s="55"/>
     </row>
     <row r="524" ht="34.5" customHeight="1">
-      <c r="B524" s="32"/>
-      <c r="C524" s="32"/>
+      <c r="B524" s="55"/>
+      <c r="C524" s="55"/>
     </row>
     <row r="525" ht="34.5" customHeight="1">
-      <c r="B525" s="32"/>
-      <c r="C525" s="32"/>
+      <c r="B525" s="55"/>
+      <c r="C525" s="55"/>
     </row>
     <row r="526" ht="34.5" customHeight="1">
-      <c r="B526" s="32"/>
-      <c r="C526" s="32"/>
+      <c r="B526" s="55"/>
+      <c r="C526" s="55"/>
     </row>
     <row r="527" ht="34.5" customHeight="1">
-      <c r="B527" s="32"/>
-      <c r="C527" s="32"/>
+      <c r="B527" s="55"/>
+      <c r="C527" s="55"/>
     </row>
     <row r="528" ht="34.5" customHeight="1">
-      <c r="B528" s="32"/>
-      <c r="C528" s="32"/>
+      <c r="B528" s="55"/>
+      <c r="C528" s="55"/>
     </row>
     <row r="529" ht="34.5" customHeight="1">
-      <c r="B529" s="32"/>
-      <c r="C529" s="32"/>
+      <c r="B529" s="55"/>
+      <c r="C529" s="55"/>
     </row>
     <row r="530" ht="34.5" customHeight="1">
-      <c r="B530" s="32"/>
-      <c r="C530" s="32"/>
+      <c r="B530" s="55"/>
+      <c r="C530" s="55"/>
     </row>
     <row r="531" ht="34.5" customHeight="1">
-      <c r="B531" s="32"/>
-      <c r="C531" s="32"/>
+      <c r="B531" s="55"/>
+      <c r="C531" s="55"/>
     </row>
     <row r="532" ht="34.5" customHeight="1">
-      <c r="B532" s="32"/>
-      <c r="C532" s="32"/>
+      <c r="B532" s="55"/>
+      <c r="C532" s="55"/>
     </row>
     <row r="533" ht="34.5" customHeight="1">
-      <c r="B533" s="32"/>
-      <c r="C533" s="32"/>
+      <c r="B533" s="55"/>
+      <c r="C533" s="55"/>
     </row>
     <row r="534" ht="34.5" customHeight="1">
-      <c r="B534" s="32"/>
-      <c r="C534" s="32"/>
+      <c r="B534" s="55"/>
+      <c r="C534" s="55"/>
     </row>
     <row r="535" ht="34.5" customHeight="1">
-      <c r="B535" s="32"/>
-      <c r="C535" s="32"/>
+      <c r="B535" s="55"/>
+      <c r="C535" s="55"/>
     </row>
     <row r="536" ht="34.5" customHeight="1">
-      <c r="B536" s="32"/>
-      <c r="C536" s="32"/>
+      <c r="B536" s="55"/>
+      <c r="C536" s="55"/>
     </row>
     <row r="537" ht="34.5" customHeight="1">
-      <c r="B537" s="32"/>
-      <c r="C537" s="32"/>
+      <c r="B537" s="55"/>
+      <c r="C537" s="55"/>
     </row>
     <row r="538" ht="34.5" customHeight="1">
-      <c r="B538" s="32"/>
-      <c r="C538" s="32"/>
+      <c r="B538" s="55"/>
+      <c r="C538" s="55"/>
     </row>
     <row r="539" ht="34.5" customHeight="1">
-      <c r="B539" s="32"/>
-      <c r="C539" s="32"/>
+      <c r="B539" s="55"/>
+      <c r="C539" s="55"/>
     </row>
     <row r="540" ht="34.5" customHeight="1">
-      <c r="B540" s="32"/>
-      <c r="C540" s="32"/>
+      <c r="B540" s="55"/>
+      <c r="C540" s="55"/>
     </row>
     <row r="541" ht="34.5" customHeight="1">
-      <c r="B541" s="32"/>
-      <c r="C541" s="32"/>
+      <c r="B541" s="55"/>
+      <c r="C541" s="55"/>
     </row>
     <row r="542" ht="34.5" customHeight="1">
-      <c r="B542" s="32"/>
-      <c r="C542" s="32"/>
+      <c r="B542" s="55"/>
+      <c r="C542" s="55"/>
     </row>
     <row r="543" ht="34.5" customHeight="1">
-      <c r="B543" s="32"/>
-      <c r="C543" s="32"/>
+      <c r="B543" s="55"/>
+      <c r="C543" s="55"/>
     </row>
     <row r="544" ht="34.5" customHeight="1">
-      <c r="B544" s="32"/>
-      <c r="C544" s="32"/>
+      <c r="B544" s="55"/>
+      <c r="C544" s="55"/>
     </row>
     <row r="545" ht="34.5" customHeight="1">
-      <c r="B545" s="32"/>
-      <c r="C545" s="32"/>
+      <c r="B545" s="55"/>
+      <c r="C545" s="55"/>
     </row>
     <row r="546" ht="34.5" customHeight="1">
-      <c r="B546" s="32"/>
-      <c r="C546" s="32"/>
+      <c r="B546" s="55"/>
+      <c r="C546" s="55"/>
     </row>
     <row r="547" ht="34.5" customHeight="1">
-      <c r="B547" s="32"/>
-      <c r="C547" s="32"/>
+      <c r="B547" s="55"/>
+      <c r="C547" s="55"/>
     </row>
     <row r="548" ht="34.5" customHeight="1">
-      <c r="B548" s="32"/>
-      <c r="C548" s="32"/>
+      <c r="B548" s="55"/>
+      <c r="C548" s="55"/>
     </row>
     <row r="549" ht="34.5" customHeight="1">
-      <c r="B549" s="32"/>
-      <c r="C549" s="32"/>
+      <c r="B549" s="55"/>
+      <c r="C549" s="55"/>
     </row>
     <row r="550" ht="34.5" customHeight="1">
-      <c r="B550" s="32"/>
-      <c r="C550" s="32"/>
+      <c r="B550" s="55"/>
+      <c r="C550" s="55"/>
     </row>
     <row r="551" ht="34.5" customHeight="1">
-      <c r="B551" s="32"/>
-      <c r="C551" s="32"/>
+      <c r="B551" s="55"/>
+      <c r="C551" s="55"/>
     </row>
     <row r="552" ht="34.5" customHeight="1">
-      <c r="B552" s="32"/>
-      <c r="C552" s="32"/>
+      <c r="B552" s="55"/>
+      <c r="C552" s="55"/>
     </row>
     <row r="553" ht="34.5" customHeight="1">
-      <c r="B553" s="32"/>
-      <c r="C553" s="32"/>
+      <c r="B553" s="55"/>
+      <c r="C553" s="55"/>
     </row>
     <row r="554" ht="34.5" customHeight="1">
-      <c r="B554" s="32"/>
-      <c r="C554" s="32"/>
+      <c r="B554" s="55"/>
+      <c r="C554" s="55"/>
     </row>
     <row r="555" ht="34.5" customHeight="1">
-      <c r="B555" s="32"/>
-      <c r="C555" s="32"/>
+      <c r="B555" s="55"/>
+      <c r="C555" s="55"/>
     </row>
     <row r="556" ht="34.5" customHeight="1">
-      <c r="B556" s="32"/>
-      <c r="C556" s="32"/>
+      <c r="B556" s="55"/>
+      <c r="C556" s="55"/>
     </row>
     <row r="557" ht="34.5" customHeight="1">
-      <c r="B557" s="32"/>
-      <c r="C557" s="32"/>
+      <c r="B557" s="55"/>
+      <c r="C557" s="55"/>
     </row>
     <row r="558" ht="34.5" customHeight="1">
-      <c r="B558" s="32"/>
-      <c r="C558" s="32"/>
+      <c r="B558" s="55"/>
+      <c r="C558" s="55"/>
     </row>
     <row r="559" ht="34.5" customHeight="1">
-      <c r="B559" s="32"/>
-      <c r="C559" s="32"/>
+      <c r="B559" s="55"/>
+      <c r="C559" s="55"/>
     </row>
     <row r="560" ht="34.5" customHeight="1">
-      <c r="B560" s="32"/>
-      <c r="C560" s="32"/>
+      <c r="B560" s="55"/>
+      <c r="C560" s="55"/>
     </row>
     <row r="561" ht="34.5" customHeight="1">
-      <c r="B561" s="32"/>
-      <c r="C561" s="32"/>
+      <c r="B561" s="55"/>
+      <c r="C561" s="55"/>
     </row>
     <row r="562" ht="34.5" customHeight="1">
-      <c r="B562" s="32"/>
-      <c r="C562" s="32"/>
+      <c r="B562" s="55"/>
+      <c r="C562" s="55"/>
     </row>
     <row r="563" ht="34.5" customHeight="1">
-      <c r="B563" s="32"/>
-      <c r="C563" s="32"/>
+      <c r="B563" s="55"/>
+      <c r="C563" s="55"/>
     </row>
     <row r="564" ht="34.5" customHeight="1">
-      <c r="B564" s="32"/>
-      <c r="C564" s="32"/>
+      <c r="B564" s="55"/>
+      <c r="C564" s="55"/>
     </row>
     <row r="565" ht="34.5" customHeight="1">
-      <c r="B565" s="32"/>
-      <c r="C565" s="32"/>
+      <c r="B565" s="55"/>
+      <c r="C565" s="55"/>
     </row>
     <row r="566" ht="34.5" customHeight="1">
-      <c r="B566" s="32"/>
-      <c r="C566" s="32"/>
+      <c r="B566" s="55"/>
+      <c r="C566" s="55"/>
     </row>
     <row r="567" ht="34.5" customHeight="1">
-      <c r="B567" s="32"/>
-      <c r="C567" s="32"/>
+      <c r="B567" s="55"/>
+      <c r="C567" s="55"/>
     </row>
     <row r="568" ht="34.5" customHeight="1">
-      <c r="B568" s="32"/>
-      <c r="C568" s="32"/>
+      <c r="B568" s="55"/>
+      <c r="C568" s="55"/>
     </row>
     <row r="569" ht="34.5" customHeight="1">
-      <c r="B569" s="32"/>
-      <c r="C569" s="32"/>
+      <c r="B569" s="55"/>
+      <c r="C569" s="55"/>
     </row>
     <row r="570" ht="34.5" customHeight="1">
-      <c r="B570" s="32"/>
-      <c r="C570" s="32"/>
+      <c r="B570" s="55"/>
+      <c r="C570" s="55"/>
     </row>
     <row r="571" ht="34.5" customHeight="1">
-      <c r="B571" s="32"/>
-      <c r="C571" s="32"/>
+      <c r="B571" s="55"/>
+      <c r="C571" s="55"/>
     </row>
     <row r="572" ht="34.5" customHeight="1">
-      <c r="B572" s="32"/>
-      <c r="C572" s="32"/>
+      <c r="B572" s="55"/>
+      <c r="C572" s="55"/>
     </row>
     <row r="573" ht="34.5" customHeight="1">
-      <c r="B573" s="32"/>
-      <c r="C573" s="32"/>
+      <c r="B573" s="55"/>
+      <c r="C573" s="55"/>
     </row>
     <row r="574" ht="34.5" customHeight="1">
-      <c r="B574" s="32"/>
-      <c r="C574" s="32"/>
+      <c r="B574" s="55"/>
+      <c r="C574" s="55"/>
     </row>
     <row r="575" ht="34.5" customHeight="1">
-      <c r="B575" s="32"/>
-      <c r="C575" s="32"/>
+      <c r="B575" s="55"/>
+      <c r="C575" s="55"/>
     </row>
     <row r="576" ht="34.5" customHeight="1">
-      <c r="B576" s="32"/>
-      <c r="C576" s="32"/>
+      <c r="B576" s="55"/>
+      <c r="C576" s="55"/>
     </row>
     <row r="577" ht="34.5" customHeight="1">
-      <c r="B577" s="32"/>
-      <c r="C577" s="32"/>
+      <c r="B577" s="55"/>
+      <c r="C577" s="55"/>
     </row>
     <row r="578" ht="34.5" customHeight="1">
-      <c r="B578" s="32"/>
-      <c r="C578" s="32"/>
+      <c r="B578" s="55"/>
+      <c r="C578" s="55"/>
     </row>
     <row r="579" ht="34.5" customHeight="1">
-      <c r="B579" s="32"/>
-      <c r="C579" s="32"/>
+      <c r="B579" s="55"/>
+      <c r="C579" s="55"/>
     </row>
     <row r="580" ht="34.5" customHeight="1">
-      <c r="B580" s="32"/>
-      <c r="C580" s="32"/>
+      <c r="B580" s="55"/>
+      <c r="C580" s="55"/>
     </row>
     <row r="581" ht="34.5" customHeight="1">
-      <c r="B581" s="32"/>
-      <c r="C581" s="32"/>
+      <c r="B581" s="55"/>
+      <c r="C581" s="55"/>
     </row>
     <row r="582" ht="34.5" customHeight="1">
-      <c r="B582" s="32"/>
-      <c r="C582" s="32"/>
+      <c r="B582" s="55"/>
+      <c r="C582" s="55"/>
     </row>
     <row r="583" ht="34.5" customHeight="1">
-      <c r="B583" s="32"/>
-      <c r="C583" s="32"/>
+      <c r="B583" s="55"/>
+      <c r="C583" s="55"/>
     </row>
     <row r="584" ht="34.5" customHeight="1">
-      <c r="B584" s="32"/>
-      <c r="C584" s="32"/>
+      <c r="B584" s="55"/>
+      <c r="C584" s="55"/>
     </row>
     <row r="585" ht="34.5" customHeight="1">
-      <c r="B585" s="32"/>
-      <c r="C585" s="32"/>
+      <c r="B585" s="55"/>
+      <c r="C585" s="55"/>
     </row>
     <row r="586" ht="34.5" customHeight="1">
-      <c r="B586" s="32"/>
-      <c r="C586" s="32"/>
+      <c r="B586" s="55"/>
+      <c r="C586" s="55"/>
     </row>
     <row r="587" ht="34.5" customHeight="1">
-      <c r="B587" s="32"/>
-      <c r="C587" s="32"/>
+      <c r="B587" s="55"/>
+      <c r="C587" s="55"/>
     </row>
     <row r="588" ht="34.5" customHeight="1">
-      <c r="B588" s="32"/>
-      <c r="C588" s="32"/>
+      <c r="B588" s="55"/>
+      <c r="C588" s="55"/>
     </row>
     <row r="589" ht="34.5" customHeight="1">
-      <c r="B589" s="32"/>
-      <c r="C589" s="32"/>
+      <c r="B589" s="55"/>
+      <c r="C589" s="55"/>
     </row>
     <row r="590" ht="34.5" customHeight="1">
-      <c r="B590" s="32"/>
-      <c r="C590" s="32"/>
+      <c r="B590" s="55"/>
+      <c r="C590" s="55"/>
     </row>
     <row r="591" ht="34.5" customHeight="1">
-      <c r="B591" s="32"/>
-      <c r="C591" s="32"/>
+      <c r="B591" s="55"/>
+      <c r="C591" s="55"/>
     </row>
     <row r="592" ht="34.5" customHeight="1">
-      <c r="B592" s="32"/>
-      <c r="C592" s="32"/>
+      <c r="B592" s="55"/>
+      <c r="C592" s="55"/>
     </row>
     <row r="593" ht="34.5" customHeight="1">
-      <c r="B593" s="32"/>
-      <c r="C593" s="32"/>
+      <c r="B593" s="55"/>
+      <c r="C593" s="55"/>
     </row>
     <row r="594" ht="34.5" customHeight="1">
-      <c r="B594" s="32"/>
-      <c r="C594" s="32"/>
+      <c r="B594" s="55"/>
+      <c r="C594" s="55"/>
     </row>
     <row r="595" ht="34.5" customHeight="1">
-      <c r="B595" s="32"/>
-      <c r="C595" s="32"/>
+      <c r="B595" s="55"/>
+      <c r="C595" s="55"/>
     </row>
     <row r="596" ht="34.5" customHeight="1">
-      <c r="B596" s="32"/>
-      <c r="C596" s="32"/>
+      <c r="B596" s="55"/>
+      <c r="C596" s="55"/>
     </row>
     <row r="597" ht="34.5" customHeight="1">
-      <c r="B597" s="32"/>
-      <c r="C597" s="32"/>
+      <c r="B597" s="55"/>
+      <c r="C597" s="55"/>
     </row>
     <row r="598" ht="34.5" customHeight="1">
-      <c r="B598" s="32"/>
-      <c r="C598" s="32"/>
+      <c r="B598" s="55"/>
+      <c r="C598" s="55"/>
     </row>
     <row r="599" ht="34.5" customHeight="1">
-      <c r="B599" s="32"/>
-      <c r="C599" s="32"/>
+      <c r="B599" s="55"/>
+      <c r="C599" s="55"/>
     </row>
     <row r="600" ht="34.5" customHeight="1">
-      <c r="B600" s="32"/>
-      <c r="C600" s="32"/>
+      <c r="B600" s="55"/>
+      <c r="C600" s="55"/>
     </row>
     <row r="601" ht="34.5" customHeight="1">
-      <c r="B601" s="32"/>
-      <c r="C601" s="32"/>
+      <c r="B601" s="55"/>
+      <c r="C601" s="55"/>
     </row>
     <row r="602" ht="34.5" customHeight="1">
-      <c r="B602" s="32"/>
-      <c r="C602" s="32"/>
+      <c r="B602" s="55"/>
+      <c r="C602" s="55"/>
     </row>
     <row r="603" ht="34.5" customHeight="1">
-      <c r="B603" s="32"/>
-      <c r="C603" s="32"/>
+      <c r="B603" s="55"/>
+      <c r="C603" s="55"/>
     </row>
     <row r="604" ht="34.5" customHeight="1">
-      <c r="B604" s="32"/>
-      <c r="C604" s="32"/>
+      <c r="B604" s="55"/>
+      <c r="C604" s="55"/>
     </row>
     <row r="605" ht="34.5" customHeight="1">
-      <c r="B605" s="32"/>
-      <c r="C605" s="32"/>
+      <c r="B605" s="55"/>
+      <c r="C605" s="55"/>
     </row>
     <row r="606" ht="34.5" customHeight="1">
-      <c r="B606" s="32"/>
-      <c r="C606" s="32"/>
+      <c r="B606" s="55"/>
+      <c r="C606" s="55"/>
     </row>
     <row r="607" ht="34.5" customHeight="1">
-      <c r="B607" s="32"/>
-      <c r="C607" s="32"/>
+      <c r="B607" s="55"/>
+      <c r="C607" s="55"/>
     </row>
     <row r="608" ht="34.5" customHeight="1">
-      <c r="B608" s="32"/>
-      <c r="C608" s="32"/>
+      <c r="B608" s="55"/>
+      <c r="C608" s="55"/>
     </row>
     <row r="609" ht="34.5" customHeight="1">
-      <c r="B609" s="32"/>
-      <c r="C609" s="32"/>
+      <c r="B609" s="55"/>
+      <c r="C609" s="55"/>
     </row>
     <row r="610" ht="34.5" customHeight="1">
-      <c r="B610" s="32"/>
-      <c r="C610" s="32"/>
+      <c r="B610" s="55"/>
+      <c r="C610" s="55"/>
     </row>
     <row r="611" ht="34.5" customHeight="1">
-      <c r="B611" s="32"/>
-      <c r="C611" s="32"/>
+      <c r="B611" s="55"/>
+      <c r="C611" s="55"/>
     </row>
     <row r="612" ht="34.5" customHeight="1">
-      <c r="B612" s="32"/>
-      <c r="C612" s="32"/>
+      <c r="B612" s="55"/>
+      <c r="C612" s="55"/>
     </row>
     <row r="613" ht="34.5" customHeight="1">
-      <c r="B613" s="32"/>
-      <c r="C613" s="32"/>
+      <c r="B613" s="55"/>
+      <c r="C613" s="55"/>
     </row>
     <row r="614" ht="34.5" customHeight="1">
-      <c r="B614" s="32"/>
-      <c r="C614" s="32"/>
+      <c r="B614" s="55"/>
+      <c r="C614" s="55"/>
     </row>
     <row r="615" ht="34.5" customHeight="1">
-      <c r="B615" s="32"/>
-      <c r="C615" s="32"/>
+      <c r="B615" s="55"/>
+      <c r="C615" s="55"/>
     </row>
     <row r="616" ht="34.5" customHeight="1">
-      <c r="B616" s="32"/>
-      <c r="C616" s="32"/>
+      <c r="B616" s="55"/>
+      <c r="C616" s="55"/>
     </row>
     <row r="617" ht="34.5" customHeight="1">
-      <c r="B617" s="32"/>
-      <c r="C617" s="32"/>
+      <c r="B617" s="55"/>
+      <c r="C617" s="55"/>
     </row>
     <row r="618" ht="34.5" customHeight="1">
-      <c r="B618" s="32"/>
-      <c r="C618" s="32"/>
+      <c r="B618" s="55"/>
+      <c r="C618" s="55"/>
     </row>
     <row r="619" ht="34.5" customHeight="1">
-      <c r="B619" s="32"/>
-      <c r="C619" s="32"/>
+      <c r="B619" s="55"/>
+      <c r="C619" s="55"/>
     </row>
     <row r="620" ht="34.5" customHeight="1">
-      <c r="B620" s="32"/>
-      <c r="C620" s="32"/>
+      <c r="B620" s="55"/>
+      <c r="C620" s="55"/>
     </row>
     <row r="621" ht="34.5" customHeight="1">
-      <c r="B621" s="32"/>
-      <c r="C621" s="32"/>
+      <c r="B621" s="55"/>
+      <c r="C621" s="55"/>
     </row>
     <row r="622" ht="34.5" customHeight="1">
-      <c r="B622" s="32"/>
-      <c r="C622" s="32"/>
+      <c r="B622" s="55"/>
+      <c r="C622" s="55"/>
     </row>
     <row r="623" ht="34.5" customHeight="1">
-      <c r="B623" s="32"/>
-      <c r="C623" s="32"/>
+      <c r="B623" s="55"/>
+      <c r="C623" s="55"/>
     </row>
     <row r="624" ht="34.5" customHeight="1">
-      <c r="B624" s="32"/>
-      <c r="C624" s="32"/>
+      <c r="B624" s="55"/>
+      <c r="C624" s="55"/>
     </row>
     <row r="625" ht="34.5" customHeight="1">
-      <c r="B625" s="32"/>
-      <c r="C625" s="32"/>
+      <c r="B625" s="55"/>
+      <c r="C625" s="55"/>
     </row>
     <row r="626" ht="34.5" customHeight="1">
-      <c r="B626" s="32"/>
-      <c r="C626" s="32"/>
+      <c r="B626" s="55"/>
+      <c r="C626" s="55"/>
     </row>
     <row r="627" ht="34.5" customHeight="1">
-      <c r="B627" s="32"/>
-      <c r="C627" s="32"/>
+      <c r="B627" s="55"/>
+      <c r="C627" s="55"/>
     </row>
     <row r="628" ht="34.5" customHeight="1">
-      <c r="B628" s="32"/>
-      <c r="C628" s="32"/>
+      <c r="B628" s="55"/>
+      <c r="C628" s="55"/>
     </row>
     <row r="629" ht="34.5" customHeight="1">
-      <c r="B629" s="32"/>
-      <c r="C629" s="32"/>
+      <c r="B629" s="55"/>
+      <c r="C629" s="55"/>
     </row>
     <row r="630" ht="34.5" customHeight="1">
-      <c r="B630" s="32"/>
-      <c r="C630" s="32"/>
+      <c r="B630" s="55"/>
+      <c r="C630" s="55"/>
     </row>
     <row r="631" ht="34.5" customHeight="1">
-      <c r="B631" s="32"/>
-      <c r="C631" s="32"/>
+      <c r="B631" s="55"/>
+      <c r="C631" s="55"/>
     </row>
     <row r="632" ht="34.5" customHeight="1">
-      <c r="B632" s="32"/>
-      <c r="C632" s="32"/>
+      <c r="B632" s="55"/>
+      <c r="C632" s="55"/>
     </row>
     <row r="633" ht="34.5" customHeight="1">
-      <c r="B633" s="32"/>
-      <c r="C633" s="32"/>
+      <c r="B633" s="55"/>
+      <c r="C633" s="55"/>
     </row>
     <row r="634" ht="34.5" customHeight="1">
-      <c r="B634" s="32"/>
-      <c r="C634" s="32"/>
+      <c r="B634" s="55"/>
+      <c r="C634" s="55"/>
     </row>
     <row r="635" ht="34.5" customHeight="1">
-      <c r="B635" s="32"/>
-      <c r="C635" s="32"/>
+      <c r="B635" s="55"/>
+      <c r="C635" s="55"/>
     </row>
     <row r="636" ht="34.5" customHeight="1">
-      <c r="B636" s="32"/>
-      <c r="C636" s="32"/>
+      <c r="B636" s="55"/>
+      <c r="C636" s="55"/>
     </row>
     <row r="637" ht="34.5" customHeight="1">
-      <c r="B637" s="32"/>
-      <c r="C637" s="32"/>
+      <c r="B637" s="55"/>
+      <c r="C637" s="55"/>
     </row>
     <row r="638" ht="34.5" customHeight="1">
-      <c r="B638" s="32"/>
-      <c r="C638" s="32"/>
+      <c r="B638" s="55"/>
+      <c r="C638" s="55"/>
     </row>
     <row r="639" ht="34.5" customHeight="1">
-      <c r="B639" s="32"/>
-      <c r="C639" s="32"/>
+      <c r="B639" s="55"/>
+      <c r="C639" s="55"/>
     </row>
     <row r="640" ht="34.5" customHeight="1">
-      <c r="B640" s="32"/>
-      <c r="C640" s="32"/>
+      <c r="B640" s="55"/>
+      <c r="C640" s="55"/>
     </row>
     <row r="641" ht="34.5" customHeight="1">
-      <c r="B641" s="32"/>
-      <c r="C641" s="32"/>
+      <c r="B641" s="55"/>
+      <c r="C641" s="55"/>
     </row>
     <row r="642" ht="34.5" customHeight="1">
-      <c r="B642" s="32"/>
-      <c r="C642" s="32"/>
+      <c r="B642" s="55"/>
+      <c r="C642" s="55"/>
     </row>
     <row r="643" ht="34.5" customHeight="1">
-      <c r="B643" s="32"/>
-      <c r="C643" s="32"/>
+      <c r="B643" s="55"/>
+      <c r="C643" s="55"/>
     </row>
     <row r="644" ht="34.5" customHeight="1">
-      <c r="B644" s="32"/>
-      <c r="C644" s="32"/>
+      <c r="B644" s="55"/>
+      <c r="C644" s="55"/>
     </row>
     <row r="645" ht="34.5" customHeight="1">
-      <c r="B645" s="32"/>
-      <c r="C645" s="32"/>
+      <c r="B645" s="55"/>
+      <c r="C645" s="55"/>
     </row>
     <row r="646" ht="34.5" customHeight="1">
-      <c r="B646" s="32"/>
-      <c r="C646" s="32"/>
+      <c r="B646" s="55"/>
+      <c r="C646" s="55"/>
     </row>
     <row r="647" ht="34.5" customHeight="1">
-      <c r="B647" s="32"/>
-      <c r="C647" s="32"/>
+      <c r="B647" s="55"/>
+      <c r="C647" s="55"/>
     </row>
     <row r="648" ht="34.5" customHeight="1">
-      <c r="B648" s="32"/>
-      <c r="C648" s="32"/>
+      <c r="B648" s="55"/>
+      <c r="C648" s="55"/>
     </row>
     <row r="649" ht="34.5" customHeight="1">
-      <c r="B649" s="32"/>
-      <c r="C649" s="32"/>
+      <c r="B649" s="55"/>
+      <c r="C649" s="55"/>
     </row>
     <row r="650" ht="34.5" customHeight="1">
-      <c r="B650" s="32"/>
-      <c r="C650" s="32"/>
+      <c r="B650" s="55"/>
+      <c r="C650" s="55"/>
     </row>
     <row r="651" ht="34.5" customHeight="1">
-      <c r="B651" s="32"/>
-      <c r="C651" s="32"/>
+      <c r="B651" s="55"/>
+      <c r="C651" s="55"/>
     </row>
     <row r="652" ht="34.5" customHeight="1">
-      <c r="B652" s="32"/>
-      <c r="C652" s="32"/>
+      <c r="B652" s="55"/>
+      <c r="C652" s="55"/>
     </row>
     <row r="653" ht="34.5" customHeight="1">
-      <c r="B653" s="32"/>
-      <c r="C653" s="32"/>
+      <c r="B653" s="55"/>
+      <c r="C653" s="55"/>
     </row>
     <row r="654" ht="34.5" customHeight="1">
-      <c r="B654" s="32"/>
-      <c r="C654" s="32"/>
+      <c r="B654" s="55"/>
+      <c r="C654" s="55"/>
     </row>
     <row r="655" ht="34.5" customHeight="1">
-      <c r="B655" s="32"/>
-      <c r="C655" s="32"/>
+      <c r="B655" s="55"/>
+      <c r="C655" s="55"/>
     </row>
     <row r="656" ht="34.5" customHeight="1">
-      <c r="B656" s="32"/>
-      <c r="C656" s="32"/>
+      <c r="B656" s="55"/>
+      <c r="C656" s="55"/>
     </row>
     <row r="657" ht="34.5" customHeight="1">
-      <c r="B657" s="32"/>
-      <c r="C657" s="32"/>
+      <c r="B657" s="55"/>
+      <c r="C657" s="55"/>
     </row>
     <row r="658" ht="34.5" customHeight="1">
-      <c r="B658" s="32"/>
-      <c r="C658" s="32"/>
+      <c r="B658" s="55"/>
+      <c r="C658" s="55"/>
     </row>
     <row r="659" ht="34.5" customHeight="1">
-      <c r="B659" s="32"/>
-      <c r="C659" s="32"/>
+      <c r="B659" s="55"/>
+      <c r="C659" s="55"/>
     </row>
     <row r="660" ht="34.5" customHeight="1">
-      <c r="B660" s="32"/>
-      <c r="C660" s="32"/>
+      <c r="B660" s="55"/>
+      <c r="C660" s="55"/>
     </row>
     <row r="661" ht="34.5" customHeight="1">
-      <c r="B661" s="32"/>
-      <c r="C661" s="32"/>
+      <c r="B661" s="55"/>
+      <c r="C661" s="55"/>
     </row>
     <row r="662" ht="34.5" customHeight="1">
-      <c r="B662" s="32"/>
-      <c r="C662" s="32"/>
+      <c r="B662" s="55"/>
+      <c r="C662" s="55"/>
     </row>
     <row r="663" ht="34.5" customHeight="1">
-      <c r="B663" s="32"/>
-      <c r="C663" s="32"/>
+      <c r="B663" s="55"/>
+      <c r="C663" s="55"/>
     </row>
     <row r="664" ht="34.5" customHeight="1">
-      <c r="B664" s="32"/>
-      <c r="C664" s="32"/>
+      <c r="B664" s="55"/>
+      <c r="C664" s="55"/>
     </row>
     <row r="665" ht="34.5" customHeight="1">
-      <c r="B665" s="32"/>
-      <c r="C665" s="32"/>
+      <c r="B665" s="55"/>
+      <c r="C665" s="55"/>
     </row>
     <row r="666" ht="34.5" customHeight="1">
-      <c r="B666" s="32"/>
-      <c r="C666" s="32"/>
+      <c r="B666" s="55"/>
+      <c r="C666" s="55"/>
     </row>
     <row r="667" ht="34.5" customHeight="1">
-      <c r="B667" s="32"/>
-      <c r="C667" s="32"/>
+      <c r="B667" s="55"/>
+      <c r="C667" s="55"/>
     </row>
     <row r="668" ht="34.5" customHeight="1">
-      <c r="B668" s="32"/>
-      <c r="C668" s="32"/>
+      <c r="B668" s="55"/>
+      <c r="C668" s="55"/>
     </row>
     <row r="669" ht="34.5" customHeight="1">
-      <c r="B669" s="32"/>
-      <c r="C669" s="32"/>
+      <c r="B669" s="55"/>
+      <c r="C669" s="55"/>
     </row>
     <row r="670" ht="34.5" customHeight="1">
-      <c r="B670" s="32"/>
-      <c r="C670" s="32"/>
+      <c r="B670" s="55"/>
+      <c r="C670" s="55"/>
     </row>
     <row r="671" ht="34.5" customHeight="1">
-      <c r="B671" s="32"/>
-      <c r="C671" s="32"/>
+      <c r="B671" s="55"/>
+      <c r="C671" s="55"/>
     </row>
     <row r="672" ht="34.5" customHeight="1">
-      <c r="B672" s="32"/>
-      <c r="C672" s="32"/>
+      <c r="B672" s="55"/>
+      <c r="C672" s="55"/>
     </row>
     <row r="673" ht="34.5" customHeight="1">
-      <c r="B673" s="32"/>
-      <c r="C673" s="32"/>
+      <c r="B673" s="55"/>
+      <c r="C673" s="55"/>
     </row>
     <row r="674" ht="34.5" customHeight="1">
-      <c r="B674" s="32"/>
-      <c r="C674" s="32"/>
+      <c r="B674" s="55"/>
+      <c r="C674" s="55"/>
     </row>
     <row r="675" ht="34.5" customHeight="1">
-      <c r="B675" s="32"/>
-      <c r="C675" s="32"/>
+      <c r="B675" s="55"/>
+      <c r="C675" s="55"/>
     </row>
     <row r="676" ht="34.5" customHeight="1">
-      <c r="B676" s="32"/>
-      <c r="C676" s="32"/>
+      <c r="B676" s="55"/>
+      <c r="C676" s="55"/>
     </row>
     <row r="677" ht="34.5" customHeight="1">
-      <c r="B677" s="32"/>
-      <c r="C677" s="32"/>
+      <c r="B677" s="55"/>
+      <c r="C677" s="55"/>
     </row>
     <row r="678" ht="34.5" customHeight="1">
-      <c r="B678" s="32"/>
-      <c r="C678" s="32"/>
+      <c r="B678" s="55"/>
+      <c r="C678" s="55"/>
     </row>
     <row r="679" ht="34.5" customHeight="1">
-      <c r="B679" s="32"/>
-      <c r="C679" s="32"/>
+      <c r="B679" s="55"/>
+      <c r="C679" s="55"/>
     </row>
     <row r="680" ht="34.5" customHeight="1">
-      <c r="B680" s="32"/>
-      <c r="C680" s="32"/>
+      <c r="B680" s="55"/>
+      <c r="C680" s="55"/>
     </row>
     <row r="681" ht="34.5" customHeight="1">
-      <c r="B681" s="32"/>
-      <c r="C681" s="32"/>
+      <c r="B681" s="55"/>
+      <c r="C681" s="55"/>
     </row>
     <row r="682" ht="34.5" customHeight="1">
-      <c r="B682" s="32"/>
-      <c r="C682" s="32"/>
+      <c r="B682" s="55"/>
+      <c r="C682" s="55"/>
     </row>
     <row r="683" ht="34.5" customHeight="1">
-      <c r="B683" s="32"/>
-      <c r="C683" s="32"/>
+      <c r="B683" s="55"/>
+      <c r="C683" s="55"/>
     </row>
     <row r="684" ht="34.5" customHeight="1">
-      <c r="B684" s="32"/>
-      <c r="C684" s="32"/>
+      <c r="B684" s="55"/>
+      <c r="C684" s="55"/>
     </row>
     <row r="685" ht="34.5" customHeight="1">
-      <c r="B685" s="32"/>
-      <c r="C685" s="32"/>
+      <c r="B685" s="55"/>
+      <c r="C685" s="55"/>
     </row>
     <row r="686" ht="34.5" customHeight="1">
-      <c r="B686" s="32"/>
-      <c r="C686" s="32"/>
+      <c r="B686" s="55"/>
+      <c r="C686" s="55"/>
     </row>
     <row r="687" ht="34.5" customHeight="1">
-      <c r="B687" s="32"/>
-      <c r="C687" s="32"/>
+      <c r="B687" s="55"/>
+      <c r="C687" s="55"/>
     </row>
     <row r="688" ht="34.5" customHeight="1">
-      <c r="B688" s="32"/>
-      <c r="C688" s="32"/>
+      <c r="B688" s="55"/>
+      <c r="C688" s="55"/>
     </row>
     <row r="689" ht="34.5" customHeight="1">
-      <c r="B689" s="32"/>
-      <c r="C689" s="32"/>
+      <c r="B689" s="55"/>
+      <c r="C689" s="55"/>
     </row>
     <row r="690" ht="34.5" customHeight="1">
-      <c r="B690" s="32"/>
-      <c r="C690" s="32"/>
+      <c r="B690" s="55"/>
+      <c r="C690" s="55"/>
     </row>
     <row r="691" ht="34.5" customHeight="1">
-      <c r="B691" s="32"/>
-      <c r="C691" s="32"/>
+      <c r="B691" s="55"/>
+      <c r="C691" s="55"/>
     </row>
     <row r="692" ht="34.5" customHeight="1">
-      <c r="B692" s="32"/>
-      <c r="C692" s="32"/>
+      <c r="B692" s="55"/>
+      <c r="C692" s="55"/>
     </row>
     <row r="693" ht="34.5" customHeight="1">
-      <c r="B693" s="32"/>
-      <c r="C693" s="32"/>
+      <c r="B693" s="55"/>
+      <c r="C693" s="55"/>
     </row>
     <row r="694" ht="34.5" customHeight="1">
-      <c r="B694" s="32"/>
-      <c r="C694" s="32"/>
+      <c r="B694" s="55"/>
+      <c r="C694" s="55"/>
     </row>
     <row r="695" ht="34.5" customHeight="1">
-      <c r="B695" s="32"/>
-      <c r="C695" s="32"/>
+      <c r="B695" s="55"/>
+      <c r="C695" s="55"/>
     </row>
     <row r="696" ht="34.5" customHeight="1">
-      <c r="B696" s="32"/>
-      <c r="C696" s="32"/>
+      <c r="B696" s="55"/>
+      <c r="C696" s="55"/>
     </row>
     <row r="697" ht="34.5" customHeight="1">
-      <c r="B697" s="32"/>
-      <c r="C697" s="32"/>
+      <c r="B697" s="55"/>
+      <c r="C697" s="55"/>
     </row>
     <row r="698" ht="34.5" customHeight="1">
-      <c r="B698" s="32"/>
-      <c r="C698" s="32"/>
+      <c r="B698" s="55"/>
+      <c r="C698" s="55"/>
     </row>
     <row r="699" ht="34.5" customHeight="1">
-      <c r="B699" s="32"/>
-      <c r="C699" s="32"/>
+      <c r="B699" s="55"/>
+      <c r="C699" s="55"/>
     </row>
     <row r="700" ht="34.5" customHeight="1">
-      <c r="B700" s="32"/>
-      <c r="C700" s="32"/>
+      <c r="B700" s="55"/>
+      <c r="C700" s="55"/>
     </row>
     <row r="701" ht="34.5" customHeight="1">
-      <c r="B701" s="32"/>
-      <c r="C701" s="32"/>
+      <c r="B701" s="55"/>
+      <c r="C701" s="55"/>
     </row>
     <row r="702" ht="34.5" customHeight="1">
-      <c r="B702" s="32"/>
-      <c r="C702" s="32"/>
+      <c r="B702" s="55"/>
+      <c r="C702" s="55"/>
     </row>
     <row r="703" ht="34.5" customHeight="1">
-      <c r="B703" s="32"/>
-      <c r="C703" s="32"/>
+      <c r="B703" s="55"/>
+      <c r="C703" s="55"/>
     </row>
     <row r="704" ht="34.5" customHeight="1">
-      <c r="B704" s="32"/>
-      <c r="C704" s="32"/>
+      <c r="B704" s="55"/>
+      <c r="C704" s="55"/>
     </row>
     <row r="705" ht="34.5" customHeight="1">
-      <c r="B705" s="32"/>
-      <c r="C705" s="32"/>
+      <c r="B705" s="55"/>
+      <c r="C705" s="55"/>
     </row>
     <row r="706" ht="34.5" customHeight="1">
-      <c r="B706" s="32"/>
-      <c r="C706" s="32"/>
+      <c r="B706" s="55"/>
+      <c r="C706" s="55"/>
     </row>
     <row r="707" ht="34.5" customHeight="1">
-      <c r="B707" s="32"/>
-      <c r="C707" s="32"/>
+      <c r="B707" s="55"/>
+      <c r="C707" s="55"/>
     </row>
     <row r="708" ht="34.5" customHeight="1">
-      <c r="B708" s="32"/>
-      <c r="C708" s="32"/>
+      <c r="B708" s="55"/>
+      <c r="C708" s="55"/>
     </row>
     <row r="709" ht="34.5" customHeight="1">
-      <c r="B709" s="32"/>
-      <c r="C709" s="32"/>
+      <c r="B709" s="55"/>
+      <c r="C709" s="55"/>
     </row>
     <row r="710" ht="34.5" customHeight="1">
-      <c r="B710" s="32"/>
-      <c r="C710" s="32"/>
+      <c r="B710" s="55"/>
+      <c r="C710" s="55"/>
     </row>
     <row r="711" ht="34.5" customHeight="1">
-      <c r="B711" s="32"/>
-      <c r="C711" s="32"/>
+      <c r="B711" s="55"/>
+      <c r="C711" s="55"/>
     </row>
     <row r="712" ht="34.5" customHeight="1">
-      <c r="B712" s="32"/>
-      <c r="C712" s="32"/>
+      <c r="B712" s="55"/>
+      <c r="C712" s="55"/>
     </row>
     <row r="713" ht="34.5" customHeight="1">
-      <c r="B713" s="32"/>
-      <c r="C713" s="32"/>
+      <c r="B713" s="55"/>
+      <c r="C713" s="55"/>
     </row>
     <row r="714" ht="34.5" customHeight="1">
-      <c r="B714" s="32"/>
-      <c r="C714" s="32"/>
+      <c r="B714" s="55"/>
+      <c r="C714" s="55"/>
     </row>
     <row r="715" ht="34.5" customHeight="1">
-      <c r="B715" s="32"/>
-      <c r="C715" s="32"/>
+      <c r="B715" s="55"/>
+      <c r="C715" s="55"/>
     </row>
     <row r="716" ht="34.5" customHeight="1">
-      <c r="B716" s="32"/>
-      <c r="C716" s="32"/>
+      <c r="B716" s="55"/>
+      <c r="C716" s="55"/>
     </row>
     <row r="717" ht="34.5" customHeight="1">
-      <c r="B717" s="32"/>
-      <c r="C717" s="32"/>
+      <c r="B717" s="55"/>
+      <c r="C717" s="55"/>
     </row>
     <row r="718" ht="34.5" customHeight="1">
-      <c r="B718" s="32"/>
-      <c r="C718" s="32"/>
+      <c r="B718" s="55"/>
+      <c r="C718" s="55"/>
     </row>
     <row r="719" ht="34.5" customHeight="1">
-      <c r="B719" s="32"/>
-      <c r="C719" s="32"/>
+      <c r="B719" s="55"/>
+      <c r="C719" s="55"/>
     </row>
     <row r="720" ht="34.5" customHeight="1">
-      <c r="B720" s="32"/>
-      <c r="C720" s="32"/>
+      <c r="B720" s="55"/>
+      <c r="C720" s="55"/>
     </row>
     <row r="721" ht="34.5" customHeight="1">
-      <c r="B721" s="32"/>
-      <c r="C721" s="32"/>
+      <c r="B721" s="55"/>
+      <c r="C721" s="55"/>
     </row>
     <row r="722" ht="34.5" customHeight="1">
-      <c r="B722" s="32"/>
-      <c r="C722" s="32"/>
+      <c r="B722" s="55"/>
+      <c r="C722" s="55"/>
     </row>
     <row r="723" ht="34.5" customHeight="1">
-      <c r="B723" s="32"/>
-      <c r="C723" s="32"/>
+      <c r="B723" s="55"/>
+      <c r="C723" s="55"/>
     </row>
     <row r="724" ht="34.5" customHeight="1">
-      <c r="B724" s="32"/>
-      <c r="C724" s="32"/>
+      <c r="B724" s="55"/>
+      <c r="C724" s="55"/>
     </row>
     <row r="725" ht="34.5" customHeight="1">
-      <c r="B725" s="32"/>
-      <c r="C725" s="32"/>
+      <c r="B725" s="55"/>
+      <c r="C725" s="55"/>
     </row>
     <row r="726" ht="34.5" customHeight="1">
-      <c r="B726" s="32"/>
-      <c r="C726" s="32"/>
+      <c r="B726" s="55"/>
+      <c r="C726" s="55"/>
     </row>
     <row r="727" ht="34.5" customHeight="1">
-      <c r="B727" s="32"/>
-      <c r="C727" s="32"/>
+      <c r="B727" s="55"/>
+      <c r="C727" s="55"/>
     </row>
     <row r="728" ht="34.5" customHeight="1">
-      <c r="B728" s="32"/>
-      <c r="C728" s="32"/>
+      <c r="B728" s="55"/>
+      <c r="C728" s="55"/>
     </row>
     <row r="729" ht="34.5" customHeight="1">
-      <c r="B729" s="32"/>
-      <c r="C729" s="32"/>
+      <c r="B729" s="55"/>
+      <c r="C729" s="55"/>
     </row>
     <row r="730" ht="34.5" customHeight="1">
-      <c r="B730" s="32"/>
-      <c r="C730" s="32"/>
+      <c r="B730" s="55"/>
+      <c r="C730" s="55"/>
     </row>
     <row r="731" ht="34.5" customHeight="1">
-      <c r="B731" s="32"/>
-      <c r="C731" s="32"/>
+      <c r="B731" s="55"/>
+      <c r="C731" s="55"/>
     </row>
     <row r="732" ht="34.5" customHeight="1">
-      <c r="B732" s="32"/>
-      <c r="C732" s="32"/>
+      <c r="B732" s="55"/>
+      <c r="C732" s="55"/>
     </row>
     <row r="733" ht="34.5" customHeight="1">
-      <c r="B733" s="32"/>
-      <c r="C733" s="32"/>
+      <c r="B733" s="55"/>
+      <c r="C733" s="55"/>
     </row>
     <row r="734" ht="34.5" customHeight="1">
-      <c r="B734" s="32"/>
-      <c r="C734" s="32"/>
+      <c r="B734" s="55"/>
+      <c r="C734" s="55"/>
     </row>
     <row r="735" ht="34.5" customHeight="1">
-      <c r="B735" s="32"/>
-      <c r="C735" s="32"/>
+      <c r="B735" s="55"/>
+      <c r="C735" s="55"/>
     </row>
     <row r="736" ht="34.5" customHeight="1">
-      <c r="B736" s="32"/>
-      <c r="C736" s="32"/>
+      <c r="B736" s="55"/>
+      <c r="C736" s="55"/>
     </row>
     <row r="737" ht="34.5" customHeight="1">
-      <c r="B737" s="32"/>
-      <c r="C737" s="32"/>
+      <c r="B737" s="55"/>
+      <c r="C737" s="55"/>
     </row>
     <row r="738" ht="34.5" customHeight="1">
-      <c r="B738" s="32"/>
-      <c r="C738" s="32"/>
+      <c r="B738" s="55"/>
+      <c r="C738" s="55"/>
     </row>
     <row r="739" ht="34.5" customHeight="1">
-      <c r="B739" s="32"/>
-      <c r="C739" s="32"/>
+      <c r="B739" s="55"/>
+      <c r="C739" s="55"/>
     </row>
     <row r="740" ht="34.5" customHeight="1">
-      <c r="B740" s="32"/>
-      <c r="C740" s="32"/>
+      <c r="B740" s="55"/>
+      <c r="C740" s="55"/>
     </row>
     <row r="741" ht="34.5" customHeight="1">
-      <c r="B741" s="32"/>
-      <c r="C741" s="32"/>
+      <c r="B741" s="55"/>
+      <c r="C741" s="55"/>
     </row>
     <row r="742" ht="34.5" customHeight="1">
-      <c r="B742" s="32"/>
-      <c r="C742" s="32"/>
+      <c r="B742" s="55"/>
+      <c r="C742" s="55"/>
     </row>
     <row r="743" ht="34.5" customHeight="1">
-      <c r="B743" s="32"/>
-      <c r="C743" s="32"/>
+      <c r="B743" s="55"/>
+      <c r="C743" s="55"/>
     </row>
     <row r="744" ht="34.5" customHeight="1">
-      <c r="B744" s="32"/>
-      <c r="C744" s="32"/>
+      <c r="B744" s="55"/>
+      <c r="C744" s="55"/>
     </row>
     <row r="745" ht="34.5" customHeight="1">
-      <c r="B745" s="32"/>
-      <c r="C745" s="32"/>
+      <c r="B745" s="55"/>
+      <c r="C745" s="55"/>
     </row>
     <row r="746" ht="34.5" customHeight="1">
-      <c r="B746" s="32"/>
-      <c r="C746" s="32"/>
+      <c r="B746" s="55"/>
+      <c r="C746" s="55"/>
     </row>
     <row r="747" ht="34.5" customHeight="1">
-      <c r="B747" s="32"/>
-      <c r="C747" s="32"/>
+      <c r="B747" s="55"/>
+      <c r="C747" s="55"/>
     </row>
     <row r="748" ht="34.5" customHeight="1">
-      <c r="B748" s="32"/>
-      <c r="C748" s="32"/>
+      <c r="B748" s="55"/>
+      <c r="C748" s="55"/>
     </row>
     <row r="749" ht="34.5" customHeight="1">
-      <c r="B749" s="32"/>
-      <c r="C749" s="32"/>
+      <c r="B749" s="55"/>
+      <c r="C749" s="55"/>
     </row>
     <row r="750" ht="34.5" customHeight="1">
-      <c r="B750" s="32"/>
-      <c r="C750" s="32"/>
+      <c r="B750" s="55"/>
+      <c r="C750" s="55"/>
     </row>
     <row r="751" ht="34.5" customHeight="1">
-      <c r="B751" s="32"/>
-      <c r="C751" s="32"/>
+      <c r="B751" s="55"/>
+      <c r="C751" s="55"/>
     </row>
     <row r="752" ht="34.5" customHeight="1">
-      <c r="B752" s="32"/>
-      <c r="C752" s="32"/>
+      <c r="B752" s="55"/>
+      <c r="C752" s="55"/>
     </row>
     <row r="753" ht="34.5" customHeight="1">
-      <c r="B753" s="32"/>
-      <c r="C753" s="32"/>
+      <c r="B753" s="55"/>
+      <c r="C753" s="55"/>
     </row>
     <row r="754" ht="34.5" customHeight="1">
-      <c r="B754" s="32"/>
-      <c r="C754" s="32"/>
+      <c r="B754" s="55"/>
+      <c r="C754" s="55"/>
     </row>
     <row r="755" ht="34.5" customHeight="1">
-      <c r="B755" s="32"/>
-      <c r="C755" s="32"/>
+      <c r="B755" s="55"/>
+      <c r="C755" s="55"/>
     </row>
     <row r="756" ht="34.5" customHeight="1">
-      <c r="B756" s="32"/>
-      <c r="C756" s="32"/>
+      <c r="B756" s="55"/>
+      <c r="C756" s="55"/>
     </row>
     <row r="757" ht="34.5" customHeight="1">
-      <c r="B757" s="32"/>
-      <c r="C757" s="32"/>
+      <c r="B757" s="55"/>
+      <c r="C757" s="55"/>
     </row>
     <row r="758" ht="34.5" customHeight="1">
-      <c r="B758" s="32"/>
-      <c r="C758" s="32"/>
+      <c r="B758" s="55"/>
+      <c r="C758" s="55"/>
     </row>
     <row r="759" ht="34.5" customHeight="1">
-      <c r="B759" s="32"/>
-      <c r="C759" s="32"/>
+      <c r="B759" s="55"/>
+      <c r="C759" s="55"/>
     </row>
     <row r="760" ht="34.5" customHeight="1">
-      <c r="B760" s="32"/>
-      <c r="C760" s="32"/>
+      <c r="B760" s="55"/>
+      <c r="C760" s="55"/>
     </row>
     <row r="761" ht="34.5" customHeight="1">
-      <c r="B761" s="32"/>
-      <c r="C761" s="32"/>
+      <c r="B761" s="55"/>
+      <c r="C761" s="55"/>
     </row>
     <row r="762" ht="34.5" customHeight="1">
-      <c r="B762" s="32"/>
-      <c r="C762" s="32"/>
+      <c r="B762" s="55"/>
+      <c r="C762" s="55"/>
     </row>
     <row r="763" ht="34.5" customHeight="1">
-      <c r="B763" s="32"/>
-      <c r="C763" s="32"/>
+      <c r="B763" s="55"/>
+      <c r="C763" s="55"/>
     </row>
     <row r="764" ht="34.5" customHeight="1">
-      <c r="B764" s="32"/>
-      <c r="C764" s="32"/>
+      <c r="B764" s="55"/>
+      <c r="C764" s="55"/>
     </row>
     <row r="765" ht="34.5" customHeight="1">
-      <c r="B765" s="32"/>
-      <c r="C765" s="32"/>
+      <c r="B765" s="55"/>
+      <c r="C765" s="55"/>
     </row>
     <row r="766" ht="34.5" customHeight="1">
-      <c r="B766" s="32"/>
-      <c r="C766" s="32"/>
+      <c r="B766" s="55"/>
+      <c r="C766" s="55"/>
     </row>
     <row r="767" ht="34.5" customHeight="1">
-      <c r="B767" s="32"/>
-      <c r="C767" s="32"/>
+      <c r="B767" s="55"/>
+      <c r="C767" s="55"/>
     </row>
     <row r="768" ht="34.5" customHeight="1">
-      <c r="B768" s="32"/>
-      <c r="C768" s="32"/>
+      <c r="B768" s="55"/>
+      <c r="C768" s="55"/>
     </row>
     <row r="769" ht="34.5" customHeight="1">
-      <c r="B769" s="32"/>
-      <c r="C769" s="32"/>
+      <c r="B769" s="55"/>
+      <c r="C769" s="55"/>
     </row>
     <row r="770" ht="34.5" customHeight="1">
-      <c r="B770" s="32"/>
-      <c r="C770" s="32"/>
+      <c r="B770" s="55"/>
+      <c r="C770" s="55"/>
     </row>
     <row r="771" ht="34.5" customHeight="1">
-      <c r="B771" s="32"/>
-      <c r="C771" s="32"/>
+      <c r="B771" s="55"/>
+      <c r="C771" s="55"/>
     </row>
     <row r="772" ht="34.5" customHeight="1">
-      <c r="B772" s="32"/>
-      <c r="C772" s="32"/>
+      <c r="B772" s="55"/>
+      <c r="C772" s="55"/>
     </row>
     <row r="773" ht="34.5" customHeight="1">
-      <c r="B773" s="32"/>
-      <c r="C773" s="32"/>
+      <c r="B773" s="55"/>
+      <c r="C773" s="55"/>
     </row>
     <row r="774" ht="34.5" customHeight="1">
-      <c r="B774" s="32"/>
-      <c r="C774" s="32"/>
+      <c r="B774" s="55"/>
+      <c r="C774" s="55"/>
     </row>
     <row r="775" ht="34.5" customHeight="1">
-      <c r="B775" s="32"/>
-      <c r="C775" s="32"/>
+      <c r="B775" s="55"/>
+      <c r="C775" s="55"/>
     </row>
     <row r="776" ht="34.5" customHeight="1">
-      <c r="B776" s="32"/>
-      <c r="C776" s="32"/>
+      <c r="B776" s="55"/>
+      <c r="C776" s="55"/>
     </row>
     <row r="777" ht="34.5" customHeight="1">
-      <c r="B777" s="32"/>
-      <c r="C777" s="32"/>
+      <c r="B777" s="55"/>
+      <c r="C777" s="55"/>
     </row>
     <row r="778" ht="34.5" customHeight="1">
-      <c r="B778" s="32"/>
-      <c r="C778" s="32"/>
+      <c r="B778" s="55"/>
+      <c r="C778" s="55"/>
     </row>
     <row r="779" ht="34.5" customHeight="1">
-      <c r="B779" s="32"/>
-      <c r="C779" s="32"/>
+      <c r="B779" s="55"/>
+      <c r="C779" s="55"/>
     </row>
     <row r="780" ht="34.5" customHeight="1">
-      <c r="B780" s="32"/>
-      <c r="C780" s="32"/>
+      <c r="B780" s="55"/>
+      <c r="C780" s="55"/>
     </row>
     <row r="781" ht="34.5" customHeight="1">
-      <c r="B781" s="32"/>
-      <c r="C781" s="32"/>
+      <c r="B781" s="55"/>
+      <c r="C781" s="55"/>
     </row>
     <row r="782" ht="34.5" customHeight="1">
-      <c r="B782" s="32"/>
-      <c r="C782" s="32"/>
+      <c r="B782" s="55"/>
+      <c r="C782" s="55"/>
     </row>
     <row r="783" ht="34.5" customHeight="1">
-      <c r="B783" s="32"/>
-      <c r="C783" s="32"/>
+      <c r="B783" s="55"/>
+      <c r="C783" s="55"/>
     </row>
     <row r="784" ht="34.5" customHeight="1">
-      <c r="B784" s="32"/>
-      <c r="C784" s="32"/>
+      <c r="B784" s="55"/>
+      <c r="C784" s="55"/>
     </row>
     <row r="785" ht="34.5" customHeight="1">
-      <c r="B785" s="32"/>
-      <c r="C785" s="32"/>
+      <c r="B785" s="55"/>
+      <c r="C785" s="55"/>
     </row>
     <row r="786" ht="34.5" customHeight="1">
-      <c r="B786" s="32"/>
-      <c r="C786" s="32"/>
+      <c r="B786" s="55"/>
+      <c r="C786" s="55"/>
     </row>
     <row r="787" ht="34.5" customHeight="1">
-      <c r="B787" s="32"/>
-      <c r="C787" s="32"/>
+      <c r="B787" s="55"/>
+      <c r="C787" s="55"/>
     </row>
     <row r="788" ht="34.5" customHeight="1">
-      <c r="B788" s="32"/>
-      <c r="C788" s="32"/>
+      <c r="B788" s="55"/>
+      <c r="C788" s="55"/>
     </row>
     <row r="789" ht="34.5" customHeight="1">
-      <c r="B789" s="32"/>
-      <c r="C789" s="32"/>
+      <c r="B789" s="55"/>
+      <c r="C789" s="55"/>
     </row>
     <row r="790" ht="34.5" customHeight="1">
-      <c r="B790" s="32"/>
-      <c r="C790" s="32"/>
+      <c r="B790" s="55"/>
+      <c r="C790" s="55"/>
     </row>
     <row r="791" ht="34.5" customHeight="1">
-      <c r="B791" s="32"/>
-      <c r="C791" s="32"/>
+      <c r="B791" s="55"/>
+      <c r="C791" s="55"/>
     </row>
     <row r="792" ht="34.5" customHeight="1">
-      <c r="B792" s="32"/>
-      <c r="C792" s="32"/>
+      <c r="B792" s="55"/>
+      <c r="C792" s="55"/>
     </row>
     <row r="793" ht="34.5" customHeight="1">
-      <c r="B793" s="32"/>
-      <c r="C793" s="32"/>
+      <c r="B793" s="55"/>
+      <c r="C793" s="55"/>
     </row>
     <row r="794" ht="34.5" customHeight="1">
-      <c r="B794" s="32"/>
-      <c r="C794" s="32"/>
+      <c r="B794" s="55"/>
+      <c r="C794" s="55"/>
     </row>
     <row r="795" ht="34.5" customHeight="1">
-      <c r="B795" s="32"/>
-      <c r="C795" s="32"/>
+      <c r="B795" s="55"/>
+      <c r="C795" s="55"/>
     </row>
     <row r="796" ht="34.5" customHeight="1">
-      <c r="B796" s="32"/>
-      <c r="C796" s="32"/>
+      <c r="B796" s="55"/>
+      <c r="C796" s="55"/>
     </row>
     <row r="797" ht="34.5" customHeight="1">
-      <c r="B797" s="32"/>
-      <c r="C797" s="32"/>
+      <c r="B797" s="55"/>
+      <c r="C797" s="55"/>
     </row>
     <row r="798" ht="34.5" customHeight="1">
-      <c r="B798" s="32"/>
-      <c r="C798" s="32"/>
+      <c r="B798" s="55"/>
+      <c r="C798" s="55"/>
     </row>
     <row r="799" ht="34.5" customHeight="1">
-      <c r="B799" s="32"/>
-      <c r="C799" s="32"/>
+      <c r="B799" s="55"/>
+      <c r="C799" s="55"/>
     </row>
     <row r="800" ht="34.5" customHeight="1">
-      <c r="B800" s="32"/>
-      <c r="C800" s="32"/>
+      <c r="B800" s="55"/>
+      <c r="C800" s="55"/>
     </row>
     <row r="801" ht="34.5" customHeight="1">
-      <c r="B801" s="32"/>
-      <c r="C801" s="32"/>
+      <c r="B801" s="55"/>
+      <c r="C801" s="55"/>
     </row>
     <row r="802" ht="34.5" customHeight="1">
-      <c r="B802" s="32"/>
-      <c r="C802" s="32"/>
+      <c r="B802" s="55"/>
+      <c r="C802" s="55"/>
     </row>
     <row r="803" ht="34.5" customHeight="1">
-      <c r="B803" s="32"/>
-      <c r="C803" s="32"/>
+      <c r="B803" s="55"/>
+      <c r="C803" s="55"/>
     </row>
     <row r="804" ht="34.5" customHeight="1">
-      <c r="B804" s="32"/>
-      <c r="C804" s="32"/>
+      <c r="B804" s="55"/>
+      <c r="C804" s="55"/>
     </row>
     <row r="805" ht="34.5" customHeight="1">
-      <c r="B805" s="32"/>
-      <c r="C805" s="32"/>
+      <c r="B805" s="55"/>
+      <c r="C805" s="55"/>
     </row>
     <row r="806" ht="34.5" customHeight="1">
-      <c r="B806" s="32"/>
-      <c r="C806" s="32"/>
+      <c r="B806" s="55"/>
+      <c r="C806" s="55"/>
     </row>
     <row r="807" ht="34.5" customHeight="1">
-      <c r="B807" s="32"/>
-      <c r="C807" s="32"/>
+      <c r="B807" s="55"/>
+      <c r="C807" s="55"/>
     </row>
     <row r="808" ht="34.5" customHeight="1">
-      <c r="B808" s="32"/>
-      <c r="C808" s="32"/>
+      <c r="B808" s="55"/>
+      <c r="C808" s="55"/>
     </row>
     <row r="809" ht="34.5" customHeight="1">
-      <c r="B809" s="32"/>
-      <c r="C809" s="32"/>
+      <c r="B809" s="55"/>
+      <c r="C809" s="55"/>
     </row>
     <row r="810" ht="34.5" customHeight="1">
-      <c r="B810" s="32"/>
-      <c r="C810" s="32"/>
+      <c r="B810" s="55"/>
+      <c r="C810" s="55"/>
     </row>
     <row r="811" ht="34.5" customHeight="1">
-      <c r="B811" s="32"/>
-      <c r="C811" s="32"/>
+      <c r="B811" s="55"/>
+      <c r="C811" s="55"/>
     </row>
     <row r="812" ht="34.5" customHeight="1">
-      <c r="B812" s="32"/>
-      <c r="C812" s="32"/>
+      <c r="B812" s="55"/>
+      <c r="C812" s="55"/>
     </row>
     <row r="813" ht="34.5" customHeight="1">
-      <c r="B813" s="32"/>
-      <c r="C813" s="32"/>
+      <c r="B813" s="55"/>
+      <c r="C813" s="55"/>
     </row>
     <row r="814" ht="34.5" customHeight="1">
-      <c r="B814" s="32"/>
-      <c r="C814" s="32"/>
+      <c r="B814" s="55"/>
+      <c r="C814" s="55"/>
     </row>
     <row r="815" ht="34.5" customHeight="1">
-      <c r="B815" s="32"/>
-      <c r="C815" s="32"/>
+      <c r="B815" s="55"/>
+      <c r="C815" s="55"/>
     </row>
     <row r="816" ht="34.5" customHeight="1">
-      <c r="B816" s="32"/>
-      <c r="C816" s="32"/>
+      <c r="B816" s="55"/>
+      <c r="C816" s="55"/>
     </row>
     <row r="817" ht="34.5" customHeight="1">
-      <c r="B817" s="32"/>
-      <c r="C817" s="32"/>
+      <c r="B817" s="55"/>
+      <c r="C817" s="55"/>
     </row>
     <row r="818" ht="34.5" customHeight="1">
-      <c r="B818" s="32"/>
-      <c r="C818" s="32"/>
+      <c r="B818" s="55"/>
+      <c r="C818" s="55"/>
     </row>
     <row r="819" ht="34.5" customHeight="1">
-      <c r="B819" s="32"/>
-      <c r="C819" s="32"/>
+      <c r="B819" s="55"/>
+      <c r="C819" s="55"/>
     </row>
     <row r="820" ht="34.5" customHeight="1">
-      <c r="B820" s="32"/>
-      <c r="C820" s="32"/>
+      <c r="B820" s="55"/>
+      <c r="C820" s="55"/>
     </row>
     <row r="821" ht="34.5" customHeight="1">
-      <c r="B821" s="32"/>
-      <c r="C821" s="32"/>
+      <c r="B821" s="55"/>
+      <c r="C821" s="55"/>
     </row>
     <row r="822" ht="34.5" customHeight="1">
-      <c r="B822" s="32"/>
-      <c r="C822" s="32"/>
+      <c r="B822" s="55"/>
+      <c r="C822" s="55"/>
     </row>
     <row r="823" ht="34.5" customHeight="1">
-      <c r="B823" s="32"/>
-      <c r="C823" s="32"/>
+      <c r="B823" s="55"/>
+      <c r="C823" s="55"/>
     </row>
     <row r="824" ht="34.5" customHeight="1">
-      <c r="B824" s="32"/>
-      <c r="C824" s="32"/>
+      <c r="B824" s="55"/>
+      <c r="C824" s="55"/>
     </row>
     <row r="825" ht="34.5" customHeight="1">
-      <c r="B825" s="32"/>
-      <c r="C825" s="32"/>
+      <c r="B825" s="55"/>
+      <c r="C825" s="55"/>
     </row>
     <row r="826" ht="34.5" customHeight="1">
-      <c r="B826" s="32"/>
-      <c r="C826" s="32"/>
+      <c r="B826" s="55"/>
+      <c r="C826" s="55"/>
     </row>
     <row r="827" ht="34.5" customHeight="1">
-      <c r="B827" s="32"/>
-      <c r="C827" s="32"/>
+      <c r="B827" s="55"/>
+      <c r="C827" s="55"/>
     </row>
     <row r="828" ht="34.5" customHeight="1">
-      <c r="B828" s="32"/>
-      <c r="C828" s="32"/>
+      <c r="B828" s="55"/>
+      <c r="C828" s="55"/>
     </row>
     <row r="829" ht="34.5" customHeight="1">
-      <c r="B829" s="32"/>
-      <c r="C829" s="32"/>
+      <c r="B829" s="55"/>
+      <c r="C829" s="55"/>
     </row>
     <row r="830" ht="34.5" customHeight="1">
-      <c r="B830" s="32"/>
-      <c r="C830" s="32"/>
+      <c r="B830" s="55"/>
+      <c r="C830" s="55"/>
     </row>
     <row r="831" ht="34.5" customHeight="1">
-      <c r="B831" s="32"/>
-      <c r="C831" s="32"/>
+      <c r="B831" s="55"/>
+      <c r="C831" s="55"/>
     </row>
     <row r="832" ht="34.5" customHeight="1">
-      <c r="B832" s="32"/>
-      <c r="C832" s="32"/>
+      <c r="B832" s="55"/>
+      <c r="C832" s="55"/>
     </row>
     <row r="833" ht="34.5" customHeight="1">
-      <c r="B833" s="32"/>
-      <c r="C833" s="32"/>
+      <c r="B833" s="55"/>
+      <c r="C833" s="55"/>
     </row>
     <row r="834" ht="34.5" customHeight="1">
-      <c r="B834" s="32"/>
-      <c r="C834" s="32"/>
+      <c r="B834" s="55"/>
+      <c r="C834" s="55"/>
     </row>
     <row r="835" ht="34.5" customHeight="1">
-      <c r="B835" s="32"/>
-      <c r="C835" s="32"/>
+      <c r="B835" s="55"/>
+      <c r="C835" s="55"/>
     </row>
     <row r="836" ht="34.5" customHeight="1">
-      <c r="B836" s="32"/>
-      <c r="C836" s="32"/>
+      <c r="B836" s="55"/>
+      <c r="C836" s="55"/>
     </row>
     <row r="837" ht="34.5" customHeight="1">
-      <c r="B837" s="32"/>
-      <c r="C837" s="32"/>
+      <c r="B837" s="55"/>
+      <c r="C837" s="55"/>
     </row>
     <row r="838" ht="34.5" customHeight="1">
-      <c r="B838" s="32"/>
-      <c r="C838" s="32"/>
+      <c r="B838" s="55"/>
+      <c r="C838" s="55"/>
     </row>
     <row r="839" ht="34.5" customHeight="1">
-      <c r="B839" s="32"/>
-      <c r="C839" s="32"/>
+      <c r="B839" s="55"/>
+      <c r="C839" s="55"/>
     </row>
     <row r="840" ht="34.5" customHeight="1">
-      <c r="B840" s="32"/>
-      <c r="C840" s="32"/>
+      <c r="B840" s="55"/>
+      <c r="C840" s="55"/>
     </row>
     <row r="841" ht="34.5" customHeight="1">
-      <c r="B841" s="32"/>
-      <c r="C841" s="32"/>
+      <c r="B841" s="55"/>
+      <c r="C841" s="55"/>
     </row>
     <row r="842" ht="34.5" customHeight="1">
-      <c r="B842" s="32"/>
-      <c r="C842" s="32"/>
+      <c r="B842" s="55"/>
+      <c r="C842" s="55"/>
     </row>
     <row r="843" ht="34.5" customHeight="1">
-      <c r="B843" s="32"/>
-      <c r="C843" s="32"/>
+      <c r="B843" s="55"/>
+      <c r="C843" s="55"/>
     </row>
     <row r="844" ht="34.5" customHeight="1">
-      <c r="B844" s="32"/>
-      <c r="C844" s="32"/>
+      <c r="B844" s="55"/>
+      <c r="C844" s="55"/>
     </row>
     <row r="845" ht="34.5" customHeight="1">
-      <c r="B845" s="32"/>
-      <c r="C845" s="32"/>
+      <c r="B845" s="55"/>
+      <c r="C845" s="55"/>
     </row>
     <row r="846" ht="34.5" customHeight="1">
-      <c r="B846" s="32"/>
-      <c r="C846" s="32"/>
+      <c r="B846" s="55"/>
+      <c r="C846" s="55"/>
     </row>
     <row r="847" ht="34.5" customHeight="1">
-      <c r="B847" s="32"/>
-      <c r="C847" s="32"/>
+      <c r="B847" s="55"/>
+      <c r="C847" s="55"/>
     </row>
     <row r="848" ht="34.5" customHeight="1">
-      <c r="B848" s="32"/>
-      <c r="C848" s="32"/>
+      <c r="B848" s="55"/>
+      <c r="C848" s="55"/>
     </row>
     <row r="849" ht="34.5" customHeight="1">
-      <c r="B849" s="32"/>
-      <c r="C849" s="32"/>
+      <c r="B849" s="55"/>
+      <c r="C849" s="55"/>
     </row>
     <row r="850" ht="34.5" customHeight="1">
-      <c r="B850" s="32"/>
-      <c r="C850" s="32"/>
+      <c r="B850" s="55"/>
+      <c r="C850" s="55"/>
     </row>
     <row r="851" ht="34.5" customHeight="1">
-      <c r="B851" s="32"/>
-      <c r="C851" s="32"/>
+      <c r="B851" s="55"/>
+      <c r="C851" s="55"/>
     </row>
     <row r="852" ht="34.5" customHeight="1">
-      <c r="B852" s="32"/>
-      <c r="C852" s="32"/>
+      <c r="B852" s="55"/>
+      <c r="C852" s="55"/>
     </row>
     <row r="853" ht="34.5" customHeight="1">
-      <c r="B853" s="32"/>
-      <c r="C853" s="32"/>
+      <c r="B853" s="55"/>
+      <c r="C853" s="55"/>
     </row>
     <row r="854" ht="34.5" customHeight="1">
-      <c r="B854" s="32"/>
-      <c r="C854" s="32"/>
+      <c r="B854" s="55"/>
+      <c r="C854" s="55"/>
     </row>
     <row r="855" ht="34.5" customHeight="1">
-      <c r="B855" s="32"/>
-      <c r="C855" s="32"/>
+      <c r="B855" s="55"/>
+      <c r="C855" s="55"/>
     </row>
     <row r="856" ht="34.5" customHeight="1">
-      <c r="B856" s="32"/>
-      <c r="C856" s="32"/>
+      <c r="B856" s="55"/>
+      <c r="C856" s="55"/>
     </row>
     <row r="857" ht="34.5" customHeight="1">
-      <c r="B857" s="32"/>
-      <c r="C857" s="32"/>
+      <c r="B857" s="55"/>
+      <c r="C857" s="55"/>
     </row>
     <row r="858" ht="34.5" customHeight="1">
-      <c r="B858" s="32"/>
-      <c r="C858" s="32"/>
+      <c r="B858" s="55"/>
+      <c r="C858" s="55"/>
     </row>
     <row r="859" ht="34.5" customHeight="1">
-      <c r="B859" s="32"/>
-      <c r="C859" s="32"/>
+      <c r="B859" s="55"/>
+      <c r="C859" s="55"/>
     </row>
     <row r="860" ht="34.5" customHeight="1">
-      <c r="B860" s="32"/>
-      <c r="C860" s="32"/>
+      <c r="B860" s="55"/>
+      <c r="C860" s="55"/>
     </row>
     <row r="861" ht="34.5" customHeight="1">
-      <c r="B861" s="32"/>
-      <c r="C861" s="32"/>
+      <c r="B861" s="55"/>
+      <c r="C861" s="55"/>
     </row>
     <row r="862" ht="34.5" customHeight="1">
-      <c r="B862" s="32"/>
-      <c r="C862" s="32"/>
+      <c r="B862" s="55"/>
+      <c r="C862" s="55"/>
     </row>
     <row r="863" ht="34.5" customHeight="1">
-      <c r="B863" s="32"/>
-      <c r="C863" s="32"/>
+      <c r="B863" s="55"/>
+      <c r="C863" s="55"/>
     </row>
     <row r="864" ht="34.5" customHeight="1">
-      <c r="B864" s="32"/>
-      <c r="C864" s="32"/>
+      <c r="B864" s="55"/>
+      <c r="C864" s="55"/>
     </row>
     <row r="865" ht="34.5" customHeight="1">
-      <c r="B865" s="32"/>
-      <c r="C865" s="32"/>
+      <c r="B865" s="55"/>
+      <c r="C865" s="55"/>
     </row>
     <row r="866" ht="34.5" customHeight="1">
-      <c r="B866" s="32"/>
-      <c r="C866" s="32"/>
+      <c r="B866" s="55"/>
+      <c r="C866" s="55"/>
     </row>
     <row r="867" ht="34.5" customHeight="1">
-      <c r="B867" s="32"/>
-      <c r="C867" s="32"/>
+      <c r="B867" s="55"/>
+      <c r="C867" s="55"/>
     </row>
     <row r="868" ht="34.5" customHeight="1">
-      <c r="B868" s="32"/>
-      <c r="C868" s="32"/>
+      <c r="B868" s="55"/>
+      <c r="C868" s="55"/>
     </row>
     <row r="869" ht="34.5" customHeight="1">
-      <c r="B869" s="32"/>
-      <c r="C869" s="32"/>
+      <c r="B869" s="55"/>
+      <c r="C869" s="55"/>
     </row>
     <row r="870" ht="34.5" customHeight="1">
-      <c r="B870" s="32"/>
-      <c r="C870" s="32"/>
+      <c r="B870" s="55"/>
+      <c r="C870" s="55"/>
     </row>
     <row r="871" ht="34.5" customHeight="1">
-      <c r="B871" s="32"/>
-      <c r="C871" s="32"/>
+      <c r="B871" s="55"/>
+      <c r="C871" s="55"/>
     </row>
     <row r="872" ht="34.5" customHeight="1">
-      <c r="B872" s="32"/>
-      <c r="C872" s="32"/>
+      <c r="B872" s="55"/>
+      <c r="C872" s="55"/>
     </row>
     <row r="873" ht="34.5" customHeight="1">
-      <c r="B873" s="32"/>
-      <c r="C873" s="32"/>
+      <c r="B873" s="55"/>
+      <c r="C873" s="55"/>
     </row>
     <row r="874" ht="34.5" customHeight="1">
-      <c r="B874" s="32"/>
-      <c r="C874" s="32"/>
+      <c r="B874" s="55"/>
+      <c r="C874" s="55"/>
     </row>
     <row r="875" ht="34.5" customHeight="1">
-      <c r="B875" s="32"/>
-      <c r="C875" s="32"/>
+      <c r="B875" s="55"/>
+      <c r="C875" s="55"/>
     </row>
     <row r="876" ht="34.5" customHeight="1">
-      <c r="B876" s="32"/>
-      <c r="C876" s="32"/>
+      <c r="B876" s="55"/>
+      <c r="C876" s="55"/>
     </row>
     <row r="877" ht="34.5" customHeight="1">
-      <c r="B877" s="32"/>
-      <c r="C877" s="32"/>
+      <c r="B877" s="55"/>
+      <c r="C877" s="55"/>
     </row>
     <row r="878" ht="34.5" customHeight="1">
-      <c r="B878" s="32"/>
-      <c r="C878" s="32"/>
+      <c r="B878" s="55"/>
+      <c r="C878" s="55"/>
     </row>
     <row r="879" ht="34.5" customHeight="1">
-      <c r="B879" s="32"/>
-      <c r="C879" s="32"/>
+      <c r="B879" s="55"/>
+      <c r="C879" s="55"/>
     </row>
     <row r="880" ht="34.5" customHeight="1">
-      <c r="B880" s="32"/>
-      <c r="C880" s="32"/>
+      <c r="B880" s="55"/>
+      <c r="C880" s="55"/>
     </row>
     <row r="881" ht="34.5" customHeight="1">
-      <c r="B881" s="32"/>
-      <c r="C881" s="32"/>
+      <c r="B881" s="55"/>
+      <c r="C881" s="55"/>
     </row>
     <row r="882" ht="34.5" customHeight="1">
-      <c r="B882" s="32"/>
-      <c r="C882" s="32"/>
+      <c r="B882" s="55"/>
+      <c r="C882" s="55"/>
     </row>
     <row r="883" ht="34.5" customHeight="1">
-      <c r="B883" s="32"/>
-      <c r="C883" s="32"/>
+      <c r="B883" s="55"/>
+      <c r="C883" s="55"/>
     </row>
     <row r="884" ht="34.5" customHeight="1">
-      <c r="B884" s="32"/>
-      <c r="C884" s="32"/>
+      <c r="B884" s="55"/>
+      <c r="C884" s="55"/>
     </row>
     <row r="885" ht="34.5" customHeight="1">
-      <c r="B885" s="32"/>
-      <c r="C885" s="32"/>
+      <c r="B885" s="55"/>
+      <c r="C885" s="55"/>
     </row>
     <row r="886" ht="34.5" customHeight="1">
-      <c r="B886" s="32"/>
-      <c r="C886" s="32"/>
+      <c r="B886" s="55"/>
+      <c r="C886" s="55"/>
     </row>
     <row r="887" ht="34.5" customHeight="1">
-      <c r="B887" s="32"/>
-      <c r="C887" s="32"/>
+      <c r="B887" s="55"/>
+      <c r="C887" s="55"/>
     </row>
     <row r="888" ht="34.5" customHeight="1">
-      <c r="B888" s="32"/>
-      <c r="C888" s="32"/>
+      <c r="B888" s="55"/>
+      <c r="C888" s="55"/>
     </row>
     <row r="889" ht="34.5" customHeight="1">
-      <c r="B889" s="32"/>
-      <c r="C889" s="32"/>
+      <c r="B889" s="55"/>
+      <c r="C889" s="55"/>
     </row>
     <row r="890" ht="34.5" customHeight="1">
-      <c r="B890" s="32"/>
-      <c r="C890" s="32"/>
+      <c r="B890" s="55"/>
+      <c r="C890" s="55"/>
     </row>
     <row r="891" ht="34.5" customHeight="1">
-      <c r="B891" s="32"/>
-      <c r="C891" s="32"/>
+      <c r="B891" s="55"/>
+      <c r="C891" s="55"/>
     </row>
     <row r="892" ht="34.5" customHeight="1">
-      <c r="B892" s="32"/>
-      <c r="C892" s="32"/>
+      <c r="B892" s="55"/>
+      <c r="C892" s="55"/>
     </row>
     <row r="893" ht="34.5" customHeight="1">
-      <c r="B893" s="32"/>
-      <c r="C893" s="32"/>
+      <c r="B893" s="55"/>
+      <c r="C893" s="55"/>
     </row>
     <row r="894" ht="34.5" customHeight="1">
-      <c r="B894" s="32"/>
-      <c r="C894" s="32"/>
+      <c r="B894" s="55"/>
+      <c r="C894" s="55"/>
     </row>
     <row r="895" ht="34.5" customHeight="1">
-      <c r="B895" s="32"/>
-      <c r="C895" s="32"/>
+      <c r="B895" s="55"/>
+      <c r="C895" s="55"/>
     </row>
     <row r="896" ht="34.5" customHeight="1">
-      <c r="B896" s="32"/>
-      <c r="C896" s="32"/>
+      <c r="B896" s="55"/>
+      <c r="C896" s="55"/>
     </row>
     <row r="897" ht="34.5" customHeight="1">
-      <c r="B897" s="32"/>
-      <c r="C897" s="32"/>
+      <c r="B897" s="55"/>
+      <c r="C897" s="55"/>
     </row>
     <row r="898" ht="34.5" customHeight="1">
-      <c r="B898" s="32"/>
-      <c r="C898" s="32"/>
+      <c r="B898" s="55"/>
+      <c r="C898" s="55"/>
     </row>
     <row r="899" ht="34.5" customHeight="1">
-      <c r="B899" s="32"/>
-      <c r="C899" s="32"/>
+      <c r="B899" s="55"/>
+      <c r="C899" s="55"/>
     </row>
     <row r="900" ht="34.5" customHeight="1">
-      <c r="B900" s="32"/>
-      <c r="C900" s="32"/>
+      <c r="B900" s="55"/>
+      <c r="C900" s="55"/>
     </row>
     <row r="901" ht="34.5" customHeight="1">
-      <c r="B901" s="32"/>
-      <c r="C901" s="32"/>
+      <c r="B901" s="55"/>
+      <c r="C901" s="55"/>
     </row>
     <row r="902" ht="34.5" customHeight="1">
-      <c r="B902" s="32"/>
-      <c r="C902" s="32"/>
+      <c r="B902" s="55"/>
+      <c r="C902" s="55"/>
     </row>
     <row r="903" ht="34.5" customHeight="1">
-      <c r="B903" s="32"/>
-      <c r="C903" s="32"/>
+      <c r="B903" s="55"/>
+      <c r="C903" s="55"/>
     </row>
     <row r="904" ht="34.5" customHeight="1">
-      <c r="B904" s="32"/>
-      <c r="C904" s="32"/>
+      <c r="B904" s="55"/>
+      <c r="C904" s="55"/>
     </row>
     <row r="905" ht="34.5" customHeight="1">
-      <c r="B905" s="32"/>
-      <c r="C905" s="32"/>
+      <c r="B905" s="55"/>
+      <c r="C905" s="55"/>
     </row>
     <row r="906" ht="34.5" customHeight="1">
-      <c r="B906" s="32"/>
-      <c r="C906" s="32"/>
+      <c r="B906" s="55"/>
+      <c r="C906" s="55"/>
     </row>
     <row r="907" ht="34.5" customHeight="1">
-      <c r="B907" s="32"/>
-      <c r="C907" s="32"/>
+      <c r="B907" s="55"/>
+      <c r="C907" s="55"/>
     </row>
     <row r="908" ht="34.5" customHeight="1">
-      <c r="B908" s="32"/>
-      <c r="C908" s="32"/>
+      <c r="B908" s="55"/>
+      <c r="C908" s="55"/>
     </row>
     <row r="909" ht="34.5" customHeight="1">
-      <c r="B909" s="32"/>
-      <c r="C909" s="32"/>
+      <c r="B909" s="55"/>
+      <c r="C909" s="55"/>
     </row>
     <row r="910" ht="34.5" customHeight="1">
-      <c r="B910" s="32"/>
-      <c r="C910" s="32"/>
+      <c r="B910" s="55"/>
+      <c r="C910" s="55"/>
     </row>
     <row r="911" ht="34.5" customHeight="1">
-      <c r="B911" s="32"/>
-      <c r="C911" s="32"/>
+      <c r="B911" s="55"/>
+      <c r="C911" s="55"/>
     </row>
     <row r="912" ht="34.5" customHeight="1">
-      <c r="B912" s="32"/>
-      <c r="C912" s="32"/>
+      <c r="B912" s="55"/>
+      <c r="C912" s="55"/>
     </row>
     <row r="913" ht="34.5" customHeight="1">
-      <c r="B913" s="32"/>
-      <c r="C913" s="32"/>
+      <c r="B913" s="55"/>
+      <c r="C913" s="55"/>
     </row>
     <row r="914" ht="34.5" customHeight="1">
-      <c r="B914" s="32"/>
-      <c r="C914" s="32"/>
+      <c r="B914" s="55"/>
+      <c r="C914" s="55"/>
     </row>
     <row r="915" ht="34.5" customHeight="1">
-      <c r="B915" s="32"/>
-      <c r="C915" s="32"/>
+      <c r="B915" s="55"/>
+      <c r="C915" s="55"/>
     </row>
     <row r="916" ht="34.5" customHeight="1">
-      <c r="B916" s="32"/>
-      <c r="C916" s="32"/>
+      <c r="B916" s="55"/>
+      <c r="C916" s="55"/>
     </row>
     <row r="917" ht="34.5" customHeight="1">
-      <c r="B917" s="32"/>
-      <c r="C917" s="32"/>
+      <c r="B917" s="55"/>
+      <c r="C917" s="55"/>
     </row>
     <row r="918" ht="34.5" customHeight="1">
-      <c r="B918" s="32"/>
-      <c r="C918" s="32"/>
+      <c r="B918" s="55"/>
+      <c r="C918" s="55"/>
     </row>
     <row r="919" ht="34.5" customHeight="1">
-      <c r="B919" s="32"/>
-      <c r="C919" s="32"/>
+      <c r="B919" s="55"/>
+      <c r="C919" s="55"/>
     </row>
     <row r="920" ht="34.5" customHeight="1">
-      <c r="B920" s="32"/>
-      <c r="C920" s="32"/>
+      <c r="B920" s="55"/>
+      <c r="C920" s="55"/>
     </row>
     <row r="921" ht="34.5" customHeight="1">
-      <c r="B921" s="32"/>
-      <c r="C921" s="32"/>
+      <c r="B921" s="55"/>
+      <c r="C921" s="55"/>
     </row>
     <row r="922" ht="34.5" customHeight="1">
-      <c r="B922" s="32"/>
-      <c r="C922" s="32"/>
+      <c r="B922" s="55"/>
+      <c r="C922" s="55"/>
     </row>
     <row r="923" ht="34.5" customHeight="1">
-      <c r="B923" s="32"/>
-      <c r="C923" s="32"/>
+      <c r="B923" s="55"/>
+      <c r="C923" s="55"/>
     </row>
     <row r="924" ht="34.5" customHeight="1">
-      <c r="B924" s="32"/>
-      <c r="C924" s="32"/>
+      <c r="B924" s="55"/>
+      <c r="C924" s="55"/>
     </row>
     <row r="925" ht="34.5" customHeight="1">
-      <c r="B925" s="32"/>
-      <c r="C925" s="32"/>
+      <c r="B925" s="55"/>
+      <c r="C925" s="55"/>
     </row>
     <row r="926" ht="34.5" customHeight="1">
-      <c r="B926" s="32"/>
-      <c r="C926" s="32"/>
+      <c r="B926" s="55"/>
+      <c r="C926" s="55"/>
     </row>
     <row r="927" ht="34.5" customHeight="1">
-      <c r="B927" s="32"/>
-      <c r="C927" s="32"/>
+      <c r="B927" s="55"/>
+      <c r="C927" s="55"/>
     </row>
     <row r="928" ht="34.5" customHeight="1">
-      <c r="B928" s="32"/>
-      <c r="C928" s="32"/>
+      <c r="B928" s="55"/>
+      <c r="C928" s="55"/>
     </row>
     <row r="929" ht="34.5" customHeight="1">
-      <c r="B929" s="32"/>
-      <c r="C929" s="32"/>
+      <c r="B929" s="55"/>
+      <c r="C929" s="55"/>
     </row>
     <row r="930" ht="34.5" customHeight="1">
-      <c r="B930" s="32"/>
-      <c r="C930" s="32"/>
+      <c r="B930" s="55"/>
+      <c r="C930" s="55"/>
     </row>
     <row r="931" ht="34.5" customHeight="1">
-      <c r="B931" s="32"/>
-      <c r="C931" s="32"/>
+      <c r="B931" s="55"/>
+      <c r="C931" s="55"/>
     </row>
     <row r="932" ht="34.5" customHeight="1">
-      <c r="B932" s="32"/>
-      <c r="C932" s="32"/>
+      <c r="B932" s="55"/>
+      <c r="C932" s="55"/>
     </row>
     <row r="933" ht="34.5" customHeight="1">
-      <c r="B933" s="32"/>
-      <c r="C933" s="32"/>
+      <c r="B933" s="55"/>
+      <c r="C933" s="55"/>
     </row>
     <row r="934" ht="34.5" customHeight="1">
-      <c r="B934" s="32"/>
-      <c r="C934" s="32"/>
+      <c r="B934" s="55"/>
+      <c r="C934" s="55"/>
     </row>
     <row r="935" ht="34.5" customHeight="1">
-      <c r="B935" s="32"/>
-      <c r="C935" s="32"/>
+      <c r="B935" s="55"/>
+      <c r="C935" s="55"/>
     </row>
     <row r="936" ht="34.5" customHeight="1">
-      <c r="B936" s="32"/>
-      <c r="C936" s="32"/>
+      <c r="B936" s="55"/>
+      <c r="C936" s="55"/>
     </row>
     <row r="937" ht="34.5" customHeight="1">
-      <c r="B937" s="32"/>
-      <c r="C937" s="32"/>
+      <c r="B937" s="55"/>
+      <c r="C937" s="55"/>
     </row>
     <row r="938" ht="34.5" customHeight="1">
-      <c r="B938" s="32"/>
-      <c r="C938" s="32"/>
+      <c r="B938" s="55"/>
+      <c r="C938" s="55"/>
     </row>
     <row r="939" ht="34.5" customHeight="1">
-      <c r="B939" s="32"/>
-      <c r="C939" s="32"/>
+      <c r="B939" s="55"/>
+      <c r="C939" s="55"/>
     </row>
     <row r="940" ht="34.5" customHeight="1">
-      <c r="B940" s="32"/>
-      <c r="C940" s="32"/>
+      <c r="B940" s="55"/>
+      <c r="C940" s="55"/>
     </row>
     <row r="941" ht="34.5" customHeight="1">
-      <c r="B941" s="32"/>
-      <c r="C941" s="32"/>
+      <c r="B941" s="55"/>
+      <c r="C941" s="55"/>
     </row>
     <row r="942" ht="34.5" customHeight="1">
-      <c r="B942" s="32"/>
-      <c r="C942" s="32"/>
+      <c r="B942" s="55"/>
+      <c r="C942" s="55"/>
     </row>
     <row r="943" ht="34.5" customHeight="1">
-      <c r="B943" s="32"/>
-      <c r="C943" s="32"/>
+      <c r="B943" s="55"/>
+      <c r="C943" s="55"/>
     </row>
     <row r="944" ht="34.5" customHeight="1">
-      <c r="B944" s="32"/>
-      <c r="C944" s="32"/>
+      <c r="B944" s="55"/>
+      <c r="C944" s="55"/>
     </row>
     <row r="945" ht="34.5" customHeight="1">
-      <c r="B945" s="32"/>
-      <c r="C945" s="32"/>
+      <c r="B945" s="55"/>
+      <c r="C945" s="55"/>
     </row>
     <row r="946" ht="34.5" customHeight="1">
-      <c r="B946" s="32"/>
-      <c r="C946" s="32"/>
+      <c r="B946" s="55"/>
+      <c r="C946" s="55"/>
     </row>
     <row r="947" ht="34.5" customHeight="1">
-      <c r="B947" s="32"/>
-      <c r="C947" s="32"/>
+      <c r="B947" s="55"/>
+      <c r="C947" s="55"/>
     </row>
     <row r="948" ht="34.5" customHeight="1">
-      <c r="B948" s="32"/>
-      <c r="C948" s="32"/>
+      <c r="B948" s="55"/>
+      <c r="C948" s="55"/>
     </row>
     <row r="949" ht="34.5" customHeight="1">
-      <c r="B949" s="32"/>
-      <c r="C949" s="32"/>
+      <c r="B949" s="55"/>
+      <c r="C949" s="55"/>
     </row>
     <row r="950" ht="34.5" customHeight="1">
-      <c r="B950" s="32"/>
-      <c r="C950" s="32"/>
+      <c r="B950" s="55"/>
+      <c r="C950" s="55"/>
     </row>
     <row r="951" ht="34.5" customHeight="1">
-      <c r="B951" s="32"/>
-      <c r="C951" s="32"/>
+      <c r="B951" s="55"/>
+      <c r="C951" s="55"/>
     </row>
     <row r="952" ht="34.5" customHeight="1">
-      <c r="B952" s="32"/>
-      <c r="C952" s="32"/>
+      <c r="B952" s="55"/>
+      <c r="C952" s="55"/>
     </row>
     <row r="953" ht="34.5" customHeight="1">
-      <c r="B953" s="32"/>
-      <c r="C953" s="32"/>
+      <c r="B953" s="55"/>
+      <c r="C953" s="55"/>
     </row>
     <row r="954" ht="34.5" customHeight="1">
-      <c r="B954" s="32"/>
-      <c r="C954" s="32"/>
+      <c r="B954" s="55"/>
+      <c r="C954" s="55"/>
     </row>
     <row r="955" ht="34.5" customHeight="1">
-      <c r="B955" s="32"/>
-      <c r="C955" s="32"/>
+      <c r="B955" s="55"/>
+      <c r="C955" s="55"/>
     </row>
     <row r="956" ht="34.5" customHeight="1">
-      <c r="B956" s="32"/>
-      <c r="C956" s="32"/>
+      <c r="B956" s="55"/>
+      <c r="C956" s="55"/>
     </row>
     <row r="957" ht="34.5" customHeight="1">
-      <c r="B957" s="32"/>
-      <c r="C957" s="32"/>
+      <c r="B957" s="55"/>
+      <c r="C957" s="55"/>
     </row>
     <row r="958" ht="34.5" customHeight="1">
-      <c r="B958" s="32"/>
-      <c r="C958" s="32"/>
+      <c r="B958" s="55"/>
+      <c r="C958" s="55"/>
     </row>
     <row r="959" ht="34.5" customHeight="1">
-      <c r="B959" s="32"/>
-      <c r="C959" s="32"/>
+      <c r="B959" s="55"/>
+      <c r="C959" s="55"/>
     </row>
     <row r="960" ht="34.5" customHeight="1">
-      <c r="B960" s="32"/>
-      <c r="C960" s="32"/>
+      <c r="B960" s="55"/>
+      <c r="C960" s="55"/>
     </row>
     <row r="961" ht="34.5" customHeight="1">
-      <c r="B961" s="32"/>
-      <c r="C961" s="32"/>
+      <c r="B961" s="55"/>
+      <c r="C961" s="55"/>
     </row>
     <row r="962" ht="34.5" customHeight="1">
-      <c r="B962" s="32"/>
-      <c r="C962" s="32"/>
+      <c r="B962" s="55"/>
+      <c r="C962" s="55"/>
     </row>
     <row r="963" ht="34.5" customHeight="1">
-      <c r="B963" s="32"/>
-      <c r="C963" s="32"/>
+      <c r="B963" s="55"/>
+      <c r="C963" s="55"/>
     </row>
     <row r="964" ht="34.5" customHeight="1">
-      <c r="B964" s="32"/>
-      <c r="C964" s="32"/>
+      <c r="B964" s="55"/>
+      <c r="C964" s="55"/>
     </row>
     <row r="965" ht="34.5" customHeight="1">
-      <c r="B965" s="32"/>
-      <c r="C965" s="32"/>
+      <c r="B965" s="55"/>
+      <c r="C965" s="55"/>
     </row>
     <row r="966" ht="34.5" customHeight="1">
-      <c r="B966" s="32"/>
-      <c r="C966" s="32"/>
+      <c r="B966" s="55"/>
+      <c r="C966" s="55"/>
     </row>
     <row r="967" ht="34.5" customHeight="1">
-      <c r="B967" s="32"/>
-      <c r="C967" s="32"/>
+      <c r="B967" s="55"/>
+      <c r="C967" s="55"/>
     </row>
     <row r="968" ht="34.5" customHeight="1">
-      <c r="B968" s="32"/>
-      <c r="C968" s="32"/>
+      <c r="B968" s="55"/>
+      <c r="C968" s="55"/>
     </row>
     <row r="969" ht="34.5" customHeight="1">
-      <c r="B969" s="32"/>
-      <c r="C969" s="32"/>
+      <c r="B969" s="55"/>
+      <c r="C969" s="55"/>
     </row>
     <row r="970" ht="34.5" customHeight="1">
-      <c r="B970" s="32"/>
-      <c r="C970" s="32"/>
+      <c r="B970" s="55"/>
+      <c r="C970" s="55"/>
     </row>
     <row r="971" ht="34.5" customHeight="1">
-      <c r="B971" s="32"/>
-      <c r="C971" s="32"/>
+      <c r="B971" s="55"/>
+      <c r="C971" s="55"/>
     </row>
     <row r="972" ht="34.5" customHeight="1">
-      <c r="B972" s="32"/>
-      <c r="C972" s="32"/>
+      <c r="B972" s="55"/>
+      <c r="C972" s="55"/>
     </row>
     <row r="973" ht="34.5" customHeight="1">
-      <c r="B973" s="32"/>
-      <c r="C973" s="32"/>
+      <c r="B973" s="55"/>
+      <c r="C973" s="55"/>
     </row>
     <row r="974" ht="34.5" customHeight="1">
-      <c r="B974" s="32"/>
-      <c r="C974" s="32"/>
+      <c r="B974" s="55"/>
+      <c r="C974" s="55"/>
     </row>
     <row r="975" ht="34.5" customHeight="1">
-      <c r="B975" s="32"/>
-      <c r="C975" s="32"/>
+      <c r="B975" s="55"/>
+      <c r="C975" s="55"/>
     </row>
     <row r="976" ht="34.5" customHeight="1">
-      <c r="B976" s="32"/>
-      <c r="C976" s="32"/>
+      <c r="B976" s="55"/>
+      <c r="C976" s="55"/>
     </row>
     <row r="977" ht="34.5" customHeight="1">
-      <c r="B977" s="32"/>
-      <c r="C977" s="32"/>
+      <c r="B977" s="55"/>
+      <c r="C977" s="55"/>
     </row>
     <row r="978" ht="34.5" customHeight="1">
-      <c r="B978" s="32"/>
-      <c r="C978" s="32"/>
+      <c r="B978" s="55"/>
+      <c r="C978" s="55"/>
     </row>
     <row r="979" ht="34.5" customHeight="1">
-      <c r="B979" s="32"/>
-      <c r="C979" s="32"/>
+      <c r="B979" s="55"/>
+      <c r="C979" s="55"/>
     </row>
     <row r="980" ht="34.5" customHeight="1">
-      <c r="B980" s="32"/>
-      <c r="C980" s="32"/>
+      <c r="B980" s="55"/>
+      <c r="C980" s="55"/>
     </row>
     <row r="981" ht="34.5" customHeight="1">
-      <c r="B981" s="32"/>
-      <c r="C981" s="32"/>
+      <c r="B981" s="55"/>
+      <c r="C981" s="55"/>
     </row>
     <row r="982" ht="34.5" customHeight="1">
-      <c r="B982" s="32"/>
-      <c r="C982" s="32"/>
+      <c r="B982" s="55"/>
+      <c r="C982" s="55"/>
     </row>
     <row r="983" ht="34.5" customHeight="1">
-      <c r="B983" s="32"/>
-      <c r="C983" s="32"/>
+      <c r="B983" s="55"/>
+      <c r="C983" s="55"/>
     </row>
     <row r="984" ht="34.5" customHeight="1">
-      <c r="B984" s="32"/>
-      <c r="C984" s="32"/>
+      <c r="B984" s="55"/>
+      <c r="C984" s="55"/>
     </row>
     <row r="985" ht="34.5" customHeight="1">
-      <c r="B985" s="32"/>
-      <c r="C985" s="32"/>
+      <c r="B985" s="55"/>
+      <c r="C985" s="55"/>
     </row>
     <row r="986" ht="34.5" customHeight="1">
-      <c r="B986" s="32"/>
-      <c r="C986" s="32"/>
+      <c r="B986" s="55"/>
+      <c r="C986" s="55"/>
     </row>
     <row r="987" ht="34.5" customHeight="1">
-      <c r="B987" s="32"/>
-      <c r="C987" s="32"/>
+      <c r="B987" s="55"/>
+      <c r="C987" s="55"/>
     </row>
     <row r="988" ht="34.5" customHeight="1">
-      <c r="B988" s="32"/>
-      <c r="C988" s="32"/>
+      <c r="B988" s="55"/>
+      <c r="C988" s="55"/>
     </row>
     <row r="989" ht="34.5" customHeight="1">
-      <c r="B989" s="32"/>
-      <c r="C989" s="32"/>
+      <c r="B989" s="55"/>
+      <c r="C989" s="55"/>
     </row>
     <row r="990" ht="34.5" customHeight="1">
-      <c r="B990" s="32"/>
-      <c r="C990" s="32"/>
+      <c r="B990" s="55"/>
+      <c r="C990" s="55"/>
     </row>
     <row r="991" ht="34.5" customHeight="1">
-      <c r="B991" s="32"/>
-      <c r="C991" s="32"/>
+      <c r="B991" s="55"/>
+      <c r="C991" s="55"/>
     </row>
     <row r="992" ht="34.5" customHeight="1">
-      <c r="B992" s="32"/>
-      <c r="C992" s="32"/>
+      <c r="B992" s="55"/>
+      <c r="C992" s="55"/>
     </row>
     <row r="993" ht="34.5" customHeight="1">
-      <c r="B993" s="32"/>
-      <c r="C993" s="32"/>
+      <c r="B993" s="55"/>
+      <c r="C993" s="55"/>
     </row>
     <row r="994" ht="34.5" customHeight="1">
-      <c r="B994" s="32"/>
-      <c r="C994" s="32"/>
+      <c r="B994" s="55"/>
+      <c r="C994" s="55"/>
     </row>
     <row r="995" ht="34.5" customHeight="1">
-      <c r="B995" s="32"/>
-      <c r="C995" s="32"/>
+      <c r="B995" s="55"/>
+      <c r="C995" s="55"/>
     </row>
     <row r="996" ht="34.5" customHeight="1">
-      <c r="B996" s="32"/>
-      <c r="C996" s="32"/>
+      <c r="B996" s="55"/>
+      <c r="C996" s="55"/>
     </row>
     <row r="997" ht="34.5" customHeight="1">
-      <c r="B997" s="32"/>
-      <c r="C997" s="32"/>
+      <c r="B997" s="55"/>
+      <c r="C997" s="55"/>
     </row>
     <row r="998" ht="34.5" customHeight="1">
-      <c r="B998" s="32"/>
-      <c r="C998" s="32"/>
+      <c r="B998" s="55"/>
+      <c r="C998" s="55"/>
     </row>
     <row r="999" ht="34.5" customHeight="1">
-      <c r="B999" s="32"/>
-      <c r="C999" s="32"/>
+      <c r="B999" s="55"/>
+      <c r="C999" s="55"/>
     </row>
     <row r="1000" ht="34.5" customHeight="1">
-      <c r="B1000" s="32"/>
-      <c r="C1000" s="32"/>
+      <c r="B1000" s="55"/>
+      <c r="C1000" s="55"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -5342,104 +6255,104 @@
   <sheetData>
     <row r="1" ht="33.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2" ht="33.0" customHeight="1">
-      <c r="A2" s="4">
+      <c r="A2" s="18">
         <v>1.0</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="14" t="s">
+      <c r="B2" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" ht="33.0" customHeight="1">
+      <c r="A3" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="B3" s="29" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" ht="33.0" customHeight="1">
-      <c r="A3" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" ht="33.0" customHeight="1">
+      <c r="A4" s="26">
+        <v>3.0</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" ht="33.0" customHeight="1">
+      <c r="A5" s="18">
+        <v>4.0</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="21" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" ht="33.0" customHeight="1">
-      <c r="A4" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="20" t="s">
+      <c r="D5" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" ht="33.0" customHeight="1">
+      <c r="A6" s="38">
+        <v>5.0</v>
+      </c>
+      <c r="B6" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="21" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" ht="33.0" customHeight="1">
-      <c r="A5" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="20" t="s">
+      <c r="C6" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" ht="33.0" customHeight="1">
-      <c r="A6" s="22">
-        <v>5.0</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>32</v>
+      <c r="D6" s="41" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="7" ht="33.0" customHeight="1"/>
@@ -6453,51 +7366,898 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>17</v>
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>25</v>
+      <c r="A2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>34</v>
+      <c r="A3" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="17" t="s">
+      <c r="A4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="9.75"/>
+    <col customWidth="1" min="2" max="2" width="15.63"/>
+    <col customWidth="1" min="3" max="3" width="37.5"/>
+    <col customWidth="1" min="4" max="4" width="31.38"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="23" t="s">
         <v>40</v>
       </c>
+      <c r="C3" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="42" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>42</v>
+      <c r="A5" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="42" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="47" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="14.0"/>
+    <col customWidth="1" min="2" max="2" width="16.5"/>
+    <col customWidth="1" min="3" max="3" width="57.63"/>
+    <col customWidth="1" min="4" max="4" width="40.0"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="56" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="19" t="s">
-        <v>50</v>
+      <c r="B3" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="D4" s="42" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="D6" s="42" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="D8" s="42" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="D11" s="42" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="D12" s="42" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="D13" s="42" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="D14" s="42" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="D15" s="42" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="D16" s="42" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="44" t="s">
+        <v>133</v>
+      </c>
+      <c r="B17" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="D17" s="47" t="s">
+        <v>169</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="10.25"/>
+    <col customWidth="1" min="2" max="2" width="16.13"/>
+    <col customWidth="1" min="3" max="3" width="34.25"/>
+    <col customWidth="1" min="4" max="4" width="29.63"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="56" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="D4" s="42" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="D6" s="42" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="D8" s="42" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>215</v>
+      </c>
+      <c r="D10" s="47" t="s">
+        <v>216</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="15.5"/>
+    <col customWidth="1" min="2" max="2" width="15.75"/>
+    <col customWidth="1" min="3" max="3" width="38.5"/>
+    <col customWidth="1" min="4" max="4" width="22.0"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="56" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="42" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="D6" s="42" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="39" t="s">
+        <v>183</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D8" s="42" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="D11" s="42" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="D12" s="42" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="D13" s="42" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="D14" s="42" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="44" t="s">
+        <v>133</v>
+      </c>
+      <c r="B15" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="D15" s="47" t="s">
+        <v>212</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="16.63"/>
+    <col customWidth="1" min="2" max="2" width="16.5"/>
+    <col customWidth="1" min="3" max="3" width="39.63"/>
+    <col customWidth="1" min="4" max="4" width="25.63"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="58" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="60"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="D4" s="42" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>223</v>
+      </c>
+      <c r="D5" s="47" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>
